--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46195.58406386574</v>
+        <v>46195.61060971065</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46195.58266539352</v>
+        <v>46195.685220740736</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="297">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215923636093325</t>
@@ -1588,7 +1591,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46195.58267695602</v>
+        <v>46196.1738728125</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1649,7 +1652,7 @@
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46195.582673819445</v>
+        <v>46196.17387517361</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1710,7 +1713,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46195.582670104166</v>
+        <v>46196.17387721065</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1771,7 +1774,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46195.685220740736</v>
+        <v>46196.17387903935</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2115,7 +2118,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46195.58282309028</v>
+        <v>46196.17145724537</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>59</v>
@@ -2159,8 +2162,8 @@
       <c r="R14" s="5">
         <v>46203</v>
       </c>
-      <c r="S14" s="10" t="s">
-        <v>32</v>
+      <c r="S14" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
@@ -2171,17 +2174,17 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46195.582819710646</v>
+        <v>46196.17145724537</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2214,7 +2217,7 @@
         <v>50</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2222,8 +2225,8 @@
       <c r="R15" s="8">
         <v>46203</v>
       </c>
-      <c r="S15" s="10" t="s">
-        <v>32</v>
+      <c r="S15" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T15" s="9">
         <v>0</v>
@@ -2234,26 +2237,26 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46195.58286476852</v>
+        <v>46196.171457187505</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2277,7 +2280,7 @@
         <v>50</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2285,8 +2288,8 @@
       <c r="R16" s="5">
         <v>46203</v>
       </c>
-      <c r="S16" s="10" t="s">
-        <v>32</v>
+      <c r="S16" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
@@ -2297,7 +2300,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2307,16 +2310,16 @@
         <v>46195.58294910879</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2337,10 +2340,10 @@
         <v>56</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2360,7 +2363,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2370,16 +2373,16 @@
         <v>46195.582945671296</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2400,10 +2403,10 @@
         <v>56</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2423,7 +2426,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2433,16 +2436,16 @@
         <v>46195.58294261574</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2463,10 +2466,10 @@
         <v>56</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2486,7 +2489,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2496,16 +2499,16 @@
         <v>46195.58293708334</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2526,10 +2529,10 @@
         <v>56</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2549,7 +2552,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2559,7 +2562,7 @@
         <v>46195.557115868054</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2583,7 +2586,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2596,7 +2599,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2606,16 +2609,16 @@
         <v>46195.58303875</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2633,13 +2636,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2659,7 +2662,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2669,16 +2672,16 @@
         <v>46195.58303091435</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2696,13 +2699,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2732,16 +2735,16 @@
         <v>46195.58302744213</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2759,13 +2762,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2785,7 +2788,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2795,7 +2798,7 @@
         <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2819,7 +2822,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2832,7 +2835,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2842,16 +2845,16 @@
         <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2869,13 +2872,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2895,7 +2898,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -2905,16 +2908,16 @@
         <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -2932,13 +2935,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2954,7 +2957,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -2964,16 +2967,16 @@
         <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -2991,13 +2994,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3013,7 +3016,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3023,16 +3026,16 @@
         <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3050,10 +3053,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3076,7 +3079,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3086,16 +3089,16 @@
         <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3113,13 +3116,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3129,7 +3132,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3139,16 +3142,16 @@
         <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3166,13 +3169,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3192,16 +3195,16 @@
         <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3219,10 +3222,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3245,7 +3248,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3255,16 +3258,16 @@
         <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3282,13 +3285,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3298,7 +3301,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3308,16 +3311,16 @@
         <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3335,13 +3338,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3351,7 +3354,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3361,16 +3364,16 @@
         <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3388,10 +3391,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3404,7 +3407,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3414,16 +3417,16 @@
         <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3441,10 +3444,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3467,7 +3470,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3477,16 +3480,16 @@
         <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3504,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3520,7 +3523,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3530,16 +3533,16 @@
         <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3557,13 +3560,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3573,7 +3576,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3583,7 +3586,7 @@
         <v>46195.55821990741</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3607,7 +3610,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3620,7 +3623,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3630,16 +3633,16 @@
         <v>46195.58420387731</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3657,13 +3660,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3683,7 +3686,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3693,16 +3696,16 @@
         <v>46195.58420070602</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3720,13 +3723,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3746,7 +3749,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3756,16 +3759,16 @@
         <v>46195.58419729167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3783,13 +3786,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3809,7 +3812,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -3819,16 +3822,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -3846,10 +3849,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -3882,16 +3885,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3907,13 +3910,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3923,7 +3926,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -3933,16 +3936,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3958,13 +3961,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -3974,7 +3977,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -3984,7 +3987,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4008,7 +4011,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4021,7 +4024,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4031,16 +4034,16 @@
         <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4058,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4084,7 +4087,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4094,16 +4097,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4121,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4147,7 +4150,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4157,16 +4160,16 @@
         <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4184,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4210,7 +4213,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4220,16 +4223,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4247,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4273,7 +4276,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4283,16 +4286,16 @@
         <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4310,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4336,7 +4339,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4346,16 +4349,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4373,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4399,7 +4402,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4409,7 +4412,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4433,7 +4436,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4446,7 +4449,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4456,16 +4459,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4483,13 +4486,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4509,7 +4512,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4519,16 +4522,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4546,13 +4549,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4562,7 +4565,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4572,16 +4575,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4599,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4615,7 +4618,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4625,16 +4628,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4652,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4678,7 +4681,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4688,16 +4691,16 @@
         <v>46195.58497643519</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4715,13 +4718,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4731,7 +4734,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4741,16 +4744,16 @@
         <v>46195.58497305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4768,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4784,7 +4787,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4794,16 +4797,16 @@
         <v>46195.58515287037</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4821,13 +4824,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -4847,7 +4850,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -4857,16 +4860,16 @@
         <v>46195.58511675926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -4884,13 +4887,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4900,7 +4903,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -4910,16 +4913,16 @@
         <v>46195.58511351852</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -4937,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4953,7 +4956,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -4963,7 +4966,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -4987,7 +4990,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5000,7 +5003,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5010,16 +5013,16 @@
         <v>46195.58524107639</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5037,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5073,16 +5076,16 @@
         <v>46195.5852381713</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5100,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5136,16 +5139,16 @@
         <v>46195.585235335646</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5163,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5189,7 +5192,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5199,16 +5202,16 @@
         <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5226,13 +5229,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5252,7 +5255,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5262,7 +5265,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5286,7 +5289,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5299,7 +5302,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5309,16 +5312,16 @@
         <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5336,13 +5339,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5372,16 +5375,16 @@
         <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5399,10 +5402,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5415,7 +5418,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5425,16 +5428,16 @@
         <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5452,10 +5455,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5478,16 +5481,16 @@
         <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5505,13 +5508,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5531,7 +5534,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5541,16 +5544,16 @@
         <v>46195.585438078706</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5568,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5584,7 +5587,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5594,16 +5597,16 @@
         <v>46195.58543432871</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5621,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5647,16 +5650,16 @@
         <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5672,13 +5675,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5698,7 +5701,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5708,16 +5711,16 @@
         <v>46195.585553310186</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5733,13 +5736,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5749,7 +5752,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5759,16 +5762,16 @@
         <v>46195.58554990741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5784,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5800,7 +5803,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -5810,16 +5813,16 @@
         <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5835,13 +5838,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5861,7 +5864,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -5871,16 +5874,16 @@
         <v>46195.58567954861</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -5898,13 +5901,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5914,7 +5917,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -5924,16 +5927,16 @@
         <v>46195.585675891205</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -5951,13 +5954,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5967,7 +5970,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -5977,16 +5980,16 @@
         <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6002,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6028,7 +6031,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6038,16 +6041,16 @@
         <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6065,13 +6068,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6081,7 +6084,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6091,16 +6094,16 @@
         <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6118,13 +6121,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6134,7 +6137,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6144,16 +6147,16 @@
         <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6171,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6197,7 +6200,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6207,16 +6210,16 @@
         <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6234,13 +6237,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6250,7 +6253,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6260,16 +6263,16 @@
         <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6287,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6303,7 +6306,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6313,7 +6316,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6337,7 +6340,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6350,7 +6353,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6360,16 +6363,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6387,13 +6390,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6413,7 +6416,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6423,16 +6426,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6448,13 +6451,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6464,7 +6467,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6474,16 +6477,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6501,13 +6504,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6517,7 +6520,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6527,16 +6530,16 @@
         <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6554,13 +6557,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6580,7 +6583,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6590,16 +6593,16 @@
         <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6617,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6633,7 +6636,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6643,16 +6646,16 @@
         <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6670,13 +6673,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6686,7 +6689,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6696,16 +6699,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6723,13 +6726,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6749,7 +6752,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6759,16 +6762,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6784,13 +6787,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6800,7 +6803,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -6810,16 +6813,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6835,13 +6838,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6851,7 +6854,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -6861,16 +6864,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -6888,13 +6891,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -6914,7 +6917,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -6924,16 +6927,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -6949,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -6975,16 +6978,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7000,13 +7003,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7016,7 +7019,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7026,7 +7029,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7050,7 +7053,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7063,7 +7066,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7073,16 +7076,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7100,13 +7103,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7126,7 +7129,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7136,7 +7139,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7163,13 +7166,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46195.61060971065</v>
+        <v>46196.61063163195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="299">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -109,7 +109,7 @@
     <t>Francisca Ramos</t>
   </si>
   <si>
-    <t>Baja</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -169,6 +169,9 @@
     <t>Ingenieria Jefe de proyecto:,propuesta motor - 4363</t>
   </si>
   <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -218,6 +221,9 @@
   </si>
   <si>
     <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Tarea Terminada</t>
   </si>
   <si>
     <t>1215932733979125</t>
@@ -977,7 +983,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
@@ -987,7 +993,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
   </fills>
@@ -1591,7 +1597,7 @@
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46196.1738728125</v>
+        <v>46197.19303634259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1652,7 +1658,7 @@
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46196.17387517361</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1713,7 +1719,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46196.17387721065</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1774,7 +1780,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46196.17387903935</v>
+        <v>46197.193034375</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1926,19 +1932,19 @@
       <c r="R10" s="5">
         <v>46198</v>
       </c>
-      <c r="S10" s="10" t="s">
-        <v>32</v>
+      <c r="S10" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
       </c>
-      <c r="U10" s="12" t="s">
-        <v>48</v>
+      <c r="U10" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="8">
         <v>46195.535038055554</v>
@@ -1948,7 +1954,7 @@
         <v>46195.58406326389</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -1981,7 +1987,7 @@
         <v>39</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="8">
         <v>46197</v>
@@ -1989,19 +1995,19 @@
       <c r="R11" s="8">
         <v>46198</v>
       </c>
-      <c r="S11" s="10" t="s">
-        <v>32</v>
+      <c r="S11" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T11" s="9">
         <v>0</v>
       </c>
-      <c r="U11" s="12" t="s">
-        <v>48</v>
+      <c r="U11" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5">
         <v>46195.53504337963</v>
@@ -2011,7 +2017,7 @@
         <v>46196.61063163195</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2044,7 +2050,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q12" s="5">
         <v>46197</v>
@@ -2052,29 +2058,29 @@
       <c r="R12" s="5">
         <v>46205</v>
       </c>
-      <c r="S12" s="10" t="s">
-        <v>32</v>
+      <c r="S12" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>48</v>
+      <c r="U12" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46195.56841365741</v>
+        <v>46197.499357939814</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2098,7 +2104,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2111,7 +2117,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
@@ -2121,7 +2127,7 @@
         <v>46196.17145724537</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2148,13 +2154,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2163,28 +2169,30 @@
         <v>46203</v>
       </c>
       <c r="S14" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="12" t="s">
-        <v>48</v>
+      <c r="U14" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="8">
+        <v>46197.49930170139</v>
+      </c>
       <c r="D15" s="8">
-        <v>46196.17145724537</v>
+        <v>46197.499318842594</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2211,13 +2219,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2226,37 +2234,39 @@
         <v>46203</v>
       </c>
       <c r="S15" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46197.49934962963</v>
+      </c>
       <c r="D16" s="5">
-        <v>46196.171457187505</v>
+        <v>46197.49936423611</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2274,13 +2284,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2289,18 +2299,18 @@
         <v>46203</v>
       </c>
       <c r="S16" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2310,16 +2320,16 @@
         <v>46195.58294910879</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2337,13 +2347,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2351,19 +2361,19 @@
       <c r="R17" s="8">
         <v>46225</v>
       </c>
-      <c r="S17" s="10" t="s">
-        <v>32</v>
+      <c r="S17" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T17" s="9">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>48</v>
+      <c r="U17" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2373,16 +2383,16 @@
         <v>46195.582945671296</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2400,13 +2410,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2414,19 +2424,19 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="10" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>48</v>
+      <c r="U18" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2436,16 +2446,16 @@
         <v>46195.58294261574</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2463,13 +2473,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2477,19 +2487,19 @@
       <c r="R19" s="8">
         <v>46225</v>
       </c>
-      <c r="S19" s="10" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T19" s="9">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>48</v>
+      <c r="U19" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2499,16 +2509,16 @@
         <v>46195.58293708334</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2526,13 +2536,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2540,29 +2550,31 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="10" t="s">
-        <v>32</v>
+      <c r="S20" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="12" t="s">
-        <v>48</v>
+      <c r="U20" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8">
+        <v>46197.50025414352</v>
+      </c>
       <c r="D21" s="8">
-        <v>46195.557115868054</v>
+        <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2586,7 +2598,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2594,31 +2606,37 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
+      <c r="T21" s="9">
+        <v>1</v>
+      </c>
+      <c r="U21" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46197.49944752315</v>
+      </c>
       <c r="D22" s="5">
-        <v>46195.58303875</v>
+        <v>46197.499464259265</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2636,13 +2654,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2650,38 +2668,40 @@
       <c r="R22" s="5">
         <v>46206</v>
       </c>
-      <c r="S22" s="10" t="s">
-        <v>32</v>
+      <c r="S22" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8">
+        <v>46197.500224166666</v>
+      </c>
       <c r="D23" s="8">
-        <v>46195.58303091435</v>
+        <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2699,13 +2719,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2713,38 +2733,40 @@
       <c r="R23" s="8">
         <v>46206</v>
       </c>
-      <c r="S23" s="10" t="s">
-        <v>32</v>
+      <c r="S23" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T23" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46197.50023636574</v>
+      </c>
       <c r="D24" s="5">
-        <v>46195.58302744213</v>
+        <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2762,13 +2784,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2776,19 +2798,19 @@
       <c r="R24" s="5">
         <v>46206</v>
       </c>
-      <c r="S24" s="10" t="s">
-        <v>32</v>
+      <c r="S24" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T24" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2798,7 +2820,7 @@
         <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2822,7 +2844,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2835,7 +2857,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2845,16 +2867,16 @@
         <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2872,13 +2894,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2886,19 +2908,19 @@
       <c r="R26" s="5">
         <v>46238</v>
       </c>
-      <c r="S26" s="10" t="s">
-        <v>32</v>
+      <c r="S26" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
-      <c r="U26" s="12" t="s">
-        <v>48</v>
+      <c r="U26" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -2908,16 +2930,16 @@
         <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -2935,29 +2957,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="10" t="s">
-        <v>32</v>
+      <c r="S27" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>48</v>
+      <c r="U27" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -2967,16 +2989,16 @@
         <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -2994,29 +3016,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="10" t="s">
-        <v>32</v>
+      <c r="S28" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>48</v>
+      <c r="U28" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3026,16 +3048,16 @@
         <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3053,10 +3075,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3067,19 +3089,19 @@
       <c r="R29" s="8">
         <v>46238</v>
       </c>
-      <c r="S29" s="10" t="s">
-        <v>32</v>
+      <c r="S29" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>48</v>
+      <c r="U29" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3089,16 +3111,16 @@
         <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3116,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3132,7 +3154,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3142,16 +3164,16 @@
         <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3169,13 +3191,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3185,7 +3207,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3195,16 +3217,16 @@
         <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3222,10 +3244,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3236,19 +3258,19 @@
       <c r="R32" s="5">
         <v>46266</v>
       </c>
-      <c r="S32" s="10" t="s">
-        <v>32</v>
+      <c r="S32" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
-        <v>48</v>
+      <c r="U32" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3258,16 +3280,16 @@
         <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3285,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3301,7 +3323,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3311,16 +3333,16 @@
         <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3338,13 +3360,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3354,7 +3376,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3364,16 +3386,16 @@
         <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3391,10 +3413,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3407,7 +3429,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3417,16 +3439,16 @@
         <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3444,10 +3466,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3458,19 +3480,19 @@
       <c r="R36" s="5">
         <v>46238</v>
       </c>
-      <c r="S36" s="10" t="s">
-        <v>32</v>
+      <c r="S36" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>48</v>
+      <c r="U36" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3480,16 +3502,16 @@
         <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3507,13 +3529,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3523,7 +3545,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3533,16 +3555,16 @@
         <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3560,13 +3582,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3576,7 +3598,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3586,7 +3608,7 @@
         <v>46195.55821990741</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3610,7 +3632,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3623,7 +3645,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3633,16 +3655,16 @@
         <v>46195.58420387731</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3660,13 +3682,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3674,19 +3696,19 @@
       <c r="R40" s="5">
         <v>46212</v>
       </c>
-      <c r="S40" s="10" t="s">
-        <v>32</v>
+      <c r="S40" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>48</v>
+      <c r="U40" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3696,16 +3718,16 @@
         <v>46195.58420070602</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3723,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3737,19 +3759,19 @@
       <c r="R41" s="8">
         <v>46190</v>
       </c>
-      <c r="S41" s="10" t="s">
-        <v>32</v>
+      <c r="S41" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>48</v>
+      <c r="U41" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3759,16 +3781,16 @@
         <v>46195.58419729167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3786,13 +3808,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3800,19 +3822,19 @@
       <c r="R42" s="5">
         <v>46223</v>
       </c>
-      <c r="S42" s="10" t="s">
-        <v>32</v>
+      <c r="S42" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>48</v>
+      <c r="U42" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -3822,16 +3844,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -3849,10 +3871,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3863,19 +3885,19 @@
       <c r="R43" s="8">
         <v>46269</v>
       </c>
-      <c r="S43" s="10" t="s">
-        <v>32</v>
+      <c r="S43" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>48</v>
+      <c r="U43" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -3885,16 +3907,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3910,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3926,7 +3948,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -3936,16 +3958,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3961,13 +3983,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -3977,7 +3999,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -3987,7 +4009,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4011,7 +4033,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4024,7 +4046,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4034,16 +4056,16 @@
         <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4061,13 +4083,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4075,19 +4097,19 @@
       <c r="R47" s="8">
         <v>46240</v>
       </c>
-      <c r="S47" s="10" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>48</v>
+      <c r="U47" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4097,16 +4119,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4124,13 +4146,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4138,19 +4160,19 @@
       <c r="R48" s="5">
         <v>46244</v>
       </c>
-      <c r="S48" s="10" t="s">
-        <v>32</v>
+      <c r="S48" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>48</v>
+      <c r="U48" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4160,16 +4182,16 @@
         <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4187,13 +4209,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4201,19 +4223,19 @@
       <c r="R49" s="8">
         <v>46240</v>
       </c>
-      <c r="S49" s="10" t="s">
-        <v>32</v>
+      <c r="S49" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>48</v>
+      <c r="U49" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4223,16 +4245,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4250,13 +4272,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4264,19 +4286,19 @@
       <c r="R50" s="5">
         <v>46244</v>
       </c>
-      <c r="S50" s="10" t="s">
-        <v>32</v>
+      <c r="S50" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>48</v>
+      <c r="U50" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4286,16 +4308,16 @@
         <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4313,13 +4335,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4327,19 +4349,19 @@
       <c r="R51" s="8">
         <v>46240</v>
       </c>
-      <c r="S51" s="10" t="s">
-        <v>32</v>
+      <c r="S51" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>48</v>
+      <c r="U51" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4349,16 +4371,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4376,13 +4398,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4390,19 +4412,19 @@
       <c r="R52" s="5">
         <v>46244</v>
       </c>
-      <c r="S52" s="10" t="s">
-        <v>32</v>
+      <c r="S52" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="12" t="s">
-        <v>48</v>
+      <c r="U52" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4412,7 +4434,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4436,7 +4458,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4449,7 +4471,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4459,16 +4481,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4486,13 +4508,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4500,19 +4522,19 @@
       <c r="R54" s="5">
         <v>46247</v>
       </c>
-      <c r="S54" s="10" t="s">
-        <v>32</v>
+      <c r="S54" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>48</v>
+      <c r="U54" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4522,16 +4544,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4549,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4565,7 +4587,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4575,16 +4597,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4602,13 +4624,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4618,7 +4640,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4628,16 +4650,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4655,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4669,19 +4691,19 @@
       <c r="R57" s="8">
         <v>46254</v>
       </c>
-      <c r="S57" s="10" t="s">
-        <v>32</v>
+      <c r="S57" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
-      <c r="U57" s="12" t="s">
-        <v>48</v>
+      <c r="U57" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4691,16 +4713,16 @@
         <v>46195.58497643519</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4718,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4734,7 +4756,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4744,16 +4766,16 @@
         <v>46195.58497305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4771,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4787,7 +4809,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4797,16 +4819,16 @@
         <v>46195.58515287037</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4824,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -4838,19 +4860,19 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="10" t="s">
-        <v>32</v>
+      <c r="S60" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>48</v>
+      <c r="U60" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -4860,16 +4882,16 @@
         <v>46195.58511675926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -4887,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4903,7 +4925,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -4913,16 +4935,16 @@
         <v>46195.58511351852</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -4940,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4956,7 +4978,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -4966,7 +4988,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -4990,7 +5012,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5003,26 +5025,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46195.58524107639</v>
+        <v>46197.500242800925</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5040,13 +5062,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5054,38 +5076,38 @@
       <c r="R64" s="5">
         <v>46209</v>
       </c>
-      <c r="S64" s="10" t="s">
-        <v>32</v>
+      <c r="S64" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>48</v>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.5852381713</v>
+        <v>46197.50025571759</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5103,13 +5125,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5117,38 +5139,38 @@
       <c r="R65" s="8">
         <v>46209</v>
       </c>
-      <c r="S65" s="10" t="s">
-        <v>32</v>
+      <c r="S65" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>48</v>
+      <c r="U65" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46195.585235335646</v>
+        <v>46197.49946436343</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5166,13 +5188,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5180,19 +5202,19 @@
       <c r="R66" s="5">
         <v>46209</v>
       </c>
-      <c r="S66" s="10" t="s">
-        <v>32</v>
+      <c r="S66" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>48</v>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5202,16 +5224,16 @@
         <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5229,13 +5251,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5243,19 +5265,19 @@
       <c r="R67" s="8">
         <v>46266</v>
       </c>
-      <c r="S67" s="10" t="s">
-        <v>32</v>
+      <c r="S67" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>48</v>
+      <c r="U67" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5265,7 +5287,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5289,7 +5311,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5302,7 +5324,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5312,16 +5334,16 @@
         <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5339,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5353,19 +5375,19 @@
       <c r="R69" s="8">
         <v>46262</v>
       </c>
-      <c r="S69" s="10" t="s">
-        <v>32</v>
+      <c r="S69" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
-      <c r="U69" s="12" t="s">
-        <v>48</v>
+      <c r="U69" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5375,16 +5397,16 @@
         <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5402,10 +5424,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5418,7 +5440,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5428,16 +5450,16 @@
         <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5455,10 +5477,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5471,7 +5493,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5481,16 +5503,16 @@
         <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5508,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5522,19 +5544,19 @@
       <c r="R72" s="5">
         <v>46265</v>
       </c>
-      <c r="S72" s="10" t="s">
-        <v>32</v>
+      <c r="S72" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>48</v>
+      <c r="U72" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5544,16 +5566,16 @@
         <v>46195.585438078706</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5571,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5587,7 +5609,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5597,16 +5619,16 @@
         <v>46195.58543432871</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5624,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5640,7 +5662,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5650,16 +5672,16 @@
         <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5675,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5689,19 +5711,19 @@
       <c r="R75" s="8">
         <v>46266</v>
       </c>
-      <c r="S75" s="10" t="s">
-        <v>32</v>
+      <c r="S75" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>48</v>
+      <c r="U75" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5711,16 +5733,16 @@
         <v>46195.585553310186</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5736,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5752,7 +5774,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5762,16 +5784,16 @@
         <v>46195.58554990741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5787,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O77" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="P77" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5803,7 +5825,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -5813,16 +5835,16 @@
         <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5838,13 +5860,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5852,19 +5874,19 @@
       <c r="R78" s="5">
         <v>46267</v>
       </c>
-      <c r="S78" s="10" t="s">
-        <v>32</v>
+      <c r="S78" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>48</v>
+      <c r="U78" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -5874,16 +5896,16 @@
         <v>46195.58567954861</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -5901,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5917,7 +5939,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -5927,16 +5949,16 @@
         <v>46195.585675891205</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -5954,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5970,7 +5992,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -5980,16 +6002,16 @@
         <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6005,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6019,19 +6041,19 @@
       <c r="R81" s="8">
         <v>46268</v>
       </c>
-      <c r="S81" s="10" t="s">
-        <v>32</v>
+      <c r="S81" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>48</v>
+      <c r="U81" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6041,16 +6063,16 @@
         <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6068,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6084,7 +6106,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6094,16 +6116,16 @@
         <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6121,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6137,7 +6159,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6147,16 +6169,16 @@
         <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6174,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6188,19 +6210,19 @@
       <c r="R84" s="5">
         <v>46272</v>
       </c>
-      <c r="S84" s="10" t="s">
-        <v>32</v>
+      <c r="S84" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="12" t="s">
-        <v>48</v>
+      <c r="U84" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6210,16 +6232,16 @@
         <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6237,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6253,7 +6275,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6263,16 +6285,16 @@
         <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6290,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6306,7 +6328,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6316,7 +6338,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6340,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6353,7 +6375,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6363,16 +6385,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6390,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6404,19 +6426,19 @@
       <c r="R88" s="5">
         <v>46273</v>
       </c>
-      <c r="S88" s="10" t="s">
-        <v>32</v>
+      <c r="S88" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>48</v>
+      <c r="U88" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6426,16 +6448,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6451,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6467,7 +6489,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6477,16 +6499,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6504,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6520,7 +6542,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6530,16 +6552,16 @@
         <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6557,13 +6579,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6571,19 +6593,19 @@
       <c r="R91" s="8">
         <v>46274</v>
       </c>
-      <c r="S91" s="10" t="s">
-        <v>32</v>
+      <c r="S91" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
-      <c r="U91" s="12" t="s">
-        <v>48</v>
+      <c r="U91" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6593,16 +6615,16 @@
         <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6620,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6636,7 +6658,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6646,16 +6668,16 @@
         <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6673,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6689,7 +6711,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6699,16 +6721,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6726,13 +6748,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6740,19 +6762,19 @@
       <c r="R94" s="5">
         <v>46275</v>
       </c>
-      <c r="S94" s="10" t="s">
-        <v>32</v>
+      <c r="S94" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>48</v>
+      <c r="U94" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6762,16 +6784,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6787,13 +6809,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6803,7 +6825,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -6813,16 +6835,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6838,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6854,7 +6876,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -6864,16 +6886,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -6891,13 +6913,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -6905,19 +6927,19 @@
       <c r="R97" s="8">
         <v>46276</v>
       </c>
-      <c r="S97" s="10" t="s">
-        <v>32</v>
+      <c r="S97" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
-      <c r="U97" s="12" t="s">
-        <v>48</v>
+      <c r="U97" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -6927,16 +6949,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -6952,13 +6974,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6968,7 +6990,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -6978,16 +7000,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7003,13 +7025,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7019,7 +7041,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7029,7 +7051,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7053,7 +7075,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7066,7 +7088,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7076,16 +7098,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7103,13 +7125,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7117,19 +7139,19 @@
       <c r="R101" s="8">
         <v>46287</v>
       </c>
-      <c r="S101" s="10" t="s">
-        <v>32</v>
+      <c r="S101" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
-      <c r="U101" s="12" t="s">
-        <v>48</v>
+      <c r="U101" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7139,7 +7161,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7166,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7180,14 +7202,14 @@
       <c r="R102" s="5">
         <v>46287</v>
       </c>
-      <c r="S102" s="10" t="s">
-        <v>32</v>
+      <c r="S102" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
-      <c r="U102" s="12" t="s">
-        <v>48</v>
+      <c r="U102" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1546,11 +1546,11 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.53486788194</v>
+        <v>46195.36820121528</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5">
-        <v>46195.54633383102</v>
+        <v>46195.37966716435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1593,11 +1593,11 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.53501399305</v>
+        <v>46195.36834732639</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46197.19303634259</v>
+        <v>46197.02636967592</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1654,11 +1654,11 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.53501732639</v>
+        <v>46195.36835065972</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46197.19303427084</v>
+        <v>46197.026367604165</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1715,11 +1715,11 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.53502171296</v>
+        <v>46195.368355046296</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46197.19303427084</v>
+        <v>46197.026367604165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1776,11 +1776,11 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.535025543984</v>
+        <v>46195.36835887731</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46197.193034375</v>
+        <v>46197.026367708335</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1837,11 +1837,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.534873819444</v>
+        <v>46195.36820715277</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46195.55209844907</v>
+        <v>46195.38543178241</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1884,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.53503290509</v>
+        <v>46195.36836623843</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.584062650465</v>
+        <v>46195.41739598379</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1947,11 +1947,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.535038055554</v>
+        <v>46195.36837138889</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46195.58406326389</v>
+        <v>46195.41739659722</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2010,11 +2010,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.53504337963</v>
+        <v>46195.36837671296</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46196.61063163195</v>
+        <v>46196.44396496528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2073,11 +2073,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.53487891203</v>
+        <v>46195.368212245376</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.499357939814</v>
+        <v>46197.33269127314</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2120,11 +2120,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.53505578704</v>
+        <v>46195.36838912037</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.17145724537</v>
+        <v>46196.00479057871</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2183,13 +2183,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.535061620365</v>
+        <v>46195.36839495371</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.49930170139</v>
+        <v>46197.33263503472</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.499318842594</v>
+        <v>46197.33265217593</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2248,13 +2248,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.53506689815</v>
+        <v>46195.368400231484</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.49934962963</v>
+        <v>46197.332682962966</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.49936423611</v>
+        <v>46197.33269756944</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2313,11 +2313,11 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.53507237269</v>
+        <v>46195.368405706016</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46195.58294910879</v>
+        <v>46195.41628244213</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2376,11 +2376,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.535077141205</v>
+        <v>46195.36841047453</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46195.582945671296</v>
+        <v>46195.416279004625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2439,11 +2439,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.53508107639</v>
+        <v>46195.36841440972</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.58294261574</v>
+        <v>46195.41627594907</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2502,11 +2502,11 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.535084918985</v>
+        <v>46195.368418252314</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46195.58293708334</v>
+        <v>46195.41627041667</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2565,13 +2565,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.55482737269</v>
+        <v>46195.38816070602</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.50025414352</v>
+        <v>46197.33358747685</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.500272743055</v>
+        <v>46197.33360607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2618,13 +2618,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.55503578704</v>
+        <v>46195.38836912037</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.49944752315</v>
+        <v>46197.33278085648</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.499464259265</v>
+        <v>46197.33279759259</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2683,13 +2683,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.5550796412</v>
+        <v>46195.38841297454</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.500224166666</v>
+        <v>46197.333557499995</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.500242662034</v>
+        <v>46197.33357599537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2748,13 +2748,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.555127037034</v>
+        <v>46195.38846037037</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.50023636574</v>
+        <v>46197.33356969907</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.50025311342</v>
+        <v>46197.33358644676</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2813,11 +2813,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.534883761575</v>
+        <v>46195.3682170949</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.56979528935</v>
+        <v>46195.40312862268</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2860,11 +2860,11 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.53514152778</v>
+        <v>46195.36847486111</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.583322719904</v>
+        <v>46195.41665605324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -2923,11 +2923,11 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.535146215276</v>
+        <v>46195.36847954861</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.583258530096</v>
+        <v>46195.416591863424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -2982,11 +2982,11 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.53519951389</v>
+        <v>46195.36853284722</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.58325561343</v>
+        <v>46195.416588946755</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3041,11 +3041,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.535206608794</v>
+        <v>46195.36853994213</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.58349109953</v>
+        <v>46195.416824432876</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3104,11 +3104,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.53521144676</v>
+        <v>46195.368544780096</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.58342974537</v>
+        <v>46195.416763078705</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>79</v>
@@ -3157,11 +3157,11 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.53521638889</v>
+        <v>46195.36854972222</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.583426701385</v>
+        <v>46195.41676003472</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3210,11 +3210,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.53522158565</v>
+        <v>46195.36855491898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.58374949074</v>
+        <v>46195.417082824075</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3273,11 +3273,11 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.53522605324</v>
+        <v>46195.368559386574</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.58357594907</v>
+        <v>46195.41690928241</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>85</v>
@@ -3326,11 +3326,11 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.5352309375</v>
+        <v>46195.36856427083</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.58357231482</v>
+        <v>46195.41690564815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3379,11 +3379,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.53523623843</v>
+        <v>46195.36856957176</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.58370322917</v>
+        <v>46195.4170365625</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3432,11 +3432,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.535239398145</v>
+        <v>46195.36857273148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.58395704861</v>
+        <v>46195.41729038194</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3495,11 +3495,11 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.53524336805</v>
+        <v>46195.36857670139</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.583877337966</v>
+        <v>46195.417210671294</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3548,11 +3548,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.53524819444</v>
+        <v>46195.36858152778</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.583909918976</v>
+        <v>46195.41724325232</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3601,11 +3601,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.5348887037</v>
+        <v>46195.36822203704</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.55821990741</v>
+        <v>46195.39155324074</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -3648,11 +3648,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.535254629634</v>
+        <v>46195.36858796296</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46195.58420387731</v>
+        <v>46195.41753721065</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -3711,11 +3711,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.53526092593</v>
+        <v>46195.36859425926</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.58420070602</v>
+        <v>46195.417534039356</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3774,11 +3774,11 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.53526833333</v>
+        <v>46195.36860166666</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46195.58419729167</v>
+        <v>46195.417530624996</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3837,11 +3837,11 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.53528606481</v>
+        <v>46195.36861939815</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46195.41768052083</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -3900,11 +3900,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.535290266205</v>
+        <v>46195.36862359954</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46195.41763832176</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -3951,11 +3951,11 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.53529509259</v>
+        <v>46195.36862842593</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46195.41763506945</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4002,11 +4002,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.53533827546</v>
+        <v>46195.3686716088</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.572334930555</v>
+        <v>46195.40566826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4049,11 +4049,11 @@
         <v>166</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.53534217592</v>
+        <v>46195.368675509264</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.58444471065</v>
+        <v>46195.41777804398</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4112,11 +4112,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.53534689815</v>
+        <v>46195.36868023148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46195.41788641203</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4175,11 +4175,11 @@
         <v>175</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.5353533912</v>
+        <v>46195.36868672454</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.584441377316</v>
+        <v>46195.417774710644</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>176</v>
@@ -4238,11 +4238,11 @@
         <v>178</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.53535798611</v>
+        <v>46195.36869131944</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46195.41788364583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>179</v>
@@ -4301,11 +4301,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.535361689814</v>
+        <v>46195.36869502315</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.584438252314</v>
+        <v>46195.41777158565</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -4364,11 +4364,11 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.53536568287</v>
+        <v>46195.3686990162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46195.41787967592</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -4427,11 +4427,11 @@
         <v>185</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.5353693287</v>
+        <v>46195.36870266203</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46195.40720042824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -4474,11 +4474,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.53537232639</v>
+        <v>46195.36870565973</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46195.41815065972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -4537,11 +4537,11 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.53537631944</v>
+        <v>46195.36870965278</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46195.41811395834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>160</v>
@@ -4590,11 +4590,11 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.53538179398</v>
+        <v>46195.36871512732</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46195.41811086806</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -4643,11 +4643,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.53540148148</v>
+        <v>46195.368734814816</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46195.418361759264</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -4706,11 +4706,11 @@
         <v>201</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.53540543982</v>
+        <v>46195.36873877315</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.58497643519</v>
+        <v>46195.418309768516</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>160</v>
@@ -4759,11 +4759,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.53541055556</v>
+        <v>46195.36874388889</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46195.58497305556</v>
+        <v>46195.41830638889</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>160</v>
@@ -4812,11 +4812,11 @@
         <v>207</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.535427650466</v>
+        <v>46195.368760983794</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46195.58515287037</v>
+        <v>46195.41848620371</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>208</v>
@@ -4875,11 +4875,11 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.53543222223</v>
+        <v>46195.368765555555</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46195.58511675926</v>
+        <v>46195.41845009259</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>160</v>
@@ -4928,11 +4928,11 @@
         <v>211</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.53543761574</v>
+        <v>46195.36877094908</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46195.58511351852</v>
+        <v>46195.41844685185</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>160</v>
@@ -4981,11 +4981,11 @@
         <v>213</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.53545577546</v>
+        <v>46195.3687891088</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.56789731482</v>
+        <v>46195.401230648145</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>164</v>
@@ -5028,11 +5028,11 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.535458576385</v>
+        <v>46195.36879190972</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.500242800925</v>
+        <v>46197.33357613426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5091,11 +5091,11 @@
         <v>218</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.535463912034</v>
+        <v>46195.36879724537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.50025571759</v>
+        <v>46197.333589050926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>219</v>
@@ -5154,11 +5154,11 @@
         <v>220</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.53547575232</v>
+        <v>46195.368809085645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.49946436343</v>
+        <v>46197.332797696756</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5217,11 +5217,11 @@
         <v>223</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.53552306713</v>
+        <v>46195.36885640046</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.58523106482</v>
+        <v>46195.41856439815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>224</v>
@@ -5280,11 +5280,11 @@
         <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.53552899306</v>
+        <v>46195.36886232639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.577845057865</v>
+        <v>46195.41117839121</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5327,11 +5327,11 @@
         <v>229</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.5355328588</v>
+        <v>46195.36886619213</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46195.418684421296</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>230</v>
@@ -5390,11 +5390,11 @@
         <v>232</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.53554157408</v>
+        <v>46195.368874907406</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46195.41864616898</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>160</v>
@@ -5443,11 +5443,11 @@
         <v>234</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.53554603009</v>
+        <v>46195.36887936342</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46195.418642916666</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>160</v>
@@ -5496,11 +5496,11 @@
         <v>235</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.535563240745</v>
+        <v>46195.36889657407</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46195.4188153588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>236</v>
@@ -5559,11 +5559,11 @@
         <v>237</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.53556773148</v>
+        <v>46195.368901064816</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.585438078706</v>
+        <v>46195.418771412034</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>160</v>
@@ -5612,11 +5612,11 @@
         <v>240</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.53557388889</v>
+        <v>46195.36890722222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.58543432871</v>
+        <v>46195.418767662035</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>160</v>
@@ -5665,11 +5665,11 @@
         <v>241</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.53559528935</v>
+        <v>46195.36892862269</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46195.41893768519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>242</v>
@@ -5726,11 +5726,11 @@
         <v>243</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.53559965278</v>
+        <v>46195.36893298611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46195.585553310186</v>
+        <v>46195.418886643514</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>160</v>
@@ -5777,11 +5777,11 @@
         <v>245</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.53560584491</v>
+        <v>46195.36893917824</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.58554990741</v>
+        <v>46195.41888324074</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>160</v>
@@ -5828,11 +5828,11 @@
         <v>246</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.53562898148</v>
+        <v>46195.36896231482</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46195.41904408565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>247</v>
@@ -5889,11 +5889,11 @@
         <v>248</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.535633541665</v>
+        <v>46195.368966875</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.58567954861</v>
+        <v>46195.41901288195</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>160</v>
@@ -5942,11 +5942,11 @@
         <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.535639050926</v>
+        <v>46195.368972384254</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.585675891205</v>
+        <v>46195.41900922454</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>160</v>
@@ -5995,11 +5995,11 @@
         <v>252</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.53570565972</v>
+        <v>46195.369038993056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46195.419168946755</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>253</v>
@@ -6056,11 +6056,11 @@
         <v>254</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.535710509255</v>
+        <v>46195.36904384259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46195.41912155093</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>160</v>
@@ -6109,11 +6109,11 @@
         <v>256</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.53571621528</v>
+        <v>46195.36904954861</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46195.4191184375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>160</v>
@@ -6162,11 +6162,11 @@
         <v>257</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.53573584491</v>
+        <v>46195.36906917824</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46195.41929259259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>258</v>
@@ -6225,11 +6225,11 @@
         <v>260</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.53574096065</v>
+        <v>46195.36907429398</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46195.41925020833</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>160</v>
@@ -6278,11 +6278,11 @@
         <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.53574520833</v>
+        <v>46195.36907854167</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46195.419247233796</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>160</v>
@@ -6331,11 +6331,11 @@
         <v>263</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.53576230324</v>
+        <v>46195.369095636575</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.58073400463</v>
+        <v>46195.41406733796</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>264</v>
@@ -6378,11 +6378,11 @@
         <v>266</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.535766319445</v>
+        <v>46195.36909965277</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46195.419515671296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>267</v>
@@ -6441,11 +6441,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.535772118055</v>
+        <v>46195.36910545139</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46195.41947037037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>160</v>
@@ -6492,11 +6492,11 @@
         <v>273</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.53577681713</v>
+        <v>46195.36911015047</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46195.419467141204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>160</v>
@@ -6545,11 +6545,11 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.535800763886</v>
+        <v>46195.36913409722</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46195.419691539355</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>275</v>
@@ -6608,11 +6608,11 @@
         <v>276</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.53580561343</v>
+        <v>46195.36913894676</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46195.41965655093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>160</v>
@@ -6661,11 +6661,11 @@
         <v>278</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.5358103125</v>
+        <v>46195.36914364583</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46195.419653414356</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>160</v>
@@ -6714,11 +6714,11 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.535868506944</v>
+        <v>46195.36920184028</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46195.4198324537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -6777,11 +6777,11 @@
         <v>281</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.535874293986</v>
+        <v>46195.369207627315</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46195.41979299768</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>160</v>
@@ -6828,11 +6828,11 @@
         <v>283</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.535884780096</v>
+        <v>46195.369218113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46195.41979018519</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>160</v>
@@ -6879,11 +6879,11 @@
         <v>285</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.53591063658</v>
+        <v>46195.36924396991</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46195.41997931713</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>286</v>
@@ -6942,11 +6942,11 @@
         <v>288</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.53591612268</v>
+        <v>46195.369249456024</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46195.41993966435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>160</v>
@@ -6993,11 +6993,11 @@
         <v>289</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.535920254624</v>
+        <v>46195.36925358797</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46195.419936412036</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>160</v>
@@ -7044,11 +7044,11 @@
         <v>290</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.53593680555</v>
+        <v>46195.36927013889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.58118991899</v>
+        <v>46195.414523252315</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>291</v>
@@ -7091,11 +7091,11 @@
         <v>293</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.535940173606</v>
+        <v>46195.36927350695</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46195.42016065972</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>294</v>
@@ -7154,11 +7154,11 @@
         <v>297</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.53594497685</v>
+        <v>46195.36927831019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46195.42010171297</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>298</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="301">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -463,25 +463,31 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259244</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215932734132723</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259244</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215932734132723</t>
   </si>
   <si>
     <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Propuesta Fabricación externa  OT 4363,propuesta Corte Laser OT 4363,Propuesta Corte plasma OT 4363,Propuesta Mecanizado OT 4363, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
@@ -1546,11 +1552,11 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.36820121528</v>
+        <v>46195.53486788194</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5">
-        <v>46195.37966716435</v>
+        <v>46195.54633383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1593,11 +1599,11 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.36834732639</v>
+        <v>46195.53501399305</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46197.02636967592</v>
+        <v>46197.19303634259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1654,11 +1660,11 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.36835065972</v>
+        <v>46195.53501732639</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46197.026367604165</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1715,11 +1721,11 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.368355046296</v>
+        <v>46195.53502171296</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46197.026367604165</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1776,11 +1782,11 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.36835887731</v>
+        <v>46195.535025543984</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46197.026367708335</v>
+        <v>46197.193034375</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1837,11 +1843,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.36820715277</v>
+        <v>46195.534873819444</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46195.38543178241</v>
+        <v>46195.55209844907</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1890,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.36836623843</v>
+        <v>46195.53503290509</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.41739598379</v>
+        <v>46195.584062650465</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1947,11 +1953,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.36837138889</v>
+        <v>46195.535038055554</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46195.41739659722</v>
+        <v>46195.58406326389</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2010,11 +2016,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.36837671296</v>
+        <v>46195.53504337963</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46196.44396496528</v>
+        <v>46196.61063163195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2073,11 +2079,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.368212245376</v>
+        <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.33269127314</v>
+        <v>46197.499357939814</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2120,11 +2126,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.36838912037</v>
+        <v>46195.53505578704</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.00479057871</v>
+        <v>46196.17145724537</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2183,13 +2189,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.36839495371</v>
+        <v>46195.535061620365</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.33263503472</v>
+        <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.33265217593</v>
+        <v>46197.499318842594</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2248,13 +2254,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.368400231484</v>
+        <v>46195.53506689815</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.332682962966</v>
+        <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.33269756944</v>
+        <v>46197.49936423611</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2313,11 +2319,11 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.368405706016</v>
+        <v>46195.53507237269</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46195.41628244213</v>
+        <v>46195.58294910879</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2376,11 +2382,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.36841047453</v>
+        <v>46195.535077141205</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46195.416279004625</v>
+        <v>46195.582945671296</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2439,11 +2445,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.36841440972</v>
+        <v>46195.53508107639</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.41627594907</v>
+        <v>46195.58294261574</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2502,11 +2508,11 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.368418252314</v>
+        <v>46195.535084918985</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46195.41627041667</v>
+        <v>46195.58293708334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2565,13 +2571,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.38816070602</v>
+        <v>46195.55482737269</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.33358747685</v>
+        <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.33360607639</v>
+        <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2618,13 +2624,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.38836912037</v>
+        <v>46195.55503578704</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.33278085648</v>
+        <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.33279759259</v>
+        <v>46197.499464259265</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2683,13 +2689,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.38841297454</v>
+        <v>46195.5550796412</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.333557499995</v>
+        <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.33357599537</v>
+        <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2748,13 +2754,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.38846037037</v>
+        <v>46195.555127037034</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.33356969907</v>
+        <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.33358644676</v>
+        <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2813,11 +2819,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.3682170949</v>
+        <v>46195.534883761575</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.40312862268</v>
+        <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2860,11 +2866,11 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.36847486111</v>
+        <v>46195.53514152778</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.41665605324</v>
+        <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -2923,11 +2929,11 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.36847954861</v>
+        <v>46195.535146215276</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.416591863424</v>
+        <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -2982,11 +2988,11 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.36853284722</v>
+        <v>46195.53519951389</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.416588946755</v>
+        <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3041,11 +3047,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.36853994213</v>
+        <v>46195.535206608794</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.416824432876</v>
+        <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3104,11 +3110,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.368544780096</v>
+        <v>46195.53521144676</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.416763078705</v>
+        <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>79</v>
@@ -3157,11 +3163,11 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.36854972222</v>
+        <v>46195.53521638889</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.41676003472</v>
+        <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3210,11 +3216,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.36855491898</v>
+        <v>46195.53522158565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.417082824075</v>
+        <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3273,11 +3279,11 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.368559386574</v>
+        <v>46195.53522605324</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.41690928241</v>
+        <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>85</v>
@@ -3326,11 +3332,11 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.36856427083</v>
+        <v>46195.5352309375</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.41690564815</v>
+        <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3379,11 +3385,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.36856957176</v>
+        <v>46195.53523623843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.4170365625</v>
+        <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3432,11 +3438,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.36857273148</v>
+        <v>46195.535239398145</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.41729038194</v>
+        <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3495,11 +3501,11 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.36857670139</v>
+        <v>46195.53524336805</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.417210671294</v>
+        <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3548,11 +3554,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.36858152778</v>
+        <v>46195.53524819444</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.41724325232</v>
+        <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3601,11 +3607,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.36822203704</v>
+        <v>46195.5348887037</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.39155324074</v>
+        <v>46195.55821990741</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -3648,11 +3654,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.36858796296</v>
+        <v>46195.535254629634</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46195.41753721065</v>
+        <v>46197.70735798611</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -3711,11 +3717,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.36859425926</v>
+        <v>46195.53526092593</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.417534039356</v>
+        <v>46197.7073890162</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3774,11 +3780,11 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.36860166666</v>
+        <v>46195.53526833333</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46195.417530624996</v>
+        <v>46195.58419729167</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3787,10 +3793,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3814,7 +3820,7 @@
         <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3834,26 +3840,26 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.36861939815</v>
+        <v>46195.53528606481</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.41768052083</v>
+        <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -3874,7 +3880,7 @@
         <v>142</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3897,26 +3903,26 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.36862359954</v>
+        <v>46195.535290266205</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.41763832176</v>
+        <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3932,13 +3938,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3948,26 +3954,26 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.36862842593</v>
+        <v>46195.53529509259</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.41763506945</v>
+        <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3983,13 +3989,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -3999,17 +4005,17 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.3686716088</v>
+        <v>46195.53533827546</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.40566826389</v>
+        <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4033,7 +4039,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4046,26 +4052,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.368675509264</v>
+        <v>46195.53534217592</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.41777804398</v>
+        <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4083,13 +4089,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4109,17 +4115,17 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.36868023148</v>
+        <v>46195.53534689815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.41788641203</v>
+        <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4146,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4172,26 +4178,26 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.36868672454</v>
+        <v>46195.5353533912</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.417774710644</v>
+        <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4209,13 +4215,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>117</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4235,17 +4241,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.36869131944</v>
+        <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.41788364583</v>
+        <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4272,13 +4278,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4298,26 +4304,26 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.36869502315</v>
+        <v>46195.535361689814</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.41777158565</v>
+        <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4335,13 +4341,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>139</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4361,17 +4367,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.3686990162</v>
+        <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.41787967592</v>
+        <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4398,13 +4404,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4424,17 +4430,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.36870266203</v>
+        <v>46195.5353693287</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.40720042824</v>
+        <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4458,7 +4464,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4471,26 +4477,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.36870565973</v>
+        <v>46195.53537232639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.41815065972</v>
+        <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4508,13 +4514,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4534,26 +4540,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.36870965278</v>
+        <v>46195.53537631944</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.41811395834</v>
+        <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4571,13 +4577,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4587,26 +4593,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.36871512732</v>
+        <v>46195.53538179398</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.41811086806</v>
+        <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4624,13 +4630,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4640,26 +4646,26 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.368734814816</v>
+        <v>46195.53540148148</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.418361759264</v>
+        <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4677,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4703,26 +4709,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.36873877315</v>
+        <v>46195.53540543982</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.418309768516</v>
+        <v>46195.58497643519</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4740,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4756,26 +4762,26 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.36874388889</v>
+        <v>46195.53541055556</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46195.41830638889</v>
+        <v>46195.58497305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4793,13 +4799,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4809,26 +4815,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.368760983794</v>
+        <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46195.41848620371</v>
+        <v>46195.58515287037</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4846,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -4872,26 +4878,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.368765555555</v>
+        <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46195.41845009259</v>
+        <v>46195.58511675926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -4909,13 +4915,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4925,26 +4931,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.36877094908</v>
+        <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46195.41844685185</v>
+        <v>46195.58511351852</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -4962,13 +4968,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4978,17 +4984,17 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.3687891088</v>
+        <v>46195.53545577546</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.401230648145</v>
+        <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5012,7 +5018,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5025,26 +5031,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.36879190972</v>
+        <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.33357613426</v>
+        <v>46197.500242800925</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5062,13 +5068,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5088,26 +5094,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.36879724537</v>
+        <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.333589050926</v>
+        <v>46197.50025571759</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5125,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5151,26 +5157,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.368809085645</v>
+        <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.332797696756</v>
+        <v>46197.49946436343</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5188,13 +5194,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5214,26 +5220,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.36885640046</v>
+        <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.41856439815</v>
+        <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5251,13 +5257,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>127</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5277,17 +5283,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.36886232639</v>
+        <v>46195.53552899306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.41117839121</v>
+        <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5311,7 +5317,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5324,17 +5330,17 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.36886619213</v>
+        <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.418684421296</v>
+        <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5361,13 +5367,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5387,17 +5393,17 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.368874907406</v>
+        <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.41864616898</v>
+        <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5424,10 +5430,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5440,17 +5446,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.36887936342</v>
+        <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.418642916666</v>
+        <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5477,10 +5483,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5493,17 +5499,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.36889657407</v>
+        <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.4188153588</v>
+        <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5530,13 +5536,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5556,17 +5562,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.368901064816</v>
+        <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.418771412034</v>
+        <v>46195.585438078706</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5593,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5609,17 +5615,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.36890722222</v>
+        <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.418767662035</v>
+        <v>46195.58543432871</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5646,13 +5652,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5662,17 +5668,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.36892862269</v>
+        <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.41893768519</v>
+        <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5697,13 +5703,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5723,17 +5729,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.36893298611</v>
+        <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46195.418886643514</v>
+        <v>46195.585553310186</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5758,13 +5764,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5774,17 +5780,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.36893917824</v>
+        <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.41888324074</v>
+        <v>46195.58554990741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5809,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O77" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="P77" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5825,17 +5831,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.36896231482</v>
+        <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.41904408565</v>
+        <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5860,13 +5866,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5886,17 +5892,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.368966875</v>
+        <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.41901288195</v>
+        <v>46195.58567954861</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -5923,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5939,17 +5945,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.368972384254</v>
+        <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.41900922454</v>
+        <v>46195.585675891205</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5976,13 +5982,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5992,17 +5998,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.369038993056</v>
+        <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.419168946755</v>
+        <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6027,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6053,17 +6059,17 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.36904384259</v>
+        <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.41912155093</v>
+        <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6090,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6106,17 +6112,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.36904954861</v>
+        <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.4191184375</v>
+        <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6143,13 +6149,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6159,17 +6165,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.36906917824</v>
+        <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.41929259259</v>
+        <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6196,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6222,17 +6228,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.36907429398</v>
+        <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.41925020833</v>
+        <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6259,13 +6265,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6275,17 +6281,17 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.36907854167</v>
+        <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.419247233796</v>
+        <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6312,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6328,17 +6334,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.369095636575</v>
+        <v>46195.53576230324</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.41406733796</v>
+        <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6362,7 +6368,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6375,26 +6381,26 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.36909965277</v>
+        <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.419515671296</v>
+        <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6412,13 +6418,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6438,26 +6444,26 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.36910545139</v>
+        <v>46195.535772118055</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.41947037037</v>
+        <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6473,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6489,26 +6495,26 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.36911015047</v>
+        <v>46195.53577681713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.419467141204</v>
+        <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6526,13 +6532,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6542,17 +6548,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.36913409722</v>
+        <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.419691539355</v>
+        <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6579,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6605,17 +6611,17 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.36913894676</v>
+        <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.41965655093</v>
+        <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6642,13 +6648,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6658,17 +6664,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.36914364583</v>
+        <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.419653414356</v>
+        <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6695,13 +6701,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6711,26 +6717,26 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.36920184028</v>
+        <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.4198324537</v>
+        <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6748,13 +6754,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6774,26 +6780,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.369207627315</v>
+        <v>46195.535874293986</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.41979299768</v>
+        <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6809,13 +6815,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6825,26 +6831,26 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.369218113425</v>
+        <v>46195.535884780096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.41979018519</v>
+        <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6860,13 +6866,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6876,26 +6882,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.36924396991</v>
+        <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.41997931713</v>
+        <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -6913,13 +6919,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -6939,26 +6945,26 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.369249456024</v>
+        <v>46195.53591612268</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.41993966435</v>
+        <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -6974,13 +6980,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6990,26 +6996,26 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.36925358797</v>
+        <v>46195.535920254624</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.419936412036</v>
+        <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7025,13 +7031,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7041,17 +7047,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.36927013889</v>
+        <v>46195.53593680555</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.414523252315</v>
+        <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7075,7 +7081,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7088,26 +7094,26 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.36927350695</v>
+        <v>46195.535940173606</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.42016065972</v>
+        <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7125,13 +7131,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7151,17 +7157,17 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.36927831019</v>
+        <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.42010171297</v>
+        <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7188,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1552,11 +1552,11 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.53486788194</v>
+        <v>46195.36820121528</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5">
-        <v>46195.54633383102</v>
+        <v>46195.37966716435</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1599,11 +1599,11 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.53501399305</v>
+        <v>46195.36834732639</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46197.19303634259</v>
+        <v>46197.02636967592</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1660,11 +1660,11 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.53501732639</v>
+        <v>46195.36835065972</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46197.19303427084</v>
+        <v>46197.026367604165</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1721,11 +1721,11 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.53502171296</v>
+        <v>46195.368355046296</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46197.19303427084</v>
+        <v>46197.026367604165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1782,11 +1782,11 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.535025543984</v>
+        <v>46195.36835887731</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46197.193034375</v>
+        <v>46197.026367708335</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1843,11 +1843,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.534873819444</v>
+        <v>46195.36820715277</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46195.55209844907</v>
+        <v>46195.38543178241</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1890,11 +1890,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.53503290509</v>
+        <v>46195.36836623843</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.584062650465</v>
+        <v>46195.41739598379</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1953,11 +1953,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.535038055554</v>
+        <v>46195.36837138889</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46195.58406326389</v>
+        <v>46195.41739659722</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2016,11 +2016,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.53504337963</v>
+        <v>46195.36837671296</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46196.61063163195</v>
+        <v>46196.44396496528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2079,11 +2079,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.53487891203</v>
+        <v>46195.368212245376</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.499357939814</v>
+        <v>46197.33269127314</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2126,11 +2126,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.53505578704</v>
+        <v>46195.36838912037</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.17145724537</v>
+        <v>46196.00479057871</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2189,13 +2189,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.535061620365</v>
+        <v>46195.36839495371</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.49930170139</v>
+        <v>46197.33263503472</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.499318842594</v>
+        <v>46197.33265217593</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2254,13 +2254,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.53506689815</v>
+        <v>46195.368400231484</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.49934962963</v>
+        <v>46197.332682962966</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.49936423611</v>
+        <v>46197.33269756944</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2319,11 +2319,11 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.53507237269</v>
+        <v>46195.368405706016</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46195.58294910879</v>
+        <v>46195.41628244213</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2382,11 +2382,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.535077141205</v>
+        <v>46195.36841047453</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46195.582945671296</v>
+        <v>46195.416279004625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2445,11 +2445,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.53508107639</v>
+        <v>46195.36841440972</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.58294261574</v>
+        <v>46195.41627594907</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2508,11 +2508,11 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.535084918985</v>
+        <v>46195.368418252314</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46195.58293708334</v>
+        <v>46195.41627041667</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2571,13 +2571,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.55482737269</v>
+        <v>46195.38816070602</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.50025414352</v>
+        <v>46197.33358747685</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.500272743055</v>
+        <v>46197.33360607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2624,13 +2624,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.55503578704</v>
+        <v>46195.38836912037</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.49944752315</v>
+        <v>46197.33278085648</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.499464259265</v>
+        <v>46197.33279759259</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2689,13 +2689,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.5550796412</v>
+        <v>46195.38841297454</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.500224166666</v>
+        <v>46197.333557499995</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.500242662034</v>
+        <v>46197.33357599537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2754,13 +2754,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.555127037034</v>
+        <v>46195.38846037037</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.50023636574</v>
+        <v>46197.33356969907</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.50025311342</v>
+        <v>46197.33358644676</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2819,11 +2819,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.534883761575</v>
+        <v>46195.3682170949</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.56979528935</v>
+        <v>46195.40312862268</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2866,11 +2866,11 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.53514152778</v>
+        <v>46195.36847486111</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.583322719904</v>
+        <v>46195.41665605324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -2929,11 +2929,11 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.535146215276</v>
+        <v>46195.36847954861</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.583258530096</v>
+        <v>46195.416591863424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -2988,11 +2988,11 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.53519951389</v>
+        <v>46195.36853284722</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.58325561343</v>
+        <v>46195.416588946755</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3047,11 +3047,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.535206608794</v>
+        <v>46195.36853994213</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.58349109953</v>
+        <v>46195.416824432876</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3110,11 +3110,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.53521144676</v>
+        <v>46195.368544780096</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.58342974537</v>
+        <v>46195.416763078705</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>79</v>
@@ -3163,11 +3163,11 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.53521638889</v>
+        <v>46195.36854972222</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.583426701385</v>
+        <v>46195.41676003472</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3216,11 +3216,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.53522158565</v>
+        <v>46195.36855491898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.58374949074</v>
+        <v>46195.417082824075</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3279,11 +3279,11 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.53522605324</v>
+        <v>46195.368559386574</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.58357594907</v>
+        <v>46195.41690928241</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>85</v>
@@ -3332,11 +3332,11 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.5352309375</v>
+        <v>46195.36856427083</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.58357231482</v>
+        <v>46195.41690564815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3385,11 +3385,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.53523623843</v>
+        <v>46195.36856957176</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.58370322917</v>
+        <v>46195.4170365625</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3438,11 +3438,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.535239398145</v>
+        <v>46195.36857273148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.58395704861</v>
+        <v>46195.41729038194</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3501,11 +3501,11 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.53524336805</v>
+        <v>46195.36857670139</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.583877337966</v>
+        <v>46195.417210671294</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3554,11 +3554,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.53524819444</v>
+        <v>46195.36858152778</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.583909918976</v>
+        <v>46195.41724325232</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3607,11 +3607,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.5348887037</v>
+        <v>46195.36822203704</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.55821990741</v>
+        <v>46195.39155324074</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -3654,11 +3654,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.535254629634</v>
+        <v>46195.36858796296</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.70735798611</v>
+        <v>46197.540691319446</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -3717,11 +3717,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.53526092593</v>
+        <v>46195.36859425926</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46197.7073890162</v>
+        <v>46197.54072234954</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3780,11 +3780,11 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.53526833333</v>
+        <v>46195.36860166666</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46195.58419729167</v>
+        <v>46195.417530624996</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3843,11 +3843,11 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.53528606481</v>
+        <v>46195.36861939815</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46195.41768052083</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3906,11 +3906,11 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.535290266205</v>
+        <v>46195.36862359954</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46195.41763832176</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -3957,11 +3957,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.53529509259</v>
+        <v>46195.36862842593</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46195.41763506945</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4008,11 +4008,11 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.53533827546</v>
+        <v>46195.3686716088</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.572334930555</v>
+        <v>46195.40566826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4055,11 +4055,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.53534217592</v>
+        <v>46195.368675509264</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.58444471065</v>
+        <v>46195.41777804398</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4118,11 +4118,11 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.53534689815</v>
+        <v>46195.36868023148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46195.41788641203</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4181,11 +4181,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.5353533912</v>
+        <v>46195.36868672454</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.584441377316</v>
+        <v>46195.417774710644</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4244,11 +4244,11 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.53535798611</v>
+        <v>46195.36869131944</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46195.41788364583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4307,11 +4307,11 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.535361689814</v>
+        <v>46195.36869502315</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.584438252314</v>
+        <v>46195.41777158565</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4370,11 +4370,11 @@
         <v>186</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.53536568287</v>
+        <v>46195.3686990162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46195.41787967592</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>185</v>
@@ -4433,11 +4433,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.5353693287</v>
+        <v>46195.36870266203</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46195.40720042824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>188</v>
@@ -4480,11 +4480,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.53537232639</v>
+        <v>46195.36870565973</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46195.41815065972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4543,11 +4543,11 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.53537631944</v>
+        <v>46195.36870965278</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46195.41811395834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>162</v>
@@ -4596,11 +4596,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.53538179398</v>
+        <v>46195.36871512732</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46195.41811086806</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4649,11 +4649,11 @@
         <v>201</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.53540148148</v>
+        <v>46195.368734814816</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46195.418361759264</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>202</v>
@@ -4712,11 +4712,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.53540543982</v>
+        <v>46195.36873877315</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.58497643519</v>
+        <v>46195.418309768516</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>162</v>
@@ -4765,11 +4765,11 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.53541055556</v>
+        <v>46195.36874388889</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46195.58497305556</v>
+        <v>46195.41830638889</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>162</v>
@@ -4818,11 +4818,11 @@
         <v>209</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.535427650466</v>
+        <v>46195.368760983794</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46195.58515287037</v>
+        <v>46195.41848620371</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>210</v>
@@ -4881,11 +4881,11 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.53543222223</v>
+        <v>46195.368765555555</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46195.58511675926</v>
+        <v>46195.41845009259</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>162</v>
@@ -4934,11 +4934,11 @@
         <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.53543761574</v>
+        <v>46195.36877094908</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46195.58511351852</v>
+        <v>46195.41844685185</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>162</v>
@@ -4987,11 +4987,11 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.53545577546</v>
+        <v>46195.3687891088</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.56789731482</v>
+        <v>46195.401230648145</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>166</v>
@@ -5034,11 +5034,11 @@
         <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.535458576385</v>
+        <v>46195.36879190972</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.500242800925</v>
+        <v>46197.33357613426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>218</v>
@@ -5097,11 +5097,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.535463912034</v>
+        <v>46195.36879724537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.50025571759</v>
+        <v>46197.333589050926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>221</v>
@@ -5160,11 +5160,11 @@
         <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.53547575232</v>
+        <v>46195.368809085645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.49946436343</v>
+        <v>46197.332797696756</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>223</v>
@@ -5223,11 +5223,11 @@
         <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.53552306713</v>
+        <v>46195.36885640046</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.58523106482</v>
+        <v>46195.41856439815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5286,11 +5286,11 @@
         <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.53552899306</v>
+        <v>46195.36886232639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.577845057865</v>
+        <v>46195.41117839121</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5333,11 +5333,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.5355328588</v>
+        <v>46195.36886619213</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46195.418684421296</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>232</v>
@@ -5396,11 +5396,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.53554157408</v>
+        <v>46195.368874907406</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46195.41864616898</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>162</v>
@@ -5449,11 +5449,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.53554603009</v>
+        <v>46195.36887936342</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46195.418642916666</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>162</v>
@@ -5502,11 +5502,11 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.535563240745</v>
+        <v>46195.36889657407</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46195.4188153588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
@@ -5565,11 +5565,11 @@
         <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.53556773148</v>
+        <v>46195.368901064816</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.585438078706</v>
+        <v>46195.418771412034</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>162</v>
@@ -5618,11 +5618,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.53557388889</v>
+        <v>46195.36890722222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.58543432871</v>
+        <v>46195.418767662035</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>162</v>
@@ -5671,11 +5671,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.53559528935</v>
+        <v>46195.36892862269</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46195.41893768519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>244</v>
@@ -5732,11 +5732,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.53559965278</v>
+        <v>46195.36893298611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46195.585553310186</v>
+        <v>46195.418886643514</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>162</v>
@@ -5783,11 +5783,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.53560584491</v>
+        <v>46195.36893917824</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.58554990741</v>
+        <v>46195.41888324074</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>162</v>
@@ -5834,11 +5834,11 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.53562898148</v>
+        <v>46195.36896231482</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46195.41904408565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>249</v>
@@ -5895,11 +5895,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.535633541665</v>
+        <v>46195.368966875</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.58567954861</v>
+        <v>46195.41901288195</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>162</v>
@@ -5948,11 +5948,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.535639050926</v>
+        <v>46195.368972384254</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.585675891205</v>
+        <v>46195.41900922454</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>162</v>
@@ -6001,11 +6001,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.53570565972</v>
+        <v>46195.369038993056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46195.419168946755</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6062,11 +6062,11 @@
         <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.535710509255</v>
+        <v>46195.36904384259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46195.41912155093</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>162</v>
@@ -6115,11 +6115,11 @@
         <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.53571621528</v>
+        <v>46195.36904954861</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46195.4191184375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>162</v>
@@ -6168,11 +6168,11 @@
         <v>259</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.53573584491</v>
+        <v>46195.36906917824</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46195.41929259259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>260</v>
@@ -6231,11 +6231,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.53574096065</v>
+        <v>46195.36907429398</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46195.41925020833</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>162</v>
@@ -6284,11 +6284,11 @@
         <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.53574520833</v>
+        <v>46195.36907854167</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46195.419247233796</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>162</v>
@@ -6337,11 +6337,11 @@
         <v>265</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.53576230324</v>
+        <v>46195.369095636575</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.58073400463</v>
+        <v>46195.41406733796</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>266</v>
@@ -6384,11 +6384,11 @@
         <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.535766319445</v>
+        <v>46195.36909965277</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46195.419515671296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>269</v>
@@ -6447,11 +6447,11 @@
         <v>273</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.535772118055</v>
+        <v>46195.36910545139</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46195.41947037037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>162</v>
@@ -6498,11 +6498,11 @@
         <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.53577681713</v>
+        <v>46195.36911015047</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46195.419467141204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>162</v>
@@ -6551,11 +6551,11 @@
         <v>276</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.535800763886</v>
+        <v>46195.36913409722</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46195.419691539355</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>277</v>
@@ -6614,11 +6614,11 @@
         <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.53580561343</v>
+        <v>46195.36913894676</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46195.41965655093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>162</v>
@@ -6667,11 +6667,11 @@
         <v>280</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.5358103125</v>
+        <v>46195.36914364583</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46195.419653414356</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>162</v>
@@ -6720,11 +6720,11 @@
         <v>281</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.535868506944</v>
+        <v>46195.36920184028</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46195.4198324537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>282</v>
@@ -6783,11 +6783,11 @@
         <v>283</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.535874293986</v>
+        <v>46195.369207627315</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46195.41979299768</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>162</v>
@@ -6834,11 +6834,11 @@
         <v>285</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.535884780096</v>
+        <v>46195.369218113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46195.41979018519</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>162</v>
@@ -6885,11 +6885,11 @@
         <v>287</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.53591063658</v>
+        <v>46195.36924396991</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46195.41997931713</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>288</v>
@@ -6948,11 +6948,11 @@
         <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.53591612268</v>
+        <v>46195.369249456024</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46195.41993966435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>162</v>
@@ -6999,11 +6999,11 @@
         <v>291</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.535920254624</v>
+        <v>46195.36925358797</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46195.419936412036</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>162</v>
@@ -7050,11 +7050,11 @@
         <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.53593680555</v>
+        <v>46195.36927013889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.58118991899</v>
+        <v>46195.414523252315</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>293</v>
@@ -7097,11 +7097,11 @@
         <v>295</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.535940173606</v>
+        <v>46195.36927350695</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46195.42016065972</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>296</v>
@@ -7160,11 +7160,11 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.53594497685</v>
+        <v>46195.36927831019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46195.42010171297</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>300</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1552,11 +1552,11 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.36820121528</v>
+        <v>46195.53486788194</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5">
-        <v>46195.37966716435</v>
+        <v>46195.54633383102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1599,11 +1599,11 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.36834732639</v>
+        <v>46195.53501399305</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8">
-        <v>46197.02636967592</v>
+        <v>46197.19303634259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1660,11 +1660,11 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.36835065972</v>
+        <v>46195.53501732639</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5">
-        <v>46197.026367604165</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1721,11 +1721,11 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.368355046296</v>
+        <v>46195.53502171296</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8">
-        <v>46197.026367604165</v>
+        <v>46197.19303427084</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1782,11 +1782,11 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.36835887731</v>
+        <v>46195.535025543984</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46197.026367708335</v>
+        <v>46197.193034375</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1843,11 +1843,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.36820715277</v>
+        <v>46195.534873819444</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46195.38543178241</v>
+        <v>46195.55209844907</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1890,11 +1890,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.36836623843</v>
+        <v>46195.53503290509</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.41739598379</v>
+        <v>46195.584062650465</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1953,11 +1953,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.36837138889</v>
+        <v>46195.535038055554</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46195.41739659722</v>
+        <v>46195.58406326389</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2016,11 +2016,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.36837671296</v>
+        <v>46195.53504337963</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46196.44396496528</v>
+        <v>46196.61063163195</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2079,11 +2079,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.368212245376</v>
+        <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.33269127314</v>
+        <v>46197.499357939814</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2126,11 +2126,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.36838912037</v>
+        <v>46195.53505578704</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.00479057871</v>
+        <v>46196.17145724537</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2189,13 +2189,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.36839495371</v>
+        <v>46195.535061620365</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.33263503472</v>
+        <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.33265217593</v>
+        <v>46197.499318842594</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2254,13 +2254,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.368400231484</v>
+        <v>46195.53506689815</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.332682962966</v>
+        <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.33269756944</v>
+        <v>46197.49936423611</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2319,11 +2319,11 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.368405706016</v>
+        <v>46195.53507237269</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46195.41628244213</v>
+        <v>46195.58294910879</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2382,11 +2382,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.36841047453</v>
+        <v>46195.535077141205</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46195.416279004625</v>
+        <v>46195.582945671296</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2445,11 +2445,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.36841440972</v>
+        <v>46195.53508107639</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.41627594907</v>
+        <v>46195.58294261574</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2508,11 +2508,11 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.368418252314</v>
+        <v>46195.535084918985</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46195.41627041667</v>
+        <v>46195.58293708334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2571,13 +2571,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.38816070602</v>
+        <v>46195.55482737269</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.33358747685</v>
+        <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.33360607639</v>
+        <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2624,13 +2624,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.38836912037</v>
+        <v>46195.55503578704</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.33278085648</v>
+        <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.33279759259</v>
+        <v>46197.499464259265</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2689,13 +2689,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.38841297454</v>
+        <v>46195.5550796412</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.333557499995</v>
+        <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.33357599537</v>
+        <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2754,13 +2754,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.38846037037</v>
+        <v>46195.555127037034</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.33356969907</v>
+        <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.33358644676</v>
+        <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2819,11 +2819,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.3682170949</v>
+        <v>46195.534883761575</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.40312862268</v>
+        <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2866,11 +2866,11 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.36847486111</v>
+        <v>46195.53514152778</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.41665605324</v>
+        <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -2929,11 +2929,11 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.36847954861</v>
+        <v>46195.535146215276</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.416591863424</v>
+        <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -2988,11 +2988,11 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.36853284722</v>
+        <v>46195.53519951389</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.416588946755</v>
+        <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3047,11 +3047,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.36853994213</v>
+        <v>46195.535206608794</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.416824432876</v>
+        <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3110,11 +3110,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.368544780096</v>
+        <v>46195.53521144676</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.416763078705</v>
+        <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>79</v>
@@ -3163,11 +3163,11 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.36854972222</v>
+        <v>46195.53521638889</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.41676003472</v>
+        <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3216,11 +3216,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.36855491898</v>
+        <v>46195.53522158565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.417082824075</v>
+        <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3279,11 +3279,11 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.368559386574</v>
+        <v>46195.53522605324</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.41690928241</v>
+        <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>85</v>
@@ -3332,11 +3332,11 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.36856427083</v>
+        <v>46195.5352309375</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.41690564815</v>
+        <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -3385,11 +3385,11 @@
         <v>129</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.36856957176</v>
+        <v>46195.53523623843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.4170365625</v>
+        <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>130</v>
@@ -3438,11 +3438,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.36857273148</v>
+        <v>46195.535239398145</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.41729038194</v>
+        <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3501,11 +3501,11 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.36857670139</v>
+        <v>46195.53524336805</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.417210671294</v>
+        <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3554,11 +3554,11 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.36858152778</v>
+        <v>46195.53524819444</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.41724325232</v>
+        <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -3607,11 +3607,11 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.36822203704</v>
+        <v>46195.5348887037</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.39155324074</v>
+        <v>46195.55821990741</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -3654,11 +3654,11 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.36858796296</v>
+        <v>46195.535254629634</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.540691319446</v>
+        <v>46197.70735798611</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>145</v>
@@ -3717,11 +3717,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.36859425926</v>
+        <v>46195.53526092593</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46197.54072234954</v>
+        <v>46197.7073890162</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -3780,11 +3780,11 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.36860166666</v>
+        <v>46195.53526833333</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46195.417530624996</v>
+        <v>46195.58419729167</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3843,11 +3843,11 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.36861939815</v>
+        <v>46195.53528606481</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.41768052083</v>
+        <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -3906,11 +3906,11 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.36862359954</v>
+        <v>46195.535290266205</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.41763832176</v>
+        <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -3957,11 +3957,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.36862842593</v>
+        <v>46195.53529509259</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.41763506945</v>
+        <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4008,11 +4008,11 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.3686716088</v>
+        <v>46195.53533827546</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.40566826389</v>
+        <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4055,11 +4055,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.368675509264</v>
+        <v>46195.53534217592</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.41777804398</v>
+        <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4118,11 +4118,11 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.36868023148</v>
+        <v>46195.53534689815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.41788641203</v>
+        <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4181,11 +4181,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.36868672454</v>
+        <v>46195.5353533912</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.417774710644</v>
+        <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4244,11 +4244,11 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.36869131944</v>
+        <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.41788364583</v>
+        <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4307,11 +4307,11 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.36869502315</v>
+        <v>46195.535361689814</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.41777158565</v>
+        <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4370,11 +4370,11 @@
         <v>186</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.3686990162</v>
+        <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.41787967592</v>
+        <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>185</v>
@@ -4433,11 +4433,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.36870266203</v>
+        <v>46195.5353693287</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.40720042824</v>
+        <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>188</v>
@@ -4480,11 +4480,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.36870565973</v>
+        <v>46195.53537232639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.41815065972</v>
+        <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4543,11 +4543,11 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.36870965278</v>
+        <v>46195.53537631944</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.41811395834</v>
+        <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>162</v>
@@ -4596,11 +4596,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.36871512732</v>
+        <v>46195.53538179398</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.41811086806</v>
+        <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4649,11 +4649,11 @@
         <v>201</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.368734814816</v>
+        <v>46195.53540148148</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.418361759264</v>
+        <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>202</v>
@@ -4712,11 +4712,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.36873877315</v>
+        <v>46195.53540543982</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.418309768516</v>
+        <v>46195.58497643519</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>162</v>
@@ -4765,11 +4765,11 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.36874388889</v>
+        <v>46195.53541055556</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46195.41830638889</v>
+        <v>46195.58497305556</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>162</v>
@@ -4818,11 +4818,11 @@
         <v>209</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.368760983794</v>
+        <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46195.41848620371</v>
+        <v>46195.58515287037</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>210</v>
@@ -4881,11 +4881,11 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.368765555555</v>
+        <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46195.41845009259</v>
+        <v>46195.58511675926</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>162</v>
@@ -4934,11 +4934,11 @@
         <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.36877094908</v>
+        <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46195.41844685185</v>
+        <v>46195.58511351852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>162</v>
@@ -4987,11 +4987,11 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.3687891088</v>
+        <v>46195.53545577546</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.401230648145</v>
+        <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>166</v>
@@ -5034,11 +5034,11 @@
         <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.36879190972</v>
+        <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.33357613426</v>
+        <v>46197.500242800925</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>218</v>
@@ -5097,11 +5097,11 @@
         <v>220</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.36879724537</v>
+        <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.333589050926</v>
+        <v>46197.50025571759</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>221</v>
@@ -5160,11 +5160,11 @@
         <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.368809085645</v>
+        <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.332797696756</v>
+        <v>46197.49946436343</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>223</v>
@@ -5223,11 +5223,11 @@
         <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.36885640046</v>
+        <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.41856439815</v>
+        <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5286,11 +5286,11 @@
         <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.36886232639</v>
+        <v>46195.53552899306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.41117839121</v>
+        <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5333,11 +5333,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.36886619213</v>
+        <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.418684421296</v>
+        <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>232</v>
@@ -5396,11 +5396,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.368874907406</v>
+        <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.41864616898</v>
+        <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>162</v>
@@ -5449,11 +5449,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.36887936342</v>
+        <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.418642916666</v>
+        <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>162</v>
@@ -5502,11 +5502,11 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.36889657407</v>
+        <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.4188153588</v>
+        <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
@@ -5565,11 +5565,11 @@
         <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.368901064816</v>
+        <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.418771412034</v>
+        <v>46195.585438078706</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>162</v>
@@ -5618,11 +5618,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.36890722222</v>
+        <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.418767662035</v>
+        <v>46195.58543432871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>162</v>
@@ -5671,11 +5671,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.36892862269</v>
+        <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.41893768519</v>
+        <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>244</v>
@@ -5732,11 +5732,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.36893298611</v>
+        <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46195.418886643514</v>
+        <v>46195.585553310186</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>162</v>
@@ -5783,11 +5783,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.36893917824</v>
+        <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.41888324074</v>
+        <v>46195.58554990741</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>162</v>
@@ -5834,11 +5834,11 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.36896231482</v>
+        <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.41904408565</v>
+        <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>249</v>
@@ -5895,11 +5895,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.368966875</v>
+        <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.41901288195</v>
+        <v>46195.58567954861</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>162</v>
@@ -5948,11 +5948,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.368972384254</v>
+        <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.41900922454</v>
+        <v>46195.585675891205</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>162</v>
@@ -6001,11 +6001,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.369038993056</v>
+        <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.419168946755</v>
+        <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6062,11 +6062,11 @@
         <v>256</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.36904384259</v>
+        <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.41912155093</v>
+        <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>162</v>
@@ -6115,11 +6115,11 @@
         <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.36904954861</v>
+        <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.4191184375</v>
+        <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>162</v>
@@ -6168,11 +6168,11 @@
         <v>259</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.36906917824</v>
+        <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.41929259259</v>
+        <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>260</v>
@@ -6231,11 +6231,11 @@
         <v>262</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.36907429398</v>
+        <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.41925020833</v>
+        <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>162</v>
@@ -6284,11 +6284,11 @@
         <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.36907854167</v>
+        <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.419247233796</v>
+        <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>162</v>
@@ -6337,11 +6337,11 @@
         <v>265</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.369095636575</v>
+        <v>46195.53576230324</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.41406733796</v>
+        <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>266</v>
@@ -6384,11 +6384,11 @@
         <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.36909965277</v>
+        <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.419515671296</v>
+        <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>269</v>
@@ -6447,11 +6447,11 @@
         <v>273</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.36910545139</v>
+        <v>46195.535772118055</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.41947037037</v>
+        <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>162</v>
@@ -6498,11 +6498,11 @@
         <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.36911015047</v>
+        <v>46195.53577681713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.419467141204</v>
+        <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>162</v>
@@ -6551,11 +6551,11 @@
         <v>276</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.36913409722</v>
+        <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.419691539355</v>
+        <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>277</v>
@@ -6614,11 +6614,11 @@
         <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.36913894676</v>
+        <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.41965655093</v>
+        <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>162</v>
@@ -6667,11 +6667,11 @@
         <v>280</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.36914364583</v>
+        <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.419653414356</v>
+        <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>162</v>
@@ -6720,11 +6720,11 @@
         <v>281</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.36920184028</v>
+        <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.4198324537</v>
+        <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>282</v>
@@ -6783,11 +6783,11 @@
         <v>283</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.369207627315</v>
+        <v>46195.535874293986</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.41979299768</v>
+        <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>162</v>
@@ -6834,11 +6834,11 @@
         <v>285</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.369218113425</v>
+        <v>46195.535884780096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.41979018519</v>
+        <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>162</v>
@@ -6885,11 +6885,11 @@
         <v>287</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.36924396991</v>
+        <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.41997931713</v>
+        <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>288</v>
@@ -6948,11 +6948,11 @@
         <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.369249456024</v>
+        <v>46195.53591612268</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.41993966435</v>
+        <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>162</v>
@@ -6999,11 +6999,11 @@
         <v>291</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.36925358797</v>
+        <v>46195.535920254624</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.419936412036</v>
+        <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>162</v>
@@ -7050,11 +7050,11 @@
         <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.36927013889</v>
+        <v>46195.53593680555</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.414523252315</v>
+        <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>293</v>
@@ -7097,11 +7097,11 @@
         <v>295</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.36927350695</v>
+        <v>46195.535940173606</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.42016065972</v>
+        <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>296</v>
@@ -7160,11 +7160,11 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.36927831019</v>
+        <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.42010171297</v>
+        <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>300</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -112,7 +112,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
+    <t>Tarea Terminada</t>
   </si>
   <si>
     <t>1215930353685932</t>
@@ -166,94 +166,134 @@
     <t>Ingenieria Basica Motor</t>
   </si>
   <si>
+    <t xml:space="preserve">    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+</t>
+  </si>
+  <si>
     <t>Ingenieria Jefe de proyecto:,propuesta motor - 4363</t>
   </si>
   <si>
     <t>Baja</t>
   </si>
   <si>
+    <t>1215923636075067</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>1215932733954927</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1566 se tienen 2 ventiladores ZVN 1-9-86/2 para Xemortiz (Minas de Oro Nacional):
+    Planos para fabricación O/4363:
+        Ventilador ZVN 1-9-86/2 con motor WEG
+        Alcance: Tobera + Rejilla + Tipo A 900mm
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+    Fecha de entrega: 04-08-2026
+    Términos contractuales / penalidades:
+        Terminación por causa, en caso de incumplimiento de las obligaciones contractuales.
+Indemnizaciones por retraso, equivalentes al 0.2% diario del valor de la Orden de Compra por atrasos en embarques o entrega de información, así como posibles penalizaciones asociadas al desempeño del suministro.</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1215922055649556</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4363,propuesta motor - 4363,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>1215930353744116</t>
+  </si>
+  <si>
+    <t>propuesta motor - 4363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1215923636093325</t>
+  </si>
+  <si>
+    <t>propuesta alabes - 4363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215932733979125</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1215932733979147</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215923636075067</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>1215932733954927</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1215922055649556</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4363,propuesta motor - 4363,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>1215930353744116</t>
-  </si>
-  <si>
-    <t>propuesta motor - 4363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1215923636093325</t>
-  </si>
-  <si>
-    <t>propuesta alabes - 4363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>Tarea Terminada</t>
-  </si>
-  <si>
-    <t>1215932733979125</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1215932733979147</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
     <t>1215922057135204</t>
@@ -994,12 +1034,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1554,9 +1594,11 @@
       <c r="B4" s="5">
         <v>46195.53486788194</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5">
+        <v>46197.84318319445</v>
+      </c>
       <c r="D4" s="5">
-        <v>46195.54633383102</v>
+        <v>46197.8432930787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1601,9 +1643,11 @@
       <c r="B5" s="8">
         <v>46195.53501399305</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="8">
+        <v>46197.8431590625</v>
+      </c>
       <c r="D5" s="8">
-        <v>46197.19303634259</v>
+        <v>46197.8431844213</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1649,7 +1693,7 @@
         <v>32</v>
       </c>
       <c r="T5" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="11" t="s">
         <v>33</v>
@@ -1662,9 +1706,11 @@
       <c r="B6" s="5">
         <v>46195.53501732639</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5">
+        <v>46197.84315976852</v>
+      </c>
       <c r="D6" s="5">
-        <v>46197.19303427084</v>
+        <v>46197.84318438657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1710,7 +1756,7 @@
         <v>32</v>
       </c>
       <c r="T6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="11" t="s">
         <v>33</v>
@@ -1723,9 +1769,11 @@
       <c r="B7" s="8">
         <v>46195.53502171296</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="8">
+        <v>46197.84316024306</v>
+      </c>
       <c r="D7" s="8">
-        <v>46197.19303427084</v>
+        <v>46197.84319010416</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1771,7 +1819,7 @@
         <v>32</v>
       </c>
       <c r="T7" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="11" t="s">
         <v>33</v>
@@ -1784,9 +1832,11 @@
       <c r="B8" s="5">
         <v>46195.535025543984</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46197.84316074074</v>
+      </c>
       <c r="D8" s="5">
-        <v>46197.193034375</v>
+        <v>46197.84318458333</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1832,7 +1882,7 @@
         <v>32</v>
       </c>
       <c r="T8" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="11" t="s">
         <v>33</v>
@@ -1845,9 +1895,11 @@
       <c r="B9" s="8">
         <v>46195.534873819444</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="8">
+        <v>46197.84431706018</v>
+      </c>
       <c r="D9" s="8">
-        <v>46195.55209844907</v>
+        <v>46197.84432748843</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1882,8 +1934,12 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
+      <c r="T9" s="9">
+        <v>1</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1892,9 +1948,11 @@
       <c r="B10" s="5">
         <v>46195.53503290509</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46197.84418690972</v>
+      </c>
       <c r="D10" s="5">
-        <v>46195.584062650465</v>
+        <v>46197.8442027662</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1918,7 +1976,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
@@ -1930,7 +1988,7 @@
         <v>39</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="5">
         <v>46197</v>
@@ -1938,14 +1996,14 @@
       <c r="R10" s="5">
         <v>46198</v>
       </c>
-      <c r="S10" s="12" t="s">
-        <v>48</v>
+      <c r="S10" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="10" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -1955,9 +2013,11 @@
       <c r="B11" s="8">
         <v>46195.535038055554</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="8">
+        <v>46197.84430075232</v>
+      </c>
       <c r="D11" s="8">
-        <v>46195.58406326389</v>
+        <v>46197.84431771991</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -1981,7 +2041,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
@@ -1993,7 +2053,7 @@
         <v>39</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="8">
         <v>46197</v>
@@ -2001,29 +2061,31 @@
       <c r="R11" s="8">
         <v>46198</v>
       </c>
-      <c r="S11" s="12" t="s">
-        <v>48</v>
+      <c r="S11" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46195.53504337963</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.843900266205</v>
+      </c>
       <c r="D12" s="5">
-        <v>46196.61063163195</v>
+        <v>46197.843917743055</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2044,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2056,7 +2118,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46197</v>
@@ -2064,29 +2126,29 @@
       <c r="R12" s="5">
         <v>46205</v>
       </c>
-      <c r="S12" s="12" t="s">
-        <v>48</v>
+      <c r="S12" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.499357939814</v>
+        <v>46197.84438787037</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2110,7 +2172,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2123,17 +2185,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46197.844381840274</v>
+      </c>
       <c r="D14" s="5">
-        <v>46196.17145724537</v>
+        <v>46197.844396712964</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2160,13 +2224,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2174,19 +2238,19 @@
       <c r="R14" s="5">
         <v>46203</v>
       </c>
-      <c r="S14" s="11" t="s">
-        <v>62</v>
+      <c r="S14" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="10" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
@@ -2195,10 +2259,10 @@
         <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.499318842594</v>
+        <v>46197.84431825232</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2225,13 +2289,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2239,19 +2303,19 @@
       <c r="R15" s="8">
         <v>46203</v>
       </c>
-      <c r="S15" s="11" t="s">
-        <v>62</v>
+      <c r="S15" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
@@ -2260,19 +2324,19 @@
         <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.49936423611</v>
+        <v>46197.84431829861</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2290,13 +2354,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2304,19 +2368,19 @@
       <c r="R16" s="5">
         <v>46203</v>
       </c>
-      <c r="S16" s="11" t="s">
-        <v>62</v>
+      <c r="S16" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2326,16 +2390,16 @@
         <v>46195.58294910879</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2353,13 +2417,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2367,19 +2431,19 @@
       <c r="R17" s="8">
         <v>46225</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>48</v>
+      <c r="S17" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T17" s="9">
         <v>0</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2389,16 +2453,16 @@
         <v>46195.582945671296</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2416,13 +2480,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2430,19 +2494,19 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>48</v>
+      <c r="S18" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2452,16 +2516,16 @@
         <v>46195.58294261574</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2479,13 +2543,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2493,19 +2557,19 @@
       <c r="R19" s="8">
         <v>46225</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>48</v>
+      <c r="S19" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T19" s="9">
         <v>0</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2515,16 +2579,16 @@
         <v>46195.58293708334</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2542,13 +2606,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2556,19 +2620,19 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>48</v>
+      <c r="S20" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2580,7 +2644,7 @@
         <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2604,7 +2668,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2615,13 +2679,13 @@
       <c r="T21" s="9">
         <v>1</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>66</v>
+      <c r="U21" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2630,19 +2694,19 @@
         <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.499464259265</v>
+        <v>46197.84440070602</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2660,13 +2724,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2674,19 +2738,19 @@
       <c r="R22" s="5">
         <v>46206</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>48</v>
+      <c r="S22" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2698,16 +2762,16 @@
         <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2725,13 +2789,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2739,19 +2803,19 @@
       <c r="R23" s="8">
         <v>46206</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>48</v>
+      <c r="S23" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>66</v>
+      <c r="U23" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2763,16 +2827,16 @@
         <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2790,13 +2854,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2804,19 +2868,19 @@
       <c r="R24" s="5">
         <v>46206</v>
       </c>
-      <c r="S24" s="12" t="s">
-        <v>48</v>
+      <c r="S24" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>66</v>
+      <c r="U24" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2826,7 +2890,7 @@
         <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2850,7 +2914,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2863,7 +2927,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2873,16 +2937,16 @@
         <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2900,13 +2964,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2914,19 +2978,19 @@
       <c r="R26" s="5">
         <v>46238</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>48</v>
+      <c r="S26" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -2936,16 +3000,16 @@
         <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -2963,29 +3027,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="12" t="s">
-        <v>48</v>
+      <c r="S27" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -2995,16 +3059,16 @@
         <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3022,29 +3086,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="12" t="s">
-        <v>48</v>
+      <c r="S28" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3054,16 +3118,16 @@
         <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3081,10 +3145,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3095,19 +3159,19 @@
       <c r="R29" s="8">
         <v>46238</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>48</v>
+      <c r="S29" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3117,16 +3181,16 @@
         <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3144,13 +3208,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3160,7 +3224,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3170,16 +3234,16 @@
         <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3197,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3213,7 +3277,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3223,16 +3287,16 @@
         <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3250,10 +3314,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3264,19 +3328,19 @@
       <c r="R32" s="5">
         <v>46266</v>
       </c>
-      <c r="S32" s="12" t="s">
-        <v>48</v>
+      <c r="S32" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3286,16 +3350,16 @@
         <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3313,13 +3377,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3329,7 +3393,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3339,16 +3403,16 @@
         <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3366,13 +3430,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3382,7 +3446,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3392,16 +3456,16 @@
         <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3419,10 +3483,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3435,7 +3499,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3445,16 +3509,16 @@
         <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3472,10 +3536,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3486,19 +3550,19 @@
       <c r="R36" s="5">
         <v>46238</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>48</v>
+      <c r="S36" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3508,16 +3572,16 @@
         <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3535,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3551,7 +3615,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3561,16 +3625,16 @@
         <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3588,13 +3652,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3604,7 +3668,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3614,7 +3678,7 @@
         <v>46195.55821990741</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3638,7 +3702,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3651,26 +3715,26 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.70735798611</v>
+        <v>46197.84391740741</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3688,13 +3752,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3702,19 +3766,19 @@
       <c r="R40" s="5">
         <v>46212</v>
       </c>
-      <c r="S40" s="12" t="s">
-        <v>48</v>
+      <c r="S40" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="10" t="s">
-        <v>49</v>
+      <c r="U40" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3724,16 +3788,16 @@
         <v>46197.7073890162</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3751,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3765,19 +3829,19 @@
       <c r="R41" s="8">
         <v>46190</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>48</v>
+      <c r="S41" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3787,16 +3851,16 @@
         <v>46195.58419729167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3814,13 +3878,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3828,19 +3892,19 @@
       <c r="R42" s="5">
         <v>46223</v>
       </c>
-      <c r="S42" s="12" t="s">
-        <v>48</v>
+      <c r="S42" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -3850,16 +3914,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -3877,10 +3941,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3891,19 +3955,19 @@
       <c r="R43" s="8">
         <v>46269</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>48</v>
+      <c r="S43" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -3913,16 +3977,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3938,13 +4002,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3954,7 +4018,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -3964,16 +4028,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3989,13 +4053,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4005,7 +4069,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4015,7 +4079,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4039,7 +4103,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4052,7 +4116,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4062,16 +4126,16 @@
         <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4089,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4103,19 +4167,19 @@
       <c r="R47" s="8">
         <v>46240</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>48</v>
+      <c r="S47" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4125,16 +4189,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4152,13 +4216,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4166,19 +4230,19 @@
       <c r="R48" s="5">
         <v>46244</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>48</v>
+      <c r="S48" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4188,16 +4252,16 @@
         <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4215,13 +4279,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4229,19 +4293,19 @@
       <c r="R49" s="8">
         <v>46240</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>48</v>
+      <c r="S49" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4251,16 +4315,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4278,13 +4342,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4292,19 +4356,19 @@
       <c r="R50" s="5">
         <v>46244</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>48</v>
+      <c r="S50" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4314,16 +4378,16 @@
         <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4341,13 +4405,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4355,19 +4419,19 @@
       <c r="R51" s="8">
         <v>46240</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>48</v>
+      <c r="S51" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4377,16 +4441,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4404,13 +4468,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4418,19 +4482,19 @@
       <c r="R52" s="5">
         <v>46244</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>48</v>
+      <c r="S52" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4440,7 +4504,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4464,7 +4528,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4477,7 +4541,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4487,16 +4551,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4514,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4528,19 +4592,19 @@
       <c r="R54" s="5">
         <v>46247</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>48</v>
+      <c r="S54" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4550,16 +4614,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4577,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4593,7 +4657,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4603,16 +4667,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4630,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4646,7 +4710,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4656,16 +4720,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4683,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4697,19 +4761,19 @@
       <c r="R57" s="8">
         <v>46254</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>48</v>
+      <c r="S57" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4719,16 +4783,16 @@
         <v>46195.58497643519</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4746,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4762,7 +4826,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4772,16 +4836,16 @@
         <v>46195.58497305556</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4799,13 +4863,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4815,26 +4879,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46195.58515287037</v>
+        <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4852,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -4866,38 +4930,38 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>48</v>
+      <c r="S60" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46195.58511675926</v>
+        <v>46197.842804050924</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -4915,13 +4979,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4931,26 +4995,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46195.58511351852</v>
+        <v>46197.84284413194</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -4968,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -4984,7 +5048,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -4994,7 +5058,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5018,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5031,7 +5095,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5041,16 +5105,16 @@
         <v>46197.500242800925</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5068,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5082,19 +5146,19 @@
       <c r="R64" s="5">
         <v>46209</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>48</v>
+      <c r="S64" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="11" t="s">
-        <v>33</v>
+      <c r="U64" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5104,16 +5168,16 @@
         <v>46197.50025571759</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5131,13 +5195,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5145,19 +5209,19 @@
       <c r="R65" s="8">
         <v>46209</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>48</v>
+      <c r="S65" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>33</v>
+      <c r="U65" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5167,16 +5231,16 @@
         <v>46197.49946436343</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5194,13 +5258,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5208,19 +5272,19 @@
       <c r="R66" s="5">
         <v>46209</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>48</v>
+      <c r="S66" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>33</v>
+      <c r="U66" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5230,16 +5294,16 @@
         <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5257,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5271,19 +5335,19 @@
       <c r="R67" s="8">
         <v>46266</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>48</v>
+      <c r="S67" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5293,7 +5357,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5317,7 +5381,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5330,7 +5394,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5340,16 +5404,16 @@
         <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5367,13 +5431,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5381,19 +5445,19 @@
       <c r="R69" s="8">
         <v>46262</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>48</v>
+      <c r="S69" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5403,16 +5467,16 @@
         <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5430,10 +5494,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5446,7 +5510,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5456,16 +5520,16 @@
         <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5483,10 +5547,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5499,7 +5563,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5509,16 +5573,16 @@
         <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5536,13 +5600,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5550,19 +5614,19 @@
       <c r="R72" s="5">
         <v>46265</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>48</v>
+      <c r="S72" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5572,16 +5636,16 @@
         <v>46195.585438078706</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5599,13 +5663,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5615,7 +5679,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5625,16 +5689,16 @@
         <v>46195.58543432871</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5652,13 +5716,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5668,7 +5732,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5678,16 +5742,16 @@
         <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5703,13 +5767,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5717,19 +5781,19 @@
       <c r="R75" s="8">
         <v>46266</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>48</v>
+      <c r="S75" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5739,16 +5803,16 @@
         <v>46195.585553310186</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5764,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5780,7 +5844,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5790,16 +5854,16 @@
         <v>46195.58554990741</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5815,13 +5879,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5831,7 +5895,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -5841,16 +5905,16 @@
         <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5866,13 +5930,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5880,19 +5944,19 @@
       <c r="R78" s="5">
         <v>46267</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>48</v>
+      <c r="S78" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -5902,16 +5966,16 @@
         <v>46195.58567954861</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -5929,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5945,7 +6009,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -5955,16 +6019,16 @@
         <v>46195.585675891205</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -5982,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5998,7 +6062,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6008,16 +6072,16 @@
         <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6033,13 +6097,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6047,19 +6111,19 @@
       <c r="R81" s="8">
         <v>46268</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>48</v>
+      <c r="S81" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6069,16 +6133,16 @@
         <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6096,13 +6160,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6112,7 +6176,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6122,16 +6186,16 @@
         <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6149,13 +6213,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6165,7 +6229,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6175,16 +6239,16 @@
         <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6202,13 +6266,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6216,19 +6280,19 @@
       <c r="R84" s="5">
         <v>46272</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>48</v>
+      <c r="S84" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6238,16 +6302,16 @@
         <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6265,13 +6329,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6281,7 +6345,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6291,16 +6355,16 @@
         <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6318,13 +6382,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6334,7 +6398,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6344,7 +6408,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6368,7 +6432,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6381,7 +6445,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6391,16 +6455,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6418,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6432,19 +6496,19 @@
       <c r="R88" s="5">
         <v>46273</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>48</v>
+      <c r="S88" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6454,16 +6518,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6479,13 +6543,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6495,7 +6559,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6505,16 +6569,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6532,13 +6596,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6548,7 +6612,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6558,16 +6622,16 @@
         <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6585,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6599,19 +6663,19 @@
       <c r="R91" s="8">
         <v>46274</v>
       </c>
-      <c r="S91" s="12" t="s">
-        <v>48</v>
+      <c r="S91" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6621,16 +6685,16 @@
         <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6648,13 +6712,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6664,7 +6728,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6674,16 +6738,16 @@
         <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6701,13 +6765,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6717,7 +6781,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6727,16 +6791,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6754,13 +6818,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6768,19 +6832,19 @@
       <c r="R94" s="5">
         <v>46275</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>48</v>
+      <c r="S94" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6790,16 +6854,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6815,13 +6879,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6831,7 +6895,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -6841,16 +6905,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6866,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6882,7 +6946,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -6892,16 +6956,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -6919,13 +6983,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -6933,19 +6997,19 @@
       <c r="R97" s="8">
         <v>46276</v>
       </c>
-      <c r="S97" s="12" t="s">
-        <v>48</v>
+      <c r="S97" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -6955,16 +7019,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -6980,13 +7044,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6996,7 +7060,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7006,16 +7070,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7031,13 +7095,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7047,7 +7111,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7057,7 +7121,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7081,7 +7145,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7094,7 +7158,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7104,16 +7168,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7131,13 +7195,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7145,19 +7209,19 @@
       <c r="R101" s="8">
         <v>46287</v>
       </c>
-      <c r="S101" s="12" t="s">
-        <v>48</v>
+      <c r="S101" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7167,7 +7231,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7194,13 +7258,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7208,14 +7272,14 @@
       <c r="R102" s="5">
         <v>46287</v>
       </c>
-      <c r="S102" s="12" t="s">
-        <v>48</v>
+      <c r="S102" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -230,6 +230,9 @@
     <t>Planos preliminar,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215922055649556</t>
   </si>
   <si>
@@ -248,9 +251,6 @@
     <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215923636093325</t>
   </si>
   <si>
@@ -293,91 +293,91 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
+    <t>1215922057135204</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057135216</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215930353764509</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363</t>
+  </si>
+  <si>
+    <t>1215927804444266</t>
+  </si>
+  <si>
+    <t>Reserva Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>1215927804444272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215927804444273</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363</t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215927804444274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215922055649558</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805761393</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215922057135204</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057135216</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215930353764509</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363</t>
-  </si>
-  <si>
-    <t>1215927804444266</t>
-  </si>
-  <si>
-    <t>Reserva Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>1215927804444272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215927804444273</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363</t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215927804444274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215922055649558</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805761393</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
     <t>1215927805772742</t>
@@ -2082,7 +2082,7 @@
         <v>46197.843900266205</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.843917743055</v>
+        <v>46198.173893935185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2126,8 +2126,8 @@
       <c r="R12" s="5">
         <v>46205</v>
       </c>
-      <c r="S12" s="11" t="s">
-        <v>49</v>
+      <c r="S12" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
@@ -2148,7 +2148,7 @@
         <v>46197.84438787037</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2172,7 +2172,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
@@ -2197,7 +2197,7 @@
         <v>46197.844396712964</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2224,13 +2224,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2239,7 +2239,7 @@
         <v>46203</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="T14" s="6">
         <v>1</v>
@@ -2289,7 +2289,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>51</v>
@@ -2304,7 +2304,7 @@
         <v>46203</v>
       </c>
       <c r="S15" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
@@ -2354,7 +2354,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>51</v>
@@ -2369,7 +2369,7 @@
         <v>46203</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46195.58294910879</v>
+        <v>46198.51059534722</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2417,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>77</v>
@@ -2437,23 +2437,23 @@
       <c r="T17" s="9">
         <v>0</v>
       </c>
-      <c r="U17" s="10" t="s">
-        <v>79</v>
+      <c r="U17" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46195.582945671296</v>
+        <v>46198.51059627315</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2480,13 +2480,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2500,23 +2500,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="10" t="s">
-        <v>79</v>
+      <c r="U18" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46195.58294261574</v>
+        <v>46198.51059506944</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2543,13 +2543,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2563,23 +2563,23 @@
       <c r="T19" s="9">
         <v>0</v>
       </c>
-      <c r="U19" s="10" t="s">
-        <v>79</v>
+      <c r="U19" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46195.58293708334</v>
+        <v>46198.51059547454</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2606,13 +2606,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2626,13 +2626,13 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="10" t="s">
-        <v>79</v>
+      <c r="U20" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2644,7 +2644,7 @@
         <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2668,7 +2668,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2697,7 +2697,7 @@
         <v>46197.84440070602</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2724,13 +2724,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2762,7 +2762,7 @@
         <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2789,13 +2789,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2827,7 +2827,7 @@
         <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2854,13 +2854,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2890,7 +2890,7 @@
         <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2914,7 +2914,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2937,16 +2937,16 @@
         <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2964,13 +2964,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3006,10 +3006,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3027,7 +3027,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>74</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3086,7 +3086,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>109</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3124,10 +3124,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3145,7 +3145,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>116</v>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3181,16 +3181,16 @@
         <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3211,7 +3211,7 @@
         <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>118</v>
@@ -3240,10 +3240,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3264,7 +3264,7 @@
         <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>121</v>
@@ -3314,7 +3314,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>126</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3350,7 +3350,7 @@
         <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3380,7 +3380,7 @@
         <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>128</v>
@@ -3433,7 +3433,7 @@
         <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>131</v>
@@ -3515,10 +3515,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3536,7 +3536,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>138</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3572,16 +3572,16 @@
         <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3602,7 +3602,7 @@
         <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>140</v>
@@ -3631,10 +3631,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3655,7 +3655,7 @@
         <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>143</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.55821990741</v>
+        <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3711,7 +3711,9 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
+      <c r="U39" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -3720,9 +3722,11 @@
       <c r="B40" s="5">
         <v>46195.535254629634</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46198.51038958333</v>
+      </c>
       <c r="D40" s="5">
-        <v>46197.84391740741</v>
+        <v>46198.51040733796</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3770,10 +3774,10 @@
         <v>49</v>
       </c>
       <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="12" t="s">
-        <v>68</v>
+        <v>1</v>
+      </c>
+      <c r="U40" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3783,9 +3787,11 @@
       <c r="B41" s="8">
         <v>46195.53526092593</v>
       </c>
-      <c r="C41" s="9"/>
+      <c r="C41" s="8">
+        <v>46198.51051443287</v>
+      </c>
       <c r="D41" s="8">
-        <v>46197.7073890162</v>
+        <v>46198.510531990745</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3833,10 +3839,10 @@
         <v>49</v>
       </c>
       <c r="T41" s="9">
-        <v>0</v>
-      </c>
-      <c r="U41" s="10" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U41" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3846,9 +3852,11 @@
       <c r="B42" s="5">
         <v>46195.53526833333</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46198.51056810185</v>
+      </c>
       <c r="D42" s="5">
-        <v>46195.58419729167</v>
+        <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>77</v>
@@ -3896,10 +3904,10 @@
         <v>49</v>
       </c>
       <c r="T42" s="6">
-        <v>0</v>
-      </c>
-      <c r="U42" s="10" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U42" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3962,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4174,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4237,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4300,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4363,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4426,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4489,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4599,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4768,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4780,7 +4788,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.58497643519</v>
+        <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4833,7 +4841,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46195.58497305556</v>
+        <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4937,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4949,7 +4957,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46197.842804050924</v>
+        <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5002,7 +5010,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46197.84284413194</v>
+        <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5135,7 +5143,7 @@
         <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>222</v>
@@ -5198,7 +5206,7 @@
         <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>222</v>
@@ -5261,7 +5269,7 @@
         <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>227</v>
@@ -5342,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5452,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5621,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5633,7 +5641,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.585438078706</v>
+        <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5686,7 +5694,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.58543432871</v>
+        <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5788,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46195.585553310186</v>
+        <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5851,7 +5859,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.58554990741</v>
+        <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5951,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -5963,7 +5971,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.58567954861</v>
+        <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6016,7 +6024,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46195.585675891205</v>
+        <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6118,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6287,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6503,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6670,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6839,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7004,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7216,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7279,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.53486788194</v>
+        <v>46195.36820121528</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.84318319445</v>
+        <v>46197.676516527776</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.8432930787</v>
+        <v>46197.67662641204</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.53501399305</v>
+        <v>46195.36834732639</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.8431590625</v>
+        <v>46197.67649239583</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.8431844213</v>
+        <v>46197.67651775463</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.53501732639</v>
+        <v>46195.36835065972</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.84315976852</v>
+        <v>46197.676493101855</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.84318438657</v>
+        <v>46197.67651771991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.53502171296</v>
+        <v>46195.368355046296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.84316024306</v>
+        <v>46197.67649357639</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.84319010416</v>
+        <v>46197.676523437505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.535025543984</v>
+        <v>46195.36835887731</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.84316074074</v>
+        <v>46197.676494074076</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.84318458333</v>
+        <v>46197.67651791667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.534873819444</v>
+        <v>46195.36820715277</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.84431706018</v>
+        <v>46197.67765039352</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.84432748843</v>
+        <v>46197.67766082176</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.53503290509</v>
+        <v>46195.36836623843</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.84418690972</v>
+        <v>46197.67752024306</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.8442027662</v>
+        <v>46197.67753609954</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.535038055554</v>
+        <v>46195.36837138889</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.84430075232</v>
+        <v>46197.677634085645</v>
       </c>
       <c r="D11" s="8">
-        <v>46197.84431771991</v>
+        <v>46197.677651053236</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2076,13 +2076,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.53504337963</v>
+        <v>46195.36837671296</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.843900266205</v>
+        <v>46197.677233599534</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.173893935185</v>
+        <v>46198.00722726852</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2141,11 +2141,11 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.53487891203</v>
+        <v>46195.368212245376</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.84438787037</v>
+        <v>46197.677721203705</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2188,13 +2188,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.53505578704</v>
+        <v>46195.36838912037</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.844381840274</v>
+        <v>46197.67771517361</v>
       </c>
       <c r="D14" s="5">
-        <v>46197.844396712964</v>
+        <v>46197.6777300463</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2253,13 +2253,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.535061620365</v>
+        <v>46195.36839495371</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.49930170139</v>
+        <v>46197.33263503472</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.84431825232</v>
+        <v>46197.67765158565</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2318,13 +2318,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.53506689815</v>
+        <v>46195.368400231484</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.49934962963</v>
+        <v>46197.332682962966</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.84431829861</v>
+        <v>46197.677651631944</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2383,11 +2383,11 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.53507237269</v>
+        <v>46195.368405706016</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46198.51059534722</v>
+        <v>46198.34392868055</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2446,11 +2446,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.535077141205</v>
+        <v>46195.36841047453</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.51059627315</v>
+        <v>46198.34392960648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2509,11 +2509,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.53508107639</v>
+        <v>46195.36841440972</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46198.51059506944</v>
+        <v>46198.34392840278</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2572,11 +2572,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.535084918985</v>
+        <v>46195.368418252314</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.51059547454</v>
+        <v>46198.343928807866</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2635,13 +2635,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.55482737269</v>
+        <v>46195.38816070602</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.50025414352</v>
+        <v>46197.33358747685</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.500272743055</v>
+        <v>46197.33360607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.55503578704</v>
+        <v>46195.38836912037</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.49944752315</v>
+        <v>46197.33278085648</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.84440070602</v>
+        <v>46197.67773403935</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2753,13 +2753,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.5550796412</v>
+        <v>46195.38841297454</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.500224166666</v>
+        <v>46197.333557499995</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.500242662034</v>
+        <v>46197.33357599537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -2818,13 +2818,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.555127037034</v>
+        <v>46195.38846037037</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.50023636574</v>
+        <v>46197.33356969907</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.50025311342</v>
+        <v>46197.33358644676</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2883,11 +2883,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.534883761575</v>
+        <v>46195.3682170949</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.56979528935</v>
+        <v>46195.40312862268</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2930,11 +2930,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.53514152778</v>
+        <v>46195.36847486111</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.583322719904</v>
+        <v>46195.41665605324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2993,11 +2993,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.535146215276</v>
+        <v>46195.36847954861</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.583258530096</v>
+        <v>46195.416591863424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3052,11 +3052,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.53519951389</v>
+        <v>46195.36853284722</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.58325561343</v>
+        <v>46195.416588946755</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3111,11 +3111,11 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.535206608794</v>
+        <v>46195.36853994213</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.58349109953</v>
+        <v>46195.416824432876</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3174,11 +3174,11 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.53521144676</v>
+        <v>46195.368544780096</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.58342974537</v>
+        <v>46195.416763078705</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>81</v>
@@ -3227,11 +3227,11 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.53521638889</v>
+        <v>46195.36854972222</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.583426701385</v>
+        <v>46195.41676003472</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3280,11 +3280,11 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.53522158565</v>
+        <v>46195.36855491898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.58374949074</v>
+        <v>46195.417082824075</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3343,11 +3343,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.53522605324</v>
+        <v>46195.368559386574</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.58357594907</v>
+        <v>46195.41690928241</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>87</v>
@@ -3396,11 +3396,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.5352309375</v>
+        <v>46195.36856427083</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.58357231482</v>
+        <v>46195.41690564815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3449,11 +3449,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.53523623843</v>
+        <v>46195.36856957176</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.58370322917</v>
+        <v>46195.4170365625</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3502,11 +3502,11 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.535239398145</v>
+        <v>46195.36857273148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.58395704861</v>
+        <v>46195.41729038194</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3565,11 +3565,11 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.53524336805</v>
+        <v>46195.36857670139</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.583877337966</v>
+        <v>46195.417210671294</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>84</v>
@@ -3618,11 +3618,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.53524819444</v>
+        <v>46195.36858152778</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.583909918976</v>
+        <v>46195.41724325232</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3671,11 +3671,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.5348887037</v>
+        <v>46195.36822203704</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.51053421297</v>
+        <v>46198.3438675463</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3720,13 +3720,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.535254629634</v>
+        <v>46195.36858796296</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.51038958333</v>
+        <v>46198.34372291667</v>
       </c>
       <c r="D40" s="5">
-        <v>46198.51040733796</v>
+        <v>46198.34374067129</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3785,13 +3785,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.53526092593</v>
+        <v>46195.36859425926</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.51051443287</v>
+        <v>46198.3438477662</v>
       </c>
       <c r="D41" s="8">
-        <v>46198.510531990745</v>
+        <v>46198.343865324074</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3850,13 +3850,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.53526833333</v>
+        <v>46195.36860166666</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.51056810185</v>
+        <v>46198.34390143519</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.51058418982</v>
+        <v>46198.34391752315</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>77</v>
@@ -3915,11 +3915,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.53528606481</v>
+        <v>46195.36861939815</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46195.41768052083</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3978,11 +3978,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.535290266205</v>
+        <v>46195.36862359954</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46195.41763832176</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4029,11 +4029,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.53529509259</v>
+        <v>46195.36862842593</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46195.41763506945</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4080,11 +4080,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.53533827546</v>
+        <v>46195.3686716088</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.572334930555</v>
+        <v>46195.40566826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4127,11 +4127,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.53534217592</v>
+        <v>46195.368675509264</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.58444471065</v>
+        <v>46195.41777804398</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4190,11 +4190,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.53534689815</v>
+        <v>46195.36868023148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46195.41788641203</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4253,11 +4253,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.5353533912</v>
+        <v>46195.36868672454</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.584441377316</v>
+        <v>46195.417774710644</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4316,11 +4316,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.53535798611</v>
+        <v>46195.36869131944</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46195.41788364583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4379,11 +4379,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.535361689814</v>
+        <v>46195.36869502315</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.584438252314</v>
+        <v>46195.41777158565</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4442,11 +4442,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.53536568287</v>
+        <v>46195.3686990162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46195.41787967592</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4505,11 +4505,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.5353693287</v>
+        <v>46195.36870266203</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46195.40720042824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4552,11 +4552,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.53537232639</v>
+        <v>46195.36870565973</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46195.41815065972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4615,11 +4615,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.53537631944</v>
+        <v>46195.36870965278</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46195.41811395834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4668,11 +4668,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.53538179398</v>
+        <v>46195.36871512732</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46195.41811086806</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.53540148148</v>
+        <v>46195.368734814816</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46195.418361759264</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4784,11 +4784,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.53540543982</v>
+        <v>46195.36873877315</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.51058690972</v>
+        <v>46198.34392024306</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4837,11 +4837,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.53541055556</v>
+        <v>46195.36874388889</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.510575162036</v>
+        <v>46198.34390849537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4890,11 +4890,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.535427650466</v>
+        <v>46195.368760983794</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.84290087963</v>
+        <v>46197.676234212966</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4953,11 +4953,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.53543222223</v>
+        <v>46195.368765555555</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.5105765162</v>
+        <v>46198.34390984954</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5006,11 +5006,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.53543761574</v>
+        <v>46195.36877094908</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.51057732639</v>
+        <v>46198.34391065972</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5059,11 +5059,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.53545577546</v>
+        <v>46195.3687891088</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.56789731482</v>
+        <v>46195.401230648145</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5106,11 +5106,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.535458576385</v>
+        <v>46195.36879190972</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.500242800925</v>
+        <v>46197.33357613426</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5169,11 +5169,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.535463912034</v>
+        <v>46195.36879724537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.50025571759</v>
+        <v>46197.333589050926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5232,11 +5232,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.53547575232</v>
+        <v>46195.368809085645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.49946436343</v>
+        <v>46197.332797696756</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5295,11 +5295,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.53552306713</v>
+        <v>46195.36885640046</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.58523106482</v>
+        <v>46195.41856439815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5358,11 +5358,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.53552899306</v>
+        <v>46195.36886232639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.577845057865</v>
+        <v>46195.41117839121</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5405,11 +5405,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.5355328588</v>
+        <v>46195.36886619213</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46195.418684421296</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5468,11 +5468,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.53554157408</v>
+        <v>46195.368874907406</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46195.41864616898</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5521,11 +5521,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.53554603009</v>
+        <v>46195.36887936342</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46195.418642916666</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5574,11 +5574,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.535563240745</v>
+        <v>46195.36889657407</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46195.4188153588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5637,11 +5637,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.53556773148</v>
+        <v>46195.368901064816</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.51057400463</v>
+        <v>46198.34390733796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5690,11 +5690,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.53557388889</v>
+        <v>46195.36890722222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.5105778125</v>
+        <v>46198.34391114583</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5743,11 +5743,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.53559528935</v>
+        <v>46195.36892862269</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46195.41893768519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5804,11 +5804,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.53559965278</v>
+        <v>46195.36893298611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.510575740744</v>
+        <v>46198.34390907407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5855,11 +5855,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.53560584491</v>
+        <v>46195.36893917824</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.510587488425</v>
+        <v>46198.34392082176</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5906,11 +5906,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.53562898148</v>
+        <v>46195.36896231482</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46195.41904408565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -5967,11 +5967,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.535633541665</v>
+        <v>46195.368966875</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.51057450232</v>
+        <v>46198.343907835646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6020,11 +6020,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.535639050926</v>
+        <v>46195.368972384254</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51057611111</v>
+        <v>46198.34390944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6073,11 +6073,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.53570565972</v>
+        <v>46195.369038993056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46195.419168946755</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6134,11 +6134,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.535710509255</v>
+        <v>46195.36904384259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46195.41912155093</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6187,11 +6187,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.53571621528</v>
+        <v>46195.36904954861</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46195.4191184375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.53573584491</v>
+        <v>46195.36906917824</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46195.41929259259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6303,11 +6303,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.53574096065</v>
+        <v>46195.36907429398</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46195.41925020833</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6356,11 +6356,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.53574520833</v>
+        <v>46195.36907854167</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46195.419247233796</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6409,11 +6409,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.53576230324</v>
+        <v>46195.369095636575</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.58073400463</v>
+        <v>46195.41406733796</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6456,11 +6456,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.535766319445</v>
+        <v>46195.36909965277</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46195.419515671296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6519,11 +6519,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.535772118055</v>
+        <v>46195.36910545139</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46195.41947037037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6570,11 +6570,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.53577681713</v>
+        <v>46195.36911015047</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46195.419467141204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6623,11 +6623,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.535800763886</v>
+        <v>46195.36913409722</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46195.419691539355</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6686,11 +6686,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.53580561343</v>
+        <v>46195.36913894676</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46195.41965655093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6739,11 +6739,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.5358103125</v>
+        <v>46195.36914364583</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46195.419653414356</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6792,11 +6792,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.535868506944</v>
+        <v>46195.36920184028</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46195.4198324537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6855,11 +6855,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.535874293986</v>
+        <v>46195.369207627315</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46195.41979299768</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6906,11 +6906,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.535884780096</v>
+        <v>46195.369218113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46195.41979018519</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6957,11 +6957,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.53591063658</v>
+        <v>46195.36924396991</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46195.41997931713</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7020,11 +7020,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.53591612268</v>
+        <v>46195.369249456024</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46195.41993966435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7071,11 +7071,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.535920254624</v>
+        <v>46195.36925358797</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46195.419936412036</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7122,11 +7122,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.53593680555</v>
+        <v>46195.36927013889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.58118991899</v>
+        <v>46195.414523252315</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7169,11 +7169,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.535940173606</v>
+        <v>46195.36927350695</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46195.42016065972</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7232,11 +7232,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.53594497685</v>
+        <v>46195.36927831019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46195.42010171297</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.36820121528</v>
+        <v>46195.53486788194</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.676516527776</v>
+        <v>46197.84318319445</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.67662641204</v>
+        <v>46197.8432930787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.36834732639</v>
+        <v>46195.53501399305</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.67649239583</v>
+        <v>46197.8431590625</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.67651775463</v>
+        <v>46197.8431844213</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.36835065972</v>
+        <v>46195.53501732639</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.676493101855</v>
+        <v>46197.84315976852</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.67651771991</v>
+        <v>46197.84318438657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.368355046296</v>
+        <v>46195.53502171296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.67649357639</v>
+        <v>46197.84316024306</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.676523437505</v>
+        <v>46197.84319010416</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.36835887731</v>
+        <v>46195.535025543984</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.676494074076</v>
+        <v>46197.84316074074</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.67651791667</v>
+        <v>46197.84318458333</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.36820715277</v>
+        <v>46195.534873819444</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.67765039352</v>
+        <v>46197.84431706018</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.67766082176</v>
+        <v>46197.84432748843</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.36836623843</v>
+        <v>46195.53503290509</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.67752024306</v>
+        <v>46197.84418690972</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.67753609954</v>
+        <v>46197.8442027662</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.36837138889</v>
+        <v>46195.535038055554</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.677634085645</v>
+        <v>46197.84430075232</v>
       </c>
       <c r="D11" s="8">
-        <v>46197.677651053236</v>
+        <v>46197.84431771991</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2076,13 +2076,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.36837671296</v>
+        <v>46195.53504337963</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.677233599534</v>
+        <v>46197.843900266205</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.00722726852</v>
+        <v>46198.173893935185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2141,11 +2141,11 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.368212245376</v>
+        <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.677721203705</v>
+        <v>46197.84438787037</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2188,13 +2188,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.36838912037</v>
+        <v>46195.53505578704</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.67771517361</v>
+        <v>46197.844381840274</v>
       </c>
       <c r="D14" s="5">
-        <v>46197.6777300463</v>
+        <v>46197.844396712964</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2253,13 +2253,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.36839495371</v>
+        <v>46195.535061620365</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.33263503472</v>
+        <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.67765158565</v>
+        <v>46197.84431825232</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2318,13 +2318,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.368400231484</v>
+        <v>46195.53506689815</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.332682962966</v>
+        <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.677651631944</v>
+        <v>46197.84431829861</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2383,11 +2383,11 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.368405706016</v>
+        <v>46195.53507237269</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46198.34392868055</v>
+        <v>46198.51059534722</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2446,11 +2446,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.36841047453</v>
+        <v>46195.535077141205</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.34392960648</v>
+        <v>46198.51059627315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2509,11 +2509,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.36841440972</v>
+        <v>46195.53508107639</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46198.34392840278</v>
+        <v>46198.51059506944</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2572,11 +2572,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.368418252314</v>
+        <v>46195.535084918985</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.343928807866</v>
+        <v>46198.51059547454</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2635,13 +2635,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.38816070602</v>
+        <v>46195.55482737269</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.33358747685</v>
+        <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.33360607639</v>
+        <v>46197.500272743055</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.38836912037</v>
+        <v>46195.55503578704</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.33278085648</v>
+        <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.67773403935</v>
+        <v>46197.84440070602</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2753,13 +2753,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.38841297454</v>
+        <v>46195.5550796412</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.333557499995</v>
+        <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.33357599537</v>
+        <v>46197.500242662034</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -2818,13 +2818,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.38846037037</v>
+        <v>46195.555127037034</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.33356969907</v>
+        <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.33358644676</v>
+        <v>46197.50025311342</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2883,11 +2883,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.3682170949</v>
+        <v>46195.534883761575</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.40312862268</v>
+        <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2930,11 +2930,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.36847486111</v>
+        <v>46195.53514152778</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.41665605324</v>
+        <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2993,11 +2993,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.36847954861</v>
+        <v>46195.535146215276</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.416591863424</v>
+        <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3052,11 +3052,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.36853284722</v>
+        <v>46195.53519951389</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.416588946755</v>
+        <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3111,11 +3111,11 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.36853994213</v>
+        <v>46195.535206608794</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.416824432876</v>
+        <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3174,11 +3174,11 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.368544780096</v>
+        <v>46195.53521144676</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.416763078705</v>
+        <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>81</v>
@@ -3227,11 +3227,11 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.36854972222</v>
+        <v>46195.53521638889</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.41676003472</v>
+        <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3280,11 +3280,11 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.36855491898</v>
+        <v>46195.53522158565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.417082824075</v>
+        <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3343,11 +3343,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.368559386574</v>
+        <v>46195.53522605324</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.41690928241</v>
+        <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>87</v>
@@ -3396,11 +3396,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.36856427083</v>
+        <v>46195.5352309375</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.41690564815</v>
+        <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3449,11 +3449,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.36856957176</v>
+        <v>46195.53523623843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.4170365625</v>
+        <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3502,11 +3502,11 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.36857273148</v>
+        <v>46195.535239398145</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.41729038194</v>
+        <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3565,11 +3565,11 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.36857670139</v>
+        <v>46195.53524336805</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.417210671294</v>
+        <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>84</v>
@@ -3618,11 +3618,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.36858152778</v>
+        <v>46195.53524819444</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.41724325232</v>
+        <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3671,11 +3671,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.36822203704</v>
+        <v>46195.5348887037</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.3438675463</v>
+        <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3720,13 +3720,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.36858796296</v>
+        <v>46195.535254629634</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.34372291667</v>
+        <v>46198.51038958333</v>
       </c>
       <c r="D40" s="5">
-        <v>46198.34374067129</v>
+        <v>46198.51040733796</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3785,13 +3785,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.36859425926</v>
+        <v>46195.53526092593</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.3438477662</v>
+        <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46198.343865324074</v>
+        <v>46198.510531990745</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3850,13 +3850,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.36860166666</v>
+        <v>46195.53526833333</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.34390143519</v>
+        <v>46198.51056810185</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.34391752315</v>
+        <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>77</v>
@@ -3915,11 +3915,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.36861939815</v>
+        <v>46195.53528606481</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.41768052083</v>
+        <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3978,11 +3978,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.36862359954</v>
+        <v>46195.535290266205</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.41763832176</v>
+        <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4029,11 +4029,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.36862842593</v>
+        <v>46195.53529509259</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.41763506945</v>
+        <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4080,11 +4080,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.3686716088</v>
+        <v>46195.53533827546</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.40566826389</v>
+        <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4127,11 +4127,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.368675509264</v>
+        <v>46195.53534217592</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.41777804398</v>
+        <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4190,11 +4190,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.36868023148</v>
+        <v>46195.53534689815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.41788641203</v>
+        <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4253,11 +4253,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.36868672454</v>
+        <v>46195.5353533912</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.417774710644</v>
+        <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4316,11 +4316,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.36869131944</v>
+        <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.41788364583</v>
+        <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4379,11 +4379,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.36869502315</v>
+        <v>46195.535361689814</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.41777158565</v>
+        <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4442,11 +4442,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.3686990162</v>
+        <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.41787967592</v>
+        <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4505,11 +4505,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.36870266203</v>
+        <v>46195.5353693287</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.40720042824</v>
+        <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4552,11 +4552,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.36870565973</v>
+        <v>46195.53537232639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.41815065972</v>
+        <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4615,11 +4615,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.36870965278</v>
+        <v>46195.53537631944</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.41811395834</v>
+        <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4668,11 +4668,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.36871512732</v>
+        <v>46195.53538179398</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.41811086806</v>
+        <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.368734814816</v>
+        <v>46195.53540148148</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.418361759264</v>
+        <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4784,11 +4784,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.36873877315</v>
+        <v>46195.53540543982</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.34392024306</v>
+        <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4837,11 +4837,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.36874388889</v>
+        <v>46195.53541055556</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.34390849537</v>
+        <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4890,11 +4890,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.368760983794</v>
+        <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.676234212966</v>
+        <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4953,11 +4953,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.368765555555</v>
+        <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.34390984954</v>
+        <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5006,11 +5006,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.36877094908</v>
+        <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.34391065972</v>
+        <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5059,11 +5059,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.3687891088</v>
+        <v>46195.53545577546</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.401230648145</v>
+        <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5106,11 +5106,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.36879190972</v>
+        <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.33357613426</v>
+        <v>46197.500242800925</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5169,11 +5169,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.36879724537</v>
+        <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.333589050926</v>
+        <v>46197.50025571759</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5232,11 +5232,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.368809085645</v>
+        <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.332797696756</v>
+        <v>46197.49946436343</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5295,11 +5295,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.36885640046</v>
+        <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.41856439815</v>
+        <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5358,11 +5358,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.36886232639</v>
+        <v>46195.53552899306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.41117839121</v>
+        <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5405,11 +5405,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.36886619213</v>
+        <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.418684421296</v>
+        <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5468,11 +5468,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.368874907406</v>
+        <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.41864616898</v>
+        <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5521,11 +5521,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.36887936342</v>
+        <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.418642916666</v>
+        <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5574,11 +5574,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.36889657407</v>
+        <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.4188153588</v>
+        <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5637,11 +5637,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.368901064816</v>
+        <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.34390733796</v>
+        <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5690,11 +5690,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.36890722222</v>
+        <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.34391114583</v>
+        <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5743,11 +5743,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.36892862269</v>
+        <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.41893768519</v>
+        <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5804,11 +5804,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.36893298611</v>
+        <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.34390907407</v>
+        <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5855,11 +5855,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.36893917824</v>
+        <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.34392082176</v>
+        <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5906,11 +5906,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.36896231482</v>
+        <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.41904408565</v>
+        <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -5967,11 +5967,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.368966875</v>
+        <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.343907835646</v>
+        <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6020,11 +6020,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.368972384254</v>
+        <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34390944445</v>
+        <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6073,11 +6073,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.369038993056</v>
+        <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.419168946755</v>
+        <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6134,11 +6134,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.36904384259</v>
+        <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.41912155093</v>
+        <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6187,11 +6187,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.36904954861</v>
+        <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.4191184375</v>
+        <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.36906917824</v>
+        <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.41929259259</v>
+        <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6303,11 +6303,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.36907429398</v>
+        <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.41925020833</v>
+        <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6356,11 +6356,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.36907854167</v>
+        <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.419247233796</v>
+        <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6409,11 +6409,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.369095636575</v>
+        <v>46195.53576230324</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.41406733796</v>
+        <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6456,11 +6456,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.36909965277</v>
+        <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.419515671296</v>
+        <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6519,11 +6519,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.36910545139</v>
+        <v>46195.535772118055</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.41947037037</v>
+        <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6570,11 +6570,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.36911015047</v>
+        <v>46195.53577681713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.419467141204</v>
+        <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6623,11 +6623,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.36913409722</v>
+        <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.419691539355</v>
+        <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6686,11 +6686,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.36913894676</v>
+        <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.41965655093</v>
+        <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6739,11 +6739,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.36914364583</v>
+        <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.419653414356</v>
+        <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6792,11 +6792,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.36920184028</v>
+        <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.4198324537</v>
+        <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6855,11 +6855,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.369207627315</v>
+        <v>46195.535874293986</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.41979299768</v>
+        <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6906,11 +6906,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.369218113425</v>
+        <v>46195.535884780096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.41979018519</v>
+        <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6957,11 +6957,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.36924396991</v>
+        <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.41997931713</v>
+        <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7020,11 +7020,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.369249456024</v>
+        <v>46195.53591612268</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.41993966435</v>
+        <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7071,11 +7071,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.36925358797</v>
+        <v>46195.535920254624</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.419936412036</v>
+        <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7122,11 +7122,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.36927013889</v>
+        <v>46195.53593680555</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.414523252315</v>
+        <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7169,11 +7169,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.36927350695</v>
+        <v>46195.535940173606</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.42016065972</v>
+        <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7232,11 +7232,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.36927831019</v>
+        <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.42010171297</v>
+        <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:,propuesta motor - 4363</t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1215923636075067</t>
@@ -291,6 +288,9 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
   <si>
     <t>1215922057135204</t>
@@ -1952,7 +1952,7 @@
         <v>46197.84418690972</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.8442027662</v>
+        <v>46199.20165502315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1996,8 +1996,8 @@
       <c r="R10" s="5">
         <v>46198</v>
       </c>
-      <c r="S10" s="11" t="s">
-        <v>49</v>
+      <c r="S10" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8">
         <v>46195.535038055554</v>
@@ -2017,10 +2017,10 @@
         <v>46197.84430075232</v>
       </c>
       <c r="D11" s="8">
-        <v>46197.84431771991</v>
+        <v>46199.201655150464</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -2041,7 +2041,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
@@ -2053,7 +2053,7 @@
         <v>39</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="8">
         <v>46197</v>
@@ -2061,8 +2061,8 @@
       <c r="R11" s="8">
         <v>46198</v>
       </c>
-      <c r="S11" s="11" t="s">
-        <v>49</v>
+      <c r="S11" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T11" s="9">
         <v>1</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5">
         <v>46195.53504337963</v>
@@ -2085,7 +2085,7 @@
         <v>46198.173893935185</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2106,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2118,7 +2118,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="5">
         <v>46197</v>
@@ -2127,7 +2127,7 @@
         <v>46205</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
@@ -2148,7 +2148,7 @@
         <v>46197.84438787037</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2172,7 +2172,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
@@ -2197,7 +2197,7 @@
         <v>46197.844396712964</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2224,13 +2224,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2239,7 +2239,7 @@
         <v>46203</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T14" s="6">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
@@ -2262,7 +2262,7 @@
         <v>46197.84431825232</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2289,13 +2289,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2304,18 +2304,18 @@
         <v>46203</v>
       </c>
       <c r="S15" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
@@ -2327,16 +2327,16 @@
         <v>46197.84431829861</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2354,13 +2354,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2369,18 +2369,18 @@
         <v>46203</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2390,16 +2390,16 @@
         <v>46198.51059534722</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2417,13 +2417,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2432,13 +2432,13 @@
         <v>46225</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T17" s="9">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2459,10 +2459,10 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2480,10 +2480,10 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>81</v>
@@ -2495,13 +2495,13 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2522,10 +2522,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2543,10 +2543,10 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>84</v>
@@ -2558,13 +2558,13 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T19" s="9">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2585,10 +2585,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2606,10 +2606,10 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>87</v>
@@ -2621,13 +2621,13 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2694,7 +2694,7 @@
         <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.84440070602</v>
+        <v>46199.19011668982</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2703,10 +2703,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2727,7 +2727,7 @@
         <v>89</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>93</v>
@@ -2738,14 +2738,14 @@
       <c r="R22" s="5">
         <v>46206</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>49</v>
+      <c r="S22" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2759,7 +2759,7 @@
         <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.500242662034</v>
+        <v>46199.19011649306</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -2768,10 +2768,10 @@
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2792,7 +2792,7 @@
         <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>96</v>
@@ -2803,8 +2803,8 @@
       <c r="R23" s="8">
         <v>46206</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>49</v>
+      <c r="S23" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -2824,7 +2824,7 @@
         <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.50025311342</v>
+        <v>46199.19011700232</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2833,10 +2833,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2857,7 +2857,7 @@
         <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>99</v>
@@ -2868,8 +2868,8 @@
       <c r="R24" s="5">
         <v>46206</v>
       </c>
-      <c r="S24" s="11" t="s">
-        <v>49</v>
+      <c r="S24" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>110</v>
@@ -3038,7 +3038,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
@@ -3097,7 +3097,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3712,7 +3712,7 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3759,7 +3759,7 @@
         <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>151</v>
@@ -3771,7 +3771,7 @@
         <v>46212</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3836,7 +3836,7 @@
         <v>46190</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3859,7 +3859,7 @@
         <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -3901,7 +3901,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4176,7 +4176,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4302,7 +4302,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -4939,7 +4939,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5155,13 +5155,13 @@
         <v>46209</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5218,13 +5218,13 @@
         <v>46209</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5281,13 +5281,13 @@
         <v>46209</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5454,7 +5454,7 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5534,10 +5534,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5587,10 +5587,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5623,7 +5623,7 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5650,10 +5650,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5703,10 +5703,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5756,10 +5756,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5790,7 +5790,7 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
@@ -5817,10 +5817,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5868,10 +5868,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5919,10 +5919,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5953,7 +5953,7 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -5980,10 +5980,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6033,10 +6033,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6086,10 +6086,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6120,7 +6120,7 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
@@ -6147,10 +6147,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6200,10 +6200,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6253,10 +6253,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6289,7 +6289,7 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6316,10 +6316,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6369,10 +6369,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6505,7 +6505,7 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6672,7 +6672,7 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6699,10 +6699,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6752,10 +6752,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6841,7 +6841,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7006,7 +7006,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
@@ -7281,7 +7281,7 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.500242800925</v>
+        <v>46202.17905025463</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5154,8 +5154,8 @@
       <c r="R64" s="5">
         <v>46209</v>
       </c>
-      <c r="S64" s="11" t="s">
-        <v>78</v>
+      <c r="S64" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.50025571759</v>
+        <v>46202.179049768514</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5217,8 +5217,8 @@
       <c r="R65" s="8">
         <v>46209</v>
       </c>
-      <c r="S65" s="11" t="s">
-        <v>78</v>
+      <c r="S65" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.49946436343</v>
+        <v>46202.179049768514</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5280,8 +5280,8 @@
       <c r="R66" s="5">
         <v>46209</v>
       </c>
-      <c r="S66" s="11" t="s">
-        <v>78</v>
+      <c r="S66" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -2641,7 +2641,7 @@
         <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.500272743055</v>
+        <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -2194,7 +2194,7 @@
         <v>46197.844381840274</v>
       </c>
       <c r="D14" s="5">
-        <v>46197.844396712964</v>
+        <v>46204.19501678241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2238,8 +2238,8 @@
       <c r="R14" s="5">
         <v>46203</v>
       </c>
-      <c r="S14" s="12" t="s">
-        <v>57</v>
+      <c r="S14" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T14" s="6">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46197.84431825232</v>
+        <v>46204.19501679398</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2303,8 +2303,8 @@
       <c r="R15" s="8">
         <v>46203</v>
       </c>
-      <c r="S15" s="12" t="s">
-        <v>57</v>
+      <c r="S15" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
@@ -2324,7 +2324,7 @@
         <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.84431829861</v>
+        <v>46204.195016655096</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2368,8 +2368,8 @@
       <c r="R16" s="5">
         <v>46203</v>
       </c>
-      <c r="S16" s="12" t="s">
-        <v>57</v>
+      <c r="S16" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.53486788194</v>
+        <v>46195.36820121528</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.84318319445</v>
+        <v>46197.676516527776</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.8432930787</v>
+        <v>46197.67662641204</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.53501399305</v>
+        <v>46195.36834732639</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.8431590625</v>
+        <v>46197.67649239583</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.8431844213</v>
+        <v>46197.67651775463</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.53501732639</v>
+        <v>46195.36835065972</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.84315976852</v>
+        <v>46197.676493101855</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.84318438657</v>
+        <v>46197.67651771991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.53502171296</v>
+        <v>46195.368355046296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.84316024306</v>
+        <v>46197.67649357639</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.84319010416</v>
+        <v>46197.676523437505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.535025543984</v>
+        <v>46195.36835887731</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.84316074074</v>
+        <v>46197.676494074076</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.84318458333</v>
+        <v>46197.67651791667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.534873819444</v>
+        <v>46195.36820715277</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.84431706018</v>
+        <v>46197.67765039352</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.84432748843</v>
+        <v>46197.67766082176</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.53503290509</v>
+        <v>46195.36836623843</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.84418690972</v>
+        <v>46197.67752024306</v>
       </c>
       <c r="D10" s="5">
-        <v>46199.20165502315</v>
+        <v>46199.03498835648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.535038055554</v>
+        <v>46195.36837138889</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.84430075232</v>
+        <v>46197.677634085645</v>
       </c>
       <c r="D11" s="8">
-        <v>46199.201655150464</v>
+        <v>46199.03498848379</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2076,13 +2076,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.53504337963</v>
+        <v>46195.36837671296</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.843900266205</v>
+        <v>46197.677233599534</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.173893935185</v>
+        <v>46198.00722726852</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2141,11 +2141,11 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.53487891203</v>
+        <v>46195.368212245376</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.84438787037</v>
+        <v>46197.677721203705</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2188,13 +2188,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.53505578704</v>
+        <v>46195.36838912037</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.844381840274</v>
+        <v>46197.67771517361</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.19501678241</v>
+        <v>46204.02835011574</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2253,13 +2253,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.535061620365</v>
+        <v>46195.36839495371</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.49930170139</v>
+        <v>46197.33263503472</v>
       </c>
       <c r="D15" s="8">
-        <v>46204.19501679398</v>
+        <v>46204.028350127315</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2318,13 +2318,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.53506689815</v>
+        <v>46195.368400231484</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.49934962963</v>
+        <v>46197.332682962966</v>
       </c>
       <c r="D16" s="5">
-        <v>46204.195016655096</v>
+        <v>46204.028349988424</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2383,11 +2383,11 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.53507237269</v>
+        <v>46195.368405706016</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46198.51059534722</v>
+        <v>46198.34392868055</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2446,11 +2446,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.535077141205</v>
+        <v>46195.36841047453</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.51059627315</v>
+        <v>46198.34392960648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2509,11 +2509,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.53508107639</v>
+        <v>46195.36841440972</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46198.51059506944</v>
+        <v>46198.34392840278</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2572,11 +2572,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.535084918985</v>
+        <v>46195.368418252314</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.51059547454</v>
+        <v>46198.343928807866</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2635,13 +2635,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.55482737269</v>
+        <v>46195.38816070602</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.50025414352</v>
+        <v>46197.33358747685</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.636544884255</v>
+        <v>46203.46987821759</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.55503578704</v>
+        <v>46195.38836912037</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.49944752315</v>
+        <v>46197.33278085648</v>
       </c>
       <c r="D22" s="5">
-        <v>46199.19011668982</v>
+        <v>46199.023450023145</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2753,13 +2753,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.5550796412</v>
+        <v>46195.38841297454</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.500224166666</v>
+        <v>46197.333557499995</v>
       </c>
       <c r="D23" s="8">
-        <v>46199.19011649306</v>
+        <v>46199.02344982639</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -2818,13 +2818,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.555127037034</v>
+        <v>46195.38846037037</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.50023636574</v>
+        <v>46197.33356969907</v>
       </c>
       <c r="D24" s="5">
-        <v>46199.19011700232</v>
+        <v>46199.02345033565</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2883,11 +2883,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.534883761575</v>
+        <v>46195.3682170949</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.56979528935</v>
+        <v>46195.40312862268</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2930,11 +2930,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.53514152778</v>
+        <v>46195.36847486111</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.583322719904</v>
+        <v>46195.41665605324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2993,11 +2993,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.535146215276</v>
+        <v>46195.36847954861</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.583258530096</v>
+        <v>46195.416591863424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3052,11 +3052,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.53519951389</v>
+        <v>46195.36853284722</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.58325561343</v>
+        <v>46195.416588946755</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3111,11 +3111,11 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.535206608794</v>
+        <v>46195.36853994213</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.58349109953</v>
+        <v>46195.416824432876</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3174,11 +3174,11 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.53521144676</v>
+        <v>46195.368544780096</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.58342974537</v>
+        <v>46195.416763078705</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>81</v>
@@ -3227,11 +3227,11 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.53521638889</v>
+        <v>46195.36854972222</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.583426701385</v>
+        <v>46195.41676003472</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3280,11 +3280,11 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.53522158565</v>
+        <v>46195.36855491898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.58374949074</v>
+        <v>46195.417082824075</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3343,11 +3343,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.53522605324</v>
+        <v>46195.368559386574</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.58357594907</v>
+        <v>46195.41690928241</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>87</v>
@@ -3396,11 +3396,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.5352309375</v>
+        <v>46195.36856427083</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.58357231482</v>
+        <v>46195.41690564815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3449,11 +3449,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.53523623843</v>
+        <v>46195.36856957176</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.58370322917</v>
+        <v>46195.4170365625</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3502,11 +3502,11 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.535239398145</v>
+        <v>46195.36857273148</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.58395704861</v>
+        <v>46195.41729038194</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3565,11 +3565,11 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.53524336805</v>
+        <v>46195.36857670139</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.583877337966</v>
+        <v>46195.417210671294</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>84</v>
@@ -3618,11 +3618,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.53524819444</v>
+        <v>46195.36858152778</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.583909918976</v>
+        <v>46195.41724325232</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3671,11 +3671,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.5348887037</v>
+        <v>46195.36822203704</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.51053421297</v>
+        <v>46198.3438675463</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3720,13 +3720,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.535254629634</v>
+        <v>46195.36858796296</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.51038958333</v>
+        <v>46198.34372291667</v>
       </c>
       <c r="D40" s="5">
-        <v>46198.51040733796</v>
+        <v>46205.04118946759</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3770,8 +3770,8 @@
       <c r="R40" s="5">
         <v>46212</v>
       </c>
-      <c r="S40" s="11" t="s">
-        <v>78</v>
+      <c r="S40" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3785,13 +3785,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.53526092593</v>
+        <v>46195.36859425926</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.51051443287</v>
+        <v>46198.3438477662</v>
       </c>
       <c r="D41" s="8">
-        <v>46198.510531990745</v>
+        <v>46198.343865324074</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3850,13 +3850,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.53526833333</v>
+        <v>46195.36860166666</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.51056810185</v>
+        <v>46198.34390143519</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.51058418982</v>
+        <v>46198.34391752315</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>76</v>
@@ -3915,11 +3915,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.53528606481</v>
+        <v>46195.36861939815</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46195.41768052083</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3978,11 +3978,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.535290266205</v>
+        <v>46195.36862359954</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46195.41763832176</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4029,11 +4029,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.53529509259</v>
+        <v>46195.36862842593</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46195.41763506945</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4080,11 +4080,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.53533827546</v>
+        <v>46195.3686716088</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.572334930555</v>
+        <v>46195.40566826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4127,11 +4127,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.53534217592</v>
+        <v>46195.368675509264</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.58444471065</v>
+        <v>46195.41777804398</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4190,11 +4190,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.53534689815</v>
+        <v>46195.36868023148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46195.41788641203</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4253,11 +4253,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.5353533912</v>
+        <v>46195.36868672454</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.584441377316</v>
+        <v>46195.417774710644</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4316,11 +4316,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.53535798611</v>
+        <v>46195.36869131944</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46195.41788364583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4379,11 +4379,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.535361689814</v>
+        <v>46195.36869502315</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.584438252314</v>
+        <v>46195.41777158565</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4442,11 +4442,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.53536568287</v>
+        <v>46195.3686990162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46195.41787967592</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4505,11 +4505,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.5353693287</v>
+        <v>46195.36870266203</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46195.40720042824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4552,11 +4552,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.53537232639</v>
+        <v>46195.36870565973</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46195.41815065972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4615,11 +4615,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.53537631944</v>
+        <v>46195.36870965278</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46195.41811395834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4668,11 +4668,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.53538179398</v>
+        <v>46195.36871512732</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46195.41811086806</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.53540148148</v>
+        <v>46195.368734814816</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46195.418361759264</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4784,11 +4784,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.53540543982</v>
+        <v>46195.36873877315</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.51058690972</v>
+        <v>46198.34392024306</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4837,11 +4837,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.53541055556</v>
+        <v>46195.36874388889</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.510575162036</v>
+        <v>46198.34390849537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4890,11 +4890,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.535427650466</v>
+        <v>46195.368760983794</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.84290087963</v>
+        <v>46197.676234212966</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4953,11 +4953,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.53543222223</v>
+        <v>46195.368765555555</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.5105765162</v>
+        <v>46198.34390984954</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5006,11 +5006,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.53543761574</v>
+        <v>46195.36877094908</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.51057732639</v>
+        <v>46198.34391065972</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5059,11 +5059,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.53545577546</v>
+        <v>46195.3687891088</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.56789731482</v>
+        <v>46195.401230648145</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5106,11 +5106,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.535458576385</v>
+        <v>46195.36879190972</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46202.17905025463</v>
+        <v>46202.012383587964</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5169,11 +5169,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.535463912034</v>
+        <v>46195.36879724537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46202.179049768514</v>
+        <v>46202.01238310186</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5232,11 +5232,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.53547575232</v>
+        <v>46195.368809085645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46202.179049768514</v>
+        <v>46202.01238310186</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5295,11 +5295,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.53552306713</v>
+        <v>46195.36885640046</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.58523106482</v>
+        <v>46195.41856439815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5358,11 +5358,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.53552899306</v>
+        <v>46195.36886232639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.577845057865</v>
+        <v>46195.41117839121</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5405,11 +5405,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.5355328588</v>
+        <v>46195.36886619213</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46195.418684421296</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5468,11 +5468,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.53554157408</v>
+        <v>46195.368874907406</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46195.41864616898</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5521,11 +5521,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.53554603009</v>
+        <v>46195.36887936342</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46195.418642916666</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5574,11 +5574,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.535563240745</v>
+        <v>46195.36889657407</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46195.4188153588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5637,11 +5637,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.53556773148</v>
+        <v>46195.368901064816</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.51057400463</v>
+        <v>46198.34390733796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5690,11 +5690,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.53557388889</v>
+        <v>46195.36890722222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.5105778125</v>
+        <v>46198.34391114583</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5743,11 +5743,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.53559528935</v>
+        <v>46195.36892862269</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46195.41893768519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5804,11 +5804,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.53559965278</v>
+        <v>46195.36893298611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.510575740744</v>
+        <v>46198.34390907407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5855,11 +5855,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.53560584491</v>
+        <v>46195.36893917824</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.510587488425</v>
+        <v>46198.34392082176</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5906,11 +5906,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.53562898148</v>
+        <v>46195.36896231482</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46195.41904408565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -5967,11 +5967,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.535633541665</v>
+        <v>46195.368966875</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.51057450232</v>
+        <v>46198.343907835646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6020,11 +6020,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.535639050926</v>
+        <v>46195.368972384254</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51057611111</v>
+        <v>46198.34390944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6073,11 +6073,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.53570565972</v>
+        <v>46195.369038993056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46195.419168946755</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6134,11 +6134,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.535710509255</v>
+        <v>46195.36904384259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46195.41912155093</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6187,11 +6187,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.53571621528</v>
+        <v>46195.36904954861</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46195.4191184375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.53573584491</v>
+        <v>46195.36906917824</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46195.41929259259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6303,11 +6303,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.53574096065</v>
+        <v>46195.36907429398</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46195.41925020833</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6356,11 +6356,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.53574520833</v>
+        <v>46195.36907854167</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46195.419247233796</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6409,11 +6409,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.53576230324</v>
+        <v>46195.369095636575</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.58073400463</v>
+        <v>46195.41406733796</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6456,11 +6456,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.535766319445</v>
+        <v>46195.36909965277</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46195.419515671296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6519,11 +6519,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.535772118055</v>
+        <v>46195.36910545139</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46195.41947037037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6570,11 +6570,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.53577681713</v>
+        <v>46195.36911015047</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46195.419467141204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6623,11 +6623,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.535800763886</v>
+        <v>46195.36913409722</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46195.419691539355</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6686,11 +6686,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.53580561343</v>
+        <v>46195.36913894676</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46195.41965655093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6739,11 +6739,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.5358103125</v>
+        <v>46195.36914364583</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46195.419653414356</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6792,11 +6792,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.535868506944</v>
+        <v>46195.36920184028</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46195.4198324537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6855,11 +6855,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.535874293986</v>
+        <v>46195.369207627315</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46195.41979299768</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6906,11 +6906,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.535884780096</v>
+        <v>46195.369218113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46195.41979018519</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6957,11 +6957,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.53591063658</v>
+        <v>46195.36924396991</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46195.41997931713</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7020,11 +7020,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.53591612268</v>
+        <v>46195.369249456024</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46195.41993966435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7071,11 +7071,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.535920254624</v>
+        <v>46195.36925358797</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46195.419936412036</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7122,11 +7122,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.53593680555</v>
+        <v>46195.36927013889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.58118991899</v>
+        <v>46195.414523252315</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7169,11 +7169,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.535940173606</v>
+        <v>46195.36927350695</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46195.42016065972</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7232,11 +7232,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.53594497685</v>
+        <v>46195.36927831019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46195.42010171297</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.36820121528</v>
+        <v>46195.53486788194</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.676516527776</v>
+        <v>46197.84318319445</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.67662641204</v>
+        <v>46197.8432930787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.36834732639</v>
+        <v>46195.53501399305</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.67649239583</v>
+        <v>46197.8431590625</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.67651775463</v>
+        <v>46197.8431844213</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.36835065972</v>
+        <v>46195.53501732639</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.676493101855</v>
+        <v>46197.84315976852</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.67651771991</v>
+        <v>46197.84318438657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.368355046296</v>
+        <v>46195.53502171296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.67649357639</v>
+        <v>46197.84316024306</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.676523437505</v>
+        <v>46197.84319010416</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.36835887731</v>
+        <v>46195.535025543984</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.676494074076</v>
+        <v>46197.84316074074</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.67651791667</v>
+        <v>46197.84318458333</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.36820715277</v>
+        <v>46195.534873819444</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.67765039352</v>
+        <v>46197.84431706018</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.67766082176</v>
+        <v>46197.84432748843</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.36836623843</v>
+        <v>46195.53503290509</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.67752024306</v>
+        <v>46197.84418690972</v>
       </c>
       <c r="D10" s="5">
-        <v>46199.03498835648</v>
+        <v>46199.20165502315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.36837138889</v>
+        <v>46195.535038055554</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.677634085645</v>
+        <v>46197.84430075232</v>
       </c>
       <c r="D11" s="8">
-        <v>46199.03498848379</v>
+        <v>46199.201655150464</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2076,13 +2076,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.36837671296</v>
+        <v>46195.53504337963</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.677233599534</v>
+        <v>46197.843900266205</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.00722726852</v>
+        <v>46198.173893935185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2141,11 +2141,11 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.368212245376</v>
+        <v>46195.53487891203</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46197.677721203705</v>
+        <v>46197.84438787037</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2188,13 +2188,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.36838912037</v>
+        <v>46195.53505578704</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.67771517361</v>
+        <v>46197.844381840274</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.02835011574</v>
+        <v>46204.19501678241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2253,13 +2253,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.36839495371</v>
+        <v>46195.535061620365</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.33263503472</v>
+        <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46204.028350127315</v>
+        <v>46204.19501679398</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2318,13 +2318,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.368400231484</v>
+        <v>46195.53506689815</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.332682962966</v>
+        <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46204.028349988424</v>
+        <v>46204.195016655096</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2383,11 +2383,11 @@
         <v>72</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.368405706016</v>
+        <v>46195.53507237269</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46198.34392868055</v>
+        <v>46198.51059534722</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2446,11 +2446,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.36841047453</v>
+        <v>46195.535077141205</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.34392960648</v>
+        <v>46198.51059627315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2509,11 +2509,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.36841440972</v>
+        <v>46195.53508107639</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46198.34392840278</v>
+        <v>46198.51059506944</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2572,11 +2572,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.368418252314</v>
+        <v>46195.535084918985</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.343928807866</v>
+        <v>46198.51059547454</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2635,13 +2635,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.38816070602</v>
+        <v>46195.55482737269</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.33358747685</v>
+        <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.46987821759</v>
+        <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.38836912037</v>
+        <v>46195.55503578704</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.33278085648</v>
+        <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46199.023450023145</v>
+        <v>46199.19011668982</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2753,13 +2753,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.38841297454</v>
+        <v>46195.5550796412</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.333557499995</v>
+        <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46199.02344982639</v>
+        <v>46199.19011649306</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -2818,13 +2818,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.38846037037</v>
+        <v>46195.555127037034</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.33356969907</v>
+        <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46199.02345033565</v>
+        <v>46199.19011700232</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2883,11 +2883,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.3682170949</v>
+        <v>46195.534883761575</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.40312862268</v>
+        <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -2930,11 +2930,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.36847486111</v>
+        <v>46195.53514152778</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.41665605324</v>
+        <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2993,11 +2993,11 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.36847954861</v>
+        <v>46195.535146215276</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.416591863424</v>
+        <v>46195.583258530096</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3052,11 +3052,11 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.36853284722</v>
+        <v>46195.53519951389</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46195.416588946755</v>
+        <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3111,11 +3111,11 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.36853994213</v>
+        <v>46195.535206608794</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46195.416824432876</v>
+        <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3174,11 +3174,11 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.368544780096</v>
+        <v>46195.53521144676</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.416763078705</v>
+        <v>46195.58342974537</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>81</v>
@@ -3227,11 +3227,11 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.36854972222</v>
+        <v>46195.53521638889</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46195.41676003472</v>
+        <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3280,11 +3280,11 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.36855491898</v>
+        <v>46195.53522158565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.417082824075</v>
+        <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3343,11 +3343,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.368559386574</v>
+        <v>46195.53522605324</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.41690928241</v>
+        <v>46195.58357594907</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>87</v>
@@ -3396,11 +3396,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.36856427083</v>
+        <v>46195.5352309375</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.41690564815</v>
+        <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3449,11 +3449,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.36856957176</v>
+        <v>46195.53523623843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.4170365625</v>
+        <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3502,11 +3502,11 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.36857273148</v>
+        <v>46195.535239398145</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.41729038194</v>
+        <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3565,11 +3565,11 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.36857670139</v>
+        <v>46195.53524336805</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.417210671294</v>
+        <v>46195.583877337966</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>84</v>
@@ -3618,11 +3618,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.36858152778</v>
+        <v>46195.53524819444</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.41724325232</v>
+        <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3671,11 +3671,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.36822203704</v>
+        <v>46195.5348887037</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.3438675463</v>
+        <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3720,13 +3720,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.36858796296</v>
+        <v>46195.535254629634</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.34372291667</v>
+        <v>46198.51038958333</v>
       </c>
       <c r="D40" s="5">
-        <v>46205.04118946759</v>
+        <v>46205.207856134264</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3785,13 +3785,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.36859425926</v>
+        <v>46195.53526092593</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.3438477662</v>
+        <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46198.343865324074</v>
+        <v>46198.510531990745</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3850,13 +3850,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.36860166666</v>
+        <v>46195.53526833333</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.34390143519</v>
+        <v>46198.51056810185</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.34391752315</v>
+        <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>76</v>
@@ -3915,11 +3915,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.36861939815</v>
+        <v>46195.53528606481</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.41768052083</v>
+        <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3978,11 +3978,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.36862359954</v>
+        <v>46195.535290266205</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.41763832176</v>
+        <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4029,11 +4029,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.36862842593</v>
+        <v>46195.53529509259</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.41763506945</v>
+        <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4080,11 +4080,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.3686716088</v>
+        <v>46195.53533827546</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.40566826389</v>
+        <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4127,11 +4127,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.368675509264</v>
+        <v>46195.53534217592</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.41777804398</v>
+        <v>46195.58444471065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4190,11 +4190,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.36868023148</v>
+        <v>46195.53534689815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.41788641203</v>
+        <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4253,11 +4253,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.36868672454</v>
+        <v>46195.5353533912</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.417774710644</v>
+        <v>46195.584441377316</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4316,11 +4316,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.36869131944</v>
+        <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.41788364583</v>
+        <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4379,11 +4379,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.36869502315</v>
+        <v>46195.535361689814</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.41777158565</v>
+        <v>46195.584438252314</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4442,11 +4442,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.3686990162</v>
+        <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.41787967592</v>
+        <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4505,11 +4505,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.36870266203</v>
+        <v>46195.5353693287</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.40720042824</v>
+        <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4552,11 +4552,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.36870565973</v>
+        <v>46195.53537232639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.41815065972</v>
+        <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4615,11 +4615,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.36870965278</v>
+        <v>46195.53537631944</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.41811395834</v>
+        <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4668,11 +4668,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.36871512732</v>
+        <v>46195.53538179398</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.41811086806</v>
+        <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.368734814816</v>
+        <v>46195.53540148148</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.418361759264</v>
+        <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4784,11 +4784,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.36873877315</v>
+        <v>46195.53540543982</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.34392024306</v>
+        <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4837,11 +4837,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.36874388889</v>
+        <v>46195.53541055556</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.34390849537</v>
+        <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4890,11 +4890,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.368760983794</v>
+        <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.676234212966</v>
+        <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4953,11 +4953,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.368765555555</v>
+        <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.34390984954</v>
+        <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5006,11 +5006,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.36877094908</v>
+        <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.34391065972</v>
+        <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5059,11 +5059,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.3687891088</v>
+        <v>46195.53545577546</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.401230648145</v>
+        <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5106,11 +5106,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.36879190972</v>
+        <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46202.012383587964</v>
+        <v>46202.17905025463</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5169,11 +5169,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.36879724537</v>
+        <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46202.01238310186</v>
+        <v>46202.179049768514</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5232,11 +5232,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.368809085645</v>
+        <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46202.01238310186</v>
+        <v>46202.179049768514</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5295,11 +5295,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.36885640046</v>
+        <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.41856439815</v>
+        <v>46195.58523106482</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5358,11 +5358,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.36886232639</v>
+        <v>46195.53552899306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.41117839121</v>
+        <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5405,11 +5405,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.36886619213</v>
+        <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.418684421296</v>
+        <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5468,11 +5468,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.368874907406</v>
+        <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.41864616898</v>
+        <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5521,11 +5521,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.36887936342</v>
+        <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.418642916666</v>
+        <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5574,11 +5574,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.36889657407</v>
+        <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.4188153588</v>
+        <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5637,11 +5637,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.368901064816</v>
+        <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.34390733796</v>
+        <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5690,11 +5690,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.36890722222</v>
+        <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.34391114583</v>
+        <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5743,11 +5743,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.36892862269</v>
+        <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.41893768519</v>
+        <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5804,11 +5804,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.36893298611</v>
+        <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.34390907407</v>
+        <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5855,11 +5855,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.36893917824</v>
+        <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.34392082176</v>
+        <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5906,11 +5906,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.36896231482</v>
+        <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.41904408565</v>
+        <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -5967,11 +5967,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.368966875</v>
+        <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.343907835646</v>
+        <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6020,11 +6020,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.368972384254</v>
+        <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34390944445</v>
+        <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6073,11 +6073,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.369038993056</v>
+        <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.419168946755</v>
+        <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6134,11 +6134,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.36904384259</v>
+        <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.41912155093</v>
+        <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6187,11 +6187,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.36904954861</v>
+        <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.4191184375</v>
+        <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6240,11 +6240,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.36906917824</v>
+        <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.41929259259</v>
+        <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6303,11 +6303,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.36907429398</v>
+        <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.41925020833</v>
+        <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6356,11 +6356,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.36907854167</v>
+        <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.419247233796</v>
+        <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6409,11 +6409,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.369095636575</v>
+        <v>46195.53576230324</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.41406733796</v>
+        <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6456,11 +6456,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.36909965277</v>
+        <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.419515671296</v>
+        <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6519,11 +6519,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.36910545139</v>
+        <v>46195.535772118055</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.41947037037</v>
+        <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6570,11 +6570,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.36911015047</v>
+        <v>46195.53577681713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.419467141204</v>
+        <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6623,11 +6623,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.36913409722</v>
+        <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.419691539355</v>
+        <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6686,11 +6686,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.36913894676</v>
+        <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.41965655093</v>
+        <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6739,11 +6739,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.36914364583</v>
+        <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.419653414356</v>
+        <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6792,11 +6792,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.36920184028</v>
+        <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.4198324537</v>
+        <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6855,11 +6855,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.369207627315</v>
+        <v>46195.535874293986</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.41979299768</v>
+        <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6906,11 +6906,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.369218113425</v>
+        <v>46195.535884780096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.41979018519</v>
+        <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6957,11 +6957,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.36924396991</v>
+        <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.41997931713</v>
+        <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7020,11 +7020,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.369249456024</v>
+        <v>46195.53591612268</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.41993966435</v>
+        <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7071,11 +7071,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.36925358797</v>
+        <v>46195.535920254624</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.419936412036</v>
+        <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7122,11 +7122,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.36927013889</v>
+        <v>46195.53593680555</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.414523252315</v>
+        <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7169,11 +7169,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.36927350695</v>
+        <v>46195.535940173606</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.42016065972</v>
+        <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7232,11 +7232,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.36927831019</v>
+        <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.42010171297</v>
+        <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -227,115 +227,115 @@
     <t>Planos preliminar,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
+    <t>1215922055649556</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4363,propuesta motor - 4363,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>1215930353744116</t>
+  </si>
+  <si>
+    <t>propuesta motor - 4363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>1215923636093325</t>
+  </si>
+  <si>
+    <t>propuesta alabes - 4363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215932733979125</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1215932733979147</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1215922057135204</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057135216</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215930353764509</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363</t>
+  </si>
+  <si>
+    <t>1215927804444266</t>
+  </si>
+  <si>
+    <t>Reserva Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>1215927804444272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion motor</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215922055649556</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4363,propuesta motor - 4363,propuesta alabes - 4363,propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>1215930353744116</t>
-  </si>
-  <si>
-    <t>propuesta motor - 4363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>1215923636093325</t>
-  </si>
-  <si>
-    <t>propuesta alabes - 4363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215932733979125</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1215932733979147</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1215922057135204</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057135216</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215930353764509</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363</t>
-  </si>
-  <si>
-    <t>1215927804444266</t>
-  </si>
-  <si>
-    <t>Reserva Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>1215927804444272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion motor</t>
   </si>
   <si>
     <t>1215927804444273</t>
@@ -2082,7 +2082,7 @@
         <v>46197.843900266205</v>
       </c>
       <c r="D12" s="5">
-        <v>46198.173893935185</v>
+        <v>46206.17883685185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2126,8 +2126,8 @@
       <c r="R12" s="5">
         <v>46205</v>
       </c>
-      <c r="S12" s="12" t="s">
-        <v>57</v>
+      <c r="S12" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2138,17 +2138,19 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8">
+        <v>46206.50646099537</v>
+      </c>
       <c r="D13" s="8">
-        <v>46197.84438787037</v>
+        <v>46206.50647436343</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2172,7 +2174,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2180,12 +2182,16 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
+      <c r="T13" s="9">
+        <v>1</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
@@ -2197,7 +2203,7 @@
         <v>46204.19501678241</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2224,13 +2230,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2250,7 +2256,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
@@ -2262,7 +2268,7 @@
         <v>46204.19501679398</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2289,13 +2295,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2310,12 +2316,12 @@
         <v>1</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
@@ -2327,16 +2333,16 @@
         <v>46204.195016655096</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2354,13 +2360,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>50</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2375,31 +2381,33 @@
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="8">
+        <v>46206.505830497685</v>
+      </c>
       <c r="D17" s="8">
-        <v>46198.51059534722</v>
+        <v>46206.50589585648</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2417,13 +2425,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2432,37 +2440,39 @@
         <v>46225</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46206.50602077546</v>
+      </c>
       <c r="D18" s="5">
-        <v>46198.51059627315</v>
+        <v>46206.506043506946</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2480,13 +2490,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2495,37 +2505,39 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8">
+        <v>46206.50625340278</v>
+      </c>
       <c r="D19" s="8">
-        <v>46198.51059506944</v>
+        <v>46206.506269930556</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2543,13 +2555,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2558,37 +2570,39 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T19" s="9">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46206.50644165509</v>
+      </c>
       <c r="D20" s="5">
-        <v>46198.51059547454</v>
+        <v>46206.50646081018</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2606,13 +2620,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2621,18 +2635,18 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2644,7 +2658,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2668,7 +2682,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2685,7 +2699,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2697,16 +2711,16 @@
         <v>46199.19011668982</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2724,13 +2738,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2739,13 +2753,13 @@
         <v>46206</v>
       </c>
       <c r="S22" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2768,10 +2782,10 @@
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2789,10 +2803,10 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>96</v>
@@ -2804,7 +2818,7 @@
         <v>46206</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -2833,10 +2847,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2854,10 +2868,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>99</v>
@@ -2869,7 +2883,7 @@
         <v>46206</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -2979,7 +2993,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -2997,7 +3011,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46195.583258530096</v>
+        <v>46206.50586751157</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -3030,7 +3044,7 @@
         <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>110</v>
@@ -3038,7 +3052,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
@@ -3097,7 +3111,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3160,7 +3174,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
@@ -3178,10 +3192,10 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.58342974537</v>
+        <v>46206.50602773148</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3211,7 +3225,7 @@
         <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>118</v>
@@ -3264,7 +3278,7 @@
         <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>121</v>
@@ -3329,7 +3343,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3347,10 +3361,10 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46195.58357594907</v>
+        <v>46206.50644957176</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3380,7 +3394,7 @@
         <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>128</v>
@@ -3433,7 +3447,7 @@
         <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>131</v>
@@ -3551,7 +3565,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3569,10 +3583,10 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46195.583877337966</v>
+        <v>46206.5062605787</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3602,7 +3616,7 @@
         <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>140</v>
@@ -3655,7 +3669,7 @@
         <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>143</v>
@@ -3712,7 +3726,7 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3771,7 +3785,7 @@
         <v>46212</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3836,7 +3850,7 @@
         <v>46190</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3859,7 +3873,7 @@
         <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -3901,7 +3915,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -3964,7 +3978,7 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4176,7 +4190,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4239,7 +4253,7 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4302,7 +4316,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4365,7 +4379,7 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4428,7 +4442,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4491,7 +4505,7 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4601,7 +4615,7 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4770,7 +4784,7 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -4939,7 +4953,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5155,13 +5169,13 @@
         <v>46209</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5218,13 +5232,13 @@
         <v>46209</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5269,7 +5283,7 @@
         <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>227</v>
@@ -5281,13 +5295,13 @@
         <v>46209</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5344,7 +5358,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5418,10 +5432,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5454,7 +5468,7 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5481,10 +5495,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5534,10 +5548,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5587,10 +5601,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5623,7 +5637,7 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5650,10 +5664,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5703,10 +5717,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5756,10 +5770,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5790,7 +5804,7 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
@@ -5817,10 +5831,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5868,10 +5882,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5919,10 +5933,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5953,7 +5967,7 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -5980,10 +5994,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6033,10 +6047,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6086,10 +6100,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6120,7 +6134,7 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
@@ -6147,10 +6161,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6200,10 +6214,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6253,10 +6267,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6289,7 +6303,7 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6316,10 +6330,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6369,10 +6383,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6505,7 +6519,7 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6636,10 +6650,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6672,7 +6686,7 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6699,10 +6713,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6752,10 +6766,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6841,7 +6855,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7006,7 +7020,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7218,7 +7232,7 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
@@ -7281,7 +7295,7 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -335,181 +335,181 @@
     <t>Reserva Material,Recepcion motor</t>
   </si>
   <si>
+    <t>1215927804444273</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363</t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215927804444274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215922055649558</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805761393</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215927805772742</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057038280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4363 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4363,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215922057235538</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>1215922057235550</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>1215932734087331</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215932734087348</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805840763</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805840780</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>1215932734105392</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215932734105404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4363 </t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115811</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115828</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215922055649560</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259222</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215927804444273</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363</t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215927804444274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215922055649558</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805761393</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215927805772742</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057038280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4363 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4363,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215922057235538</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>1215922057235550</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>1215932734087331</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215932734087348</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805840763</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805840780</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>1215932734105392</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215932734105404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4363 </t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115811</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115828</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215922055649560</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259222</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
   </si>
   <si>
     <t>1215922057259244</t>
@@ -2708,7 +2708,7 @@
         <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46199.19011668982</v>
+        <v>46207.17694376157</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2752,8 +2752,8 @@
       <c r="R22" s="5">
         <v>46206</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>93</v>
+      <c r="S22" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2773,10 +2773,10 @@
         <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46199.19011649306</v>
+        <v>46207.17694680556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2809,7 +2809,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2817,8 +2817,8 @@
       <c r="R23" s="8">
         <v>46206</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>93</v>
+      <c r="S23" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2838,10 +2838,10 @@
         <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46199.19011700232</v>
+        <v>46207.176943784725</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2874,7 +2874,7 @@
         <v>64</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2882,8 +2882,8 @@
       <c r="R24" s="5">
         <v>46206</v>
       </c>
-      <c r="S24" s="12" t="s">
-        <v>93</v>
+      <c r="S24" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2904,7 +2904,7 @@
         <v>46195.56979528935</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2928,7 +2928,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2951,16 +2951,16 @@
         <v>46195.583322719904</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2978,13 +2978,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2999,12 +2999,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3014,16 +3014,16 @@
         <v>46206.50586751157</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3041,13 +3041,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3058,12 +3058,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3073,16 +3073,16 @@
         <v>46195.58325561343</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3100,13 +3100,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3117,12 +3117,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3132,16 +3132,16 @@
         <v>46195.58349109953</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3159,10 +3159,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3180,12 +3180,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3201,10 +3201,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3222,13 +3222,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3248,16 +3248,16 @@
         <v>46195.583426701385</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3275,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3301,16 +3301,16 @@
         <v>46195.58374949074</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3328,10 +3328,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3349,12 +3349,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3370,10 +3370,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3391,13 +3391,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3417,16 +3417,16 @@
         <v>46195.58357231482</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3444,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3470,16 +3470,16 @@
         <v>46195.58370322917</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3497,10 +3497,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3523,16 +3523,16 @@
         <v>46195.58395704861</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3550,10 +3550,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3571,12 +3571,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3592,10 +3592,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3613,13 +3613,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3639,16 +3639,16 @@
         <v>46195.583909918976</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3666,13 +3666,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3692,7 +3692,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3716,7 +3716,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3743,16 +3743,16 @@
         <v>46205.207856134264</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3770,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3785,7 +3785,7 @@
         <v>46212</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3814,10 +3814,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3835,10 +3835,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>154</v>
@@ -3900,7 +3900,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>153</v>
@@ -3963,7 +3963,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>163</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4178,7 +4178,7 @@
         <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>175</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4217,10 +4217,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>182</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4343,10 +4343,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4430,7 +4430,7 @@
         <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>188</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4469,10 +4469,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4917,10 +4917,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4980,10 +4980,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5033,10 +5033,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5157,7 +5157,7 @@
         <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>222</v>
@@ -5169,7 +5169,7 @@
         <v>46209</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>222</v>
@@ -5232,7 +5232,7 @@
         <v>46209</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5295,7 +5295,7 @@
         <v>46209</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>230</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6140,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6309,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6525,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7238,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3805,7 +3805,7 @@
         <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46198.510531990745</v>
+        <v>46208.70532195602</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3847,7 +3847,7 @@
         <v>46213</v>
       </c>
       <c r="R41" s="8">
-        <v>46190</v>
+        <v>46220</v>
       </c>
       <c r="S41" s="11" t="s">
         <v>77</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46202.17905025463</v>
+        <v>46209.17185111111</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46202.179049768514</v>
+        <v>46209.171852685184</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46202.179049768514</v>
+        <v>46209.17176650463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3296,9 +3296,11 @@
       <c r="B32" s="5">
         <v>46195.53522158565</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46209.61768758102</v>
+      </c>
       <c r="D32" s="5">
-        <v>46195.58374949074</v>
+        <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3346,10 +3348,10 @@
         <v>77</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3359,9 +3361,11 @@
       <c r="B33" s="8">
         <v>46195.53522605324</v>
       </c>
-      <c r="C33" s="9"/>
+      <c r="C33" s="8">
+        <v>46209.617590127316</v>
+      </c>
       <c r="D33" s="8">
-        <v>46206.50644957176</v>
+        <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>86</v>
@@ -3412,9 +3416,11 @@
       <c r="B34" s="5">
         <v>46195.5352309375</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46209.61763306713</v>
+      </c>
       <c r="D34" s="5">
-        <v>46195.58357231482</v>
+        <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3467,7 +3473,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46195.58370322917</v>
+        <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -5313,7 +5319,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.58523106482</v>
+        <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5363,8 +5369,8 @@
       <c r="T67" s="9">
         <v>0</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>106</v>
+      <c r="U67" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -374,16 +374,16 @@
     <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
+    <t>1215927805772742</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215927805772742</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
   </si>
   <si>
     <t>1215922057038280</t>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46195.56979528935</v>
+        <v>46209.82007104167</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2937,7 +2937,9 @@
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
+      <c r="U25" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -2946,9 +2948,11 @@
       <c r="B26" s="5">
         <v>46195.53514152778</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46209.82004709491</v>
+      </c>
       <c r="D26" s="5">
-        <v>46195.583322719904</v>
+        <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -2996,25 +3000,27 @@
         <v>77</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46209.81999097222</v>
+      </c>
       <c r="D27" s="8">
-        <v>46206.50586751157</v>
+        <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3047,7 +3053,7 @@
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3058,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3068,9 +3074,11 @@
       <c r="B28" s="5">
         <v>46195.53519951389</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46209.820031400464</v>
+      </c>
       <c r="D28" s="5">
-        <v>46195.58325561343</v>
+        <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3103,7 +3111,7 @@
         <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>112</v>
@@ -3117,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3127,9 +3135,11 @@
       <c r="B29" s="8">
         <v>46195.535206608794</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46209.82046094908</v>
+      </c>
       <c r="D29" s="8">
-        <v>46195.58349109953</v>
+        <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3177,10 +3187,10 @@
         <v>77</v>
       </c>
       <c r="T29" s="9">
-        <v>0</v>
-      </c>
-      <c r="U29" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3190,9 +3200,11 @@
       <c r="B30" s="5">
         <v>46195.53521144676</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46209.82040699074</v>
+      </c>
       <c r="D30" s="5">
-        <v>46206.50602773148</v>
+        <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>80</v>
@@ -3243,9 +3255,11 @@
       <c r="B31" s="8">
         <v>46195.53521638889</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46209.820448506944</v>
+      </c>
       <c r="D31" s="8">
-        <v>46195.583426701385</v>
+        <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3524,9 +3538,11 @@
       <c r="B36" s="5">
         <v>46195.535239398145</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46209.82157210648</v>
+      </c>
       <c r="D36" s="5">
-        <v>46195.58395704861</v>
+        <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3574,10 +3590,10 @@
         <v>77</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3587,9 +3603,11 @@
       <c r="B37" s="8">
         <v>46195.53524336805</v>
       </c>
-      <c r="C37" s="9"/>
+      <c r="C37" s="8">
+        <v>46209.821492222225</v>
+      </c>
       <c r="D37" s="8">
-        <v>46206.5062605787</v>
+        <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>83</v>
@@ -3640,9 +3658,11 @@
       <c r="B38" s="5">
         <v>46195.53524819444</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46209.821557268515</v>
+      </c>
       <c r="D38" s="5">
-        <v>46195.583909918976</v>
+        <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3990,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4151,7 +4171,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46195.58444471065</v>
+        <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4201,8 +4221,8 @@
       <c r="T47" s="9">
         <v>0</v>
       </c>
-      <c r="U47" s="10" t="s">
-        <v>106</v>
+      <c r="U47" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4265,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4277,7 +4297,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.584441377316</v>
+        <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4327,8 +4347,8 @@
       <c r="T49" s="9">
         <v>0</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>106</v>
+      <c r="U49" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4391,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4403,7 +4423,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46195.584438252314</v>
+        <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4453,8 +4473,8 @@
       <c r="T51" s="9">
         <v>0</v>
       </c>
-      <c r="U51" s="10" t="s">
-        <v>106</v>
+      <c r="U51" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4517,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4627,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4796,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4965,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5480,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5649,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5816,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5979,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6146,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6315,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6531,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6698,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6867,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7032,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7244,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7307,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5150,7 +5150,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46209.17185111111</v>
+        <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5194,8 +5194,8 @@
       <c r="R64" s="5">
         <v>46209</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>151</v>
+      <c r="S64" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46209.171852685184</v>
+        <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5257,8 +5257,8 @@
       <c r="R65" s="8">
         <v>46209</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>151</v>
+      <c r="S65" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46209.17176650463</v>
+        <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5320,8 +5320,8 @@
       <c r="R66" s="5">
         <v>46209</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>151</v>
+      <c r="S66" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.53486788194</v>
+        <v>46195.36820121528</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.84318319445</v>
+        <v>46197.676516527776</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.8432930787</v>
+        <v>46197.67662641204</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.53501399305</v>
+        <v>46195.36834732639</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.8431590625</v>
+        <v>46197.67649239583</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.8431844213</v>
+        <v>46197.67651775463</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.53501732639</v>
+        <v>46195.36835065972</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.84315976852</v>
+        <v>46197.676493101855</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.84318438657</v>
+        <v>46197.67651771991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.53502171296</v>
+        <v>46195.368355046296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.84316024306</v>
+        <v>46197.67649357639</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.84319010416</v>
+        <v>46197.676523437505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.535025543984</v>
+        <v>46195.36835887731</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.84316074074</v>
+        <v>46197.676494074076</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.84318458333</v>
+        <v>46197.67651791667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.534873819444</v>
+        <v>46195.36820715277</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.84431706018</v>
+        <v>46197.67765039352</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.84432748843</v>
+        <v>46197.67766082176</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.53503290509</v>
+        <v>46195.36836623843</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.84418690972</v>
+        <v>46197.67752024306</v>
       </c>
       <c r="D10" s="5">
-        <v>46199.20165502315</v>
+        <v>46199.03498835648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.535038055554</v>
+        <v>46195.36837138889</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.84430075232</v>
+        <v>46197.677634085645</v>
       </c>
       <c r="D11" s="8">
-        <v>46199.201655150464</v>
+        <v>46199.03498848379</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2076,13 +2076,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.53504337963</v>
+        <v>46195.36837671296</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.843900266205</v>
+        <v>46197.677233599534</v>
       </c>
       <c r="D12" s="5">
-        <v>46206.17883685185</v>
+        <v>46206.01217018519</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2141,13 +2141,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.53487891203</v>
+        <v>46195.368212245376</v>
       </c>
       <c r="C13" s="8">
-        <v>46206.50646099537</v>
+        <v>46206.339794328705</v>
       </c>
       <c r="D13" s="8">
-        <v>46206.50647436343</v>
+        <v>46206.33980769676</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2194,13 +2194,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.53505578704</v>
+        <v>46195.36838912037</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.844381840274</v>
+        <v>46197.67771517361</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.19501678241</v>
+        <v>46204.02835011574</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2259,13 +2259,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.535061620365</v>
+        <v>46195.36839495371</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.49930170139</v>
+        <v>46197.33263503472</v>
       </c>
       <c r="D15" s="8">
-        <v>46204.19501679398</v>
+        <v>46204.028350127315</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2324,13 +2324,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.53506689815</v>
+        <v>46195.368400231484</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.49934962963</v>
+        <v>46197.332682962966</v>
       </c>
       <c r="D16" s="5">
-        <v>46204.195016655096</v>
+        <v>46204.028349988424</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2389,13 +2389,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.53507237269</v>
+        <v>46195.368405706016</v>
       </c>
       <c r="C17" s="8">
-        <v>46206.505830497685</v>
+        <v>46206.33916383101</v>
       </c>
       <c r="D17" s="8">
-        <v>46206.50589585648</v>
+        <v>46206.33922918982</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2454,13 +2454,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.535077141205</v>
+        <v>46195.36841047453</v>
       </c>
       <c r="C18" s="5">
-        <v>46206.50602077546</v>
+        <v>46206.3393541088</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.506043506946</v>
+        <v>46206.339376840275</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2519,13 +2519,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.53508107639</v>
+        <v>46195.36841440972</v>
       </c>
       <c r="C19" s="8">
-        <v>46206.50625340278</v>
+        <v>46206.33958673611</v>
       </c>
       <c r="D19" s="8">
-        <v>46206.506269930556</v>
+        <v>46206.339603263885</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>82</v>
@@ -2584,13 +2584,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.535084918985</v>
+        <v>46195.368418252314</v>
       </c>
       <c r="C20" s="5">
-        <v>46206.50644165509</v>
+        <v>46206.339774988424</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.50646081018</v>
+        <v>46206.33979414352</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2649,13 +2649,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.55482737269</v>
+        <v>46195.38816070602</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.50025414352</v>
+        <v>46197.33358747685</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.636544884255</v>
+        <v>46203.46987821759</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2702,13 +2702,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.55503578704</v>
+        <v>46195.38836912037</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.49944752315</v>
+        <v>46197.33278085648</v>
       </c>
       <c r="D22" s="5">
-        <v>46207.17694376157</v>
+        <v>46207.01027709491</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2767,13 +2767,13 @@
         <v>93</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.5550796412</v>
+        <v>46195.38841297454</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.500224166666</v>
+        <v>46197.333557499995</v>
       </c>
       <c r="D23" s="8">
-        <v>46207.17694680556</v>
+        <v>46207.010280138886</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>94</v>
@@ -2832,13 +2832,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.555127037034</v>
+        <v>46195.38846037037</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.50023636574</v>
+        <v>46197.33356969907</v>
       </c>
       <c r="D24" s="5">
-        <v>46207.176943784725</v>
+        <v>46207.01027711805</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2897,11 +2897,11 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.534883761575</v>
+        <v>46195.3682170949</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46209.82007104167</v>
+        <v>46209.653404375</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2946,13 +2946,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.53514152778</v>
+        <v>46195.36847486111</v>
       </c>
       <c r="C26" s="5">
-        <v>46209.82004709491</v>
+        <v>46209.65338042824</v>
       </c>
       <c r="D26" s="5">
-        <v>46209.820063900464</v>
+        <v>46209.65339723379</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -3011,13 +3011,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.535146215276</v>
+        <v>46195.36847954861</v>
       </c>
       <c r="C27" s="8">
-        <v>46209.81999097222</v>
+        <v>46209.65332430556</v>
       </c>
       <c r="D27" s="8">
-        <v>46209.8199925463</v>
+        <v>46209.653325879626</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3072,13 +3072,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.53519951389</v>
+        <v>46195.36853284722</v>
       </c>
       <c r="C28" s="5">
-        <v>46209.820031400464</v>
+        <v>46209.65336473379</v>
       </c>
       <c r="D28" s="5">
-        <v>46209.82003284722</v>
+        <v>46209.65336618056</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3133,13 +3133,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.535206608794</v>
+        <v>46195.36853994213</v>
       </c>
       <c r="C29" s="8">
-        <v>46209.82046094908</v>
+        <v>46209.65379428241</v>
       </c>
       <c r="D29" s="8">
-        <v>46209.82047291667</v>
+        <v>46209.653806250004</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3198,13 +3198,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.53521144676</v>
+        <v>46195.368544780096</v>
       </c>
       <c r="C30" s="5">
-        <v>46209.82040699074</v>
+        <v>46209.65374032407</v>
       </c>
       <c r="D30" s="5">
-        <v>46209.82040827547</v>
+        <v>46209.653741608796</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>80</v>
@@ -3253,13 +3253,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.53521638889</v>
+        <v>46195.36854972222</v>
       </c>
       <c r="C31" s="8">
-        <v>46209.820448506944</v>
+        <v>46209.65378184028</v>
       </c>
       <c r="D31" s="8">
-        <v>46209.82044996528</v>
+        <v>46209.65378329861</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3308,13 +3308,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.53522158565</v>
+        <v>46195.36855491898</v>
       </c>
       <c r="C32" s="5">
-        <v>46209.61768758102</v>
+        <v>46209.45102091435</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.6177050463</v>
+        <v>46209.45103837963</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3373,13 +3373,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.53522605324</v>
+        <v>46195.368559386574</v>
       </c>
       <c r="C33" s="8">
-        <v>46209.617590127316</v>
+        <v>46209.45092346065</v>
       </c>
       <c r="D33" s="8">
-        <v>46209.617592256945</v>
+        <v>46209.45092559028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>86</v>
@@ -3428,13 +3428,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.5352309375</v>
+        <v>46195.36856427083</v>
       </c>
       <c r="C34" s="5">
-        <v>46209.61763306713</v>
+        <v>46209.45096640046</v>
       </c>
       <c r="D34" s="5">
-        <v>46209.61763451389</v>
+        <v>46209.450967847224</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3483,11 +3483,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.53523623843</v>
+        <v>46195.36856957176</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46209.61764521991</v>
+        <v>46209.45097855324</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3536,13 +3536,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.535239398145</v>
+        <v>46195.36857273148</v>
       </c>
       <c r="C36" s="5">
-        <v>46209.82157210648</v>
+        <v>46209.65490543982</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.82158354166</v>
+        <v>46209.654916875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3601,13 +3601,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.53524336805</v>
+        <v>46195.36857670139</v>
       </c>
       <c r="C37" s="8">
-        <v>46209.821492222225</v>
+        <v>46209.65482555555</v>
       </c>
       <c r="D37" s="8">
-        <v>46209.82149362269</v>
+        <v>46209.654826956015</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>83</v>
@@ -3656,13 +3656,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.53524819444</v>
+        <v>46195.36858152778</v>
       </c>
       <c r="C38" s="5">
-        <v>46209.821557268515</v>
+        <v>46209.65489060185</v>
       </c>
       <c r="D38" s="5">
-        <v>46209.82155890046</v>
+        <v>46209.6548922338</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3711,11 +3711,11 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.5348887037</v>
+        <v>46195.36822203704</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.51053421297</v>
+        <v>46198.3438675463</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3760,13 +3760,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.535254629634</v>
+        <v>46195.36858796296</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.51038958333</v>
+        <v>46198.34372291667</v>
       </c>
       <c r="D40" s="5">
-        <v>46205.207856134264</v>
+        <v>46205.04118946759</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3825,13 +3825,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.53526092593</v>
+        <v>46195.36859425926</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.51051443287</v>
+        <v>46198.3438477662</v>
       </c>
       <c r="D41" s="8">
-        <v>46208.70532195602</v>
+        <v>46208.53865528935</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3890,13 +3890,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.53526833333</v>
+        <v>46195.36860166666</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.51056810185</v>
+        <v>46198.34390143519</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.51058418982</v>
+        <v>46198.34391752315</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3955,11 +3955,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.53528606481</v>
+        <v>46195.36861939815</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46195.41768052083</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4018,11 +4018,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.535290266205</v>
+        <v>46195.36862359954</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46195.41763832176</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4069,11 +4069,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.53529509259</v>
+        <v>46195.36862842593</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46195.41763506945</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4120,11 +4120,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.53533827546</v>
+        <v>46195.3686716088</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.572334930555</v>
+        <v>46195.40566826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4167,11 +4167,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.53534217592</v>
+        <v>46195.368675509264</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46209.82004871528</v>
+        <v>46209.65338204861</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4230,11 +4230,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.53534689815</v>
+        <v>46195.36868023148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46195.41788641203</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4293,11 +4293,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.5353533912</v>
+        <v>46195.36868672454</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46209.82046545139</v>
+        <v>46209.653798784726</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4356,11 +4356,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.53535798611</v>
+        <v>46195.36869131944</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46195.41788364583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4419,11 +4419,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.535361689814</v>
+        <v>46195.36869502315</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46209.82157645833</v>
+        <v>46209.654909791665</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4482,11 +4482,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.53536568287</v>
+        <v>46195.3686990162</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46195.41787967592</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4545,11 +4545,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.5353693287</v>
+        <v>46195.36870266203</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46195.40720042824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4592,11 +4592,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.53537232639</v>
+        <v>46195.36870565973</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46195.41815065972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4655,11 +4655,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.53537631944</v>
+        <v>46195.36870965278</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46195.41811395834</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4708,11 +4708,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.53538179398</v>
+        <v>46195.36871512732</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46195.41811086806</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4761,11 +4761,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.53540148148</v>
+        <v>46195.368734814816</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46195.418361759264</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4824,11 +4824,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.53540543982</v>
+        <v>46195.36873877315</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.51058690972</v>
+        <v>46198.34392024306</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4877,11 +4877,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.53541055556</v>
+        <v>46195.36874388889</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.510575162036</v>
+        <v>46198.34390849537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4930,11 +4930,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.535427650466</v>
+        <v>46195.368760983794</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.84290087963</v>
+        <v>46197.676234212966</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4993,11 +4993,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.53543222223</v>
+        <v>46195.368765555555</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.5105765162</v>
+        <v>46198.34390984954</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5046,11 +5046,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.53543761574</v>
+        <v>46195.36877094908</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.51057732639</v>
+        <v>46198.34391065972</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5099,11 +5099,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.53545577546</v>
+        <v>46195.3687891088</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.56789731482</v>
+        <v>46195.401230648145</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5146,11 +5146,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.535458576385</v>
+        <v>46195.36879190972</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46210.20645508102</v>
+        <v>46210.03978841435</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5209,11 +5209,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.535463912034</v>
+        <v>46195.36879724537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46210.206457175926</v>
+        <v>46210.039790509254</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5272,11 +5272,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.53547575232</v>
+        <v>46195.368809085645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46210.20645534722</v>
+        <v>46210.03978868056</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5335,11 +5335,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.53552306713</v>
+        <v>46195.36885640046</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46209.617651782406</v>
+        <v>46209.45098511574</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5398,11 +5398,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.53552899306</v>
+        <v>46195.36886232639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.577845057865</v>
+        <v>46195.41117839121</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5445,11 +5445,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.5355328588</v>
+        <v>46195.36886619213</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46195.418684421296</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5508,11 +5508,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.53554157408</v>
+        <v>46195.368874907406</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46195.41864616898</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5561,11 +5561,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.53554603009</v>
+        <v>46195.36887936342</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46195.418642916666</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5614,11 +5614,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.535563240745</v>
+        <v>46195.36889657407</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46195.4188153588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5677,11 +5677,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.53556773148</v>
+        <v>46195.368901064816</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.51057400463</v>
+        <v>46198.34390733796</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5730,11 +5730,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.53557388889</v>
+        <v>46195.36890722222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.5105778125</v>
+        <v>46198.34391114583</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5783,11 +5783,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.53559528935</v>
+        <v>46195.36892862269</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46195.41893768519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5844,11 +5844,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.53559965278</v>
+        <v>46195.36893298611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.510575740744</v>
+        <v>46198.34390907407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5895,11 +5895,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.53560584491</v>
+        <v>46195.36893917824</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.510587488425</v>
+        <v>46198.34392082176</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5946,11 +5946,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.53562898148</v>
+        <v>46195.36896231482</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46195.41904408565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6007,11 +6007,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.535633541665</v>
+        <v>46195.368966875</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.51057450232</v>
+        <v>46198.343907835646</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6060,11 +6060,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.535639050926</v>
+        <v>46195.368972384254</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51057611111</v>
+        <v>46198.34390944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6113,11 +6113,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.53570565972</v>
+        <v>46195.369038993056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46195.419168946755</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6174,11 +6174,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.535710509255</v>
+        <v>46195.36904384259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46195.41912155093</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6227,11 +6227,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.53571621528</v>
+        <v>46195.36904954861</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46195.4191184375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6280,11 +6280,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.53573584491</v>
+        <v>46195.36906917824</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46195.41929259259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6343,11 +6343,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.53574096065</v>
+        <v>46195.36907429398</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46195.41925020833</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6396,11 +6396,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.53574520833</v>
+        <v>46195.36907854167</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46195.419247233796</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6449,11 +6449,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.53576230324</v>
+        <v>46195.369095636575</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.58073400463</v>
+        <v>46195.41406733796</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6496,11 +6496,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.535766319445</v>
+        <v>46195.36909965277</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46195.419515671296</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6559,11 +6559,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.535772118055</v>
+        <v>46195.36910545139</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46195.41947037037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6610,11 +6610,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.53577681713</v>
+        <v>46195.36911015047</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46195.419467141204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6663,11 +6663,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.535800763886</v>
+        <v>46195.36913409722</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46195.419691539355</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6726,11 +6726,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.53580561343</v>
+        <v>46195.36913894676</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46195.41965655093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6779,11 +6779,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.5358103125</v>
+        <v>46195.36914364583</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46195.419653414356</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6832,11 +6832,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.535868506944</v>
+        <v>46195.36920184028</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46195.4198324537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6895,11 +6895,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.535874293986</v>
+        <v>46195.369207627315</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46195.41979299768</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6946,11 +6946,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.535884780096</v>
+        <v>46195.369218113425</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46195.41979018519</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6997,11 +6997,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.53591063658</v>
+        <v>46195.36924396991</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46195.41997931713</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7060,11 +7060,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.53591612268</v>
+        <v>46195.369249456024</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46195.41993966435</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7111,11 +7111,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.535920254624</v>
+        <v>46195.36925358797</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46195.419936412036</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7162,11 +7162,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.53593680555</v>
+        <v>46195.36927013889</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.58118991899</v>
+        <v>46195.414523252315</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7209,11 +7209,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.535940173606</v>
+        <v>46195.36927350695</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.58682732639</v>
+        <v>46195.42016065972</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7272,11 +7272,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.53594497685</v>
+        <v>46195.36927831019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.58676837963</v>
+        <v>46195.42010171297</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1592,13 +1592,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46195.36820121528</v>
+        <v>46195.53486788194</v>
       </c>
       <c r="C4" s="5">
-        <v>46197.676516527776</v>
+        <v>46197.84318319445</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.67662641204</v>
+        <v>46197.8432930787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1641,13 +1641,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46195.36834732639</v>
+        <v>46195.53501399305</v>
       </c>
       <c r="C5" s="8">
-        <v>46197.67649239583</v>
+        <v>46197.8431590625</v>
       </c>
       <c r="D5" s="8">
-        <v>46197.67651775463</v>
+        <v>46197.8431844213</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1704,13 +1704,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.36835065972</v>
+        <v>46195.53501732639</v>
       </c>
       <c r="C6" s="5">
-        <v>46197.676493101855</v>
+        <v>46197.84315976852</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.67651771991</v>
+        <v>46197.84318438657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1767,13 +1767,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46195.368355046296</v>
+        <v>46195.53502171296</v>
       </c>
       <c r="C7" s="8">
-        <v>46197.67649357639</v>
+        <v>46197.84316024306</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.676523437505</v>
+        <v>46197.84319010416</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1830,13 +1830,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46195.36835887731</v>
+        <v>46195.535025543984</v>
       </c>
       <c r="C8" s="5">
-        <v>46197.676494074076</v>
+        <v>46197.84316074074</v>
       </c>
       <c r="D8" s="5">
-        <v>46197.67651791667</v>
+        <v>46197.84318458333</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -1893,13 +1893,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46195.36820715277</v>
+        <v>46195.534873819444</v>
       </c>
       <c r="C9" s="8">
-        <v>46197.67765039352</v>
+        <v>46197.84431706018</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.67766082176</v>
+        <v>46197.84432748843</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1946,13 +1946,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46195.36836623843</v>
+        <v>46195.53503290509</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.67752024306</v>
+        <v>46197.84418690972</v>
       </c>
       <c r="D10" s="5">
-        <v>46199.03498835648</v>
+        <v>46199.20165502315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2011,13 +2011,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46195.36837138889</v>
+        <v>46195.535038055554</v>
       </c>
       <c r="C11" s="8">
-        <v>46197.677634085645</v>
+        <v>46197.84430075232</v>
       </c>
       <c r="D11" s="8">
-        <v>46199.03498848379</v>
+        <v>46199.201655150464</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2076,13 +2076,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46195.36837671296</v>
+        <v>46195.53504337963</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.677233599534</v>
+        <v>46197.843900266205</v>
       </c>
       <c r="D12" s="5">
-        <v>46206.01217018519</v>
+        <v>46206.17883685185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2141,13 +2141,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46195.368212245376</v>
+        <v>46195.53487891203</v>
       </c>
       <c r="C13" s="8">
-        <v>46206.339794328705</v>
+        <v>46206.50646099537</v>
       </c>
       <c r="D13" s="8">
-        <v>46206.33980769676</v>
+        <v>46206.50647436343</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2194,13 +2194,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46195.36838912037</v>
+        <v>46195.53505578704</v>
       </c>
       <c r="C14" s="5">
-        <v>46197.67771517361</v>
+        <v>46197.844381840274</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.02835011574</v>
+        <v>46204.19501678241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2259,13 +2259,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46195.36839495371</v>
+        <v>46195.535061620365</v>
       </c>
       <c r="C15" s="8">
-        <v>46197.33263503472</v>
+        <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46204.028350127315</v>
+        <v>46204.19501679398</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2324,13 +2324,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46195.368400231484</v>
+        <v>46195.53506689815</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.332682962966</v>
+        <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46204.028349988424</v>
+        <v>46204.195016655096</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2389,13 +2389,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46195.368405706016</v>
+        <v>46195.53507237269</v>
       </c>
       <c r="C17" s="8">
-        <v>46206.33916383101</v>
+        <v>46206.505830497685</v>
       </c>
       <c r="D17" s="8">
-        <v>46206.33922918982</v>
+        <v>46206.50589585648</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2454,13 +2454,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46195.36841047453</v>
+        <v>46195.535077141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46206.3393541088</v>
+        <v>46206.50602077546</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.339376840275</v>
+        <v>46206.506043506946</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2519,13 +2519,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="8">
-        <v>46195.36841440972</v>
+        <v>46195.53508107639</v>
       </c>
       <c r="C19" s="8">
-        <v>46206.33958673611</v>
+        <v>46206.50625340278</v>
       </c>
       <c r="D19" s="8">
-        <v>46206.339603263885</v>
+        <v>46206.506269930556</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>82</v>
@@ -2584,13 +2584,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46195.368418252314</v>
+        <v>46195.535084918985</v>
       </c>
       <c r="C20" s="5">
-        <v>46206.339774988424</v>
+        <v>46206.50644165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.33979414352</v>
+        <v>46206.50646081018</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2649,13 +2649,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46195.38816070602</v>
+        <v>46195.55482737269</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.33358747685</v>
+        <v>46197.50025414352</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.46987821759</v>
+        <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2702,13 +2702,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46195.38836912037</v>
+        <v>46195.55503578704</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.33278085648</v>
+        <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46207.01027709491</v>
+        <v>46207.17694376157</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2767,13 +2767,13 @@
         <v>93</v>
       </c>
       <c r="B23" s="8">
-        <v>46195.38841297454</v>
+        <v>46195.5550796412</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.333557499995</v>
+        <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46207.010280138886</v>
+        <v>46207.17694680556</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>94</v>
@@ -2832,13 +2832,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46195.38846037037</v>
+        <v>46195.555127037034</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.33356969907</v>
+        <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46207.01027711805</v>
+        <v>46207.176943784725</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2897,11 +2897,11 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46195.3682170949</v>
+        <v>46195.534883761575</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46209.653404375</v>
+        <v>46209.82007104167</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2946,13 +2946,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46195.36847486111</v>
+        <v>46195.53514152778</v>
       </c>
       <c r="C26" s="5">
-        <v>46209.65338042824</v>
+        <v>46209.82004709491</v>
       </c>
       <c r="D26" s="5">
-        <v>46209.65339723379</v>
+        <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>101</v>
@@ -3011,13 +3011,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46195.36847954861</v>
+        <v>46195.535146215276</v>
       </c>
       <c r="C27" s="8">
-        <v>46209.65332430556</v>
+        <v>46209.81999097222</v>
       </c>
       <c r="D27" s="8">
-        <v>46209.653325879626</v>
+        <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -3072,13 +3072,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46195.36853284722</v>
+        <v>46195.53519951389</v>
       </c>
       <c r="C28" s="5">
-        <v>46209.65336473379</v>
+        <v>46209.820031400464</v>
       </c>
       <c r="D28" s="5">
-        <v>46209.65336618056</v>
+        <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3133,13 +3133,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46195.36853994213</v>
+        <v>46195.535206608794</v>
       </c>
       <c r="C29" s="8">
-        <v>46209.65379428241</v>
+        <v>46209.82046094908</v>
       </c>
       <c r="D29" s="8">
-        <v>46209.653806250004</v>
+        <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3198,13 +3198,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46195.368544780096</v>
+        <v>46195.53521144676</v>
       </c>
       <c r="C30" s="5">
-        <v>46209.65374032407</v>
+        <v>46209.82040699074</v>
       </c>
       <c r="D30" s="5">
-        <v>46209.653741608796</v>
+        <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>80</v>
@@ -3253,13 +3253,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46195.36854972222</v>
+        <v>46195.53521638889</v>
       </c>
       <c r="C31" s="8">
-        <v>46209.65378184028</v>
+        <v>46209.820448506944</v>
       </c>
       <c r="D31" s="8">
-        <v>46209.65378329861</v>
+        <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3308,13 +3308,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46195.36855491898</v>
+        <v>46195.53522158565</v>
       </c>
       <c r="C32" s="5">
-        <v>46209.45102091435</v>
+        <v>46209.61768758102</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.45103837963</v>
+        <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3373,13 +3373,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46195.368559386574</v>
+        <v>46195.53522605324</v>
       </c>
       <c r="C33" s="8">
-        <v>46209.45092346065</v>
+        <v>46209.617590127316</v>
       </c>
       <c r="D33" s="8">
-        <v>46209.45092559028</v>
+        <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>86</v>
@@ -3428,13 +3428,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46195.36856427083</v>
+        <v>46195.5352309375</v>
       </c>
       <c r="C34" s="5">
-        <v>46209.45096640046</v>
+        <v>46209.61763306713</v>
       </c>
       <c r="D34" s="5">
-        <v>46209.450967847224</v>
+        <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3483,11 +3483,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46195.36856957176</v>
+        <v>46195.53523623843</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46209.45097855324</v>
+        <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3536,13 +3536,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46195.36857273148</v>
+        <v>46195.535239398145</v>
       </c>
       <c r="C36" s="5">
-        <v>46209.65490543982</v>
+        <v>46209.82157210648</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.654916875</v>
+        <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3601,13 +3601,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46195.36857670139</v>
+        <v>46195.53524336805</v>
       </c>
       <c r="C37" s="8">
-        <v>46209.65482555555</v>
+        <v>46209.821492222225</v>
       </c>
       <c r="D37" s="8">
-        <v>46209.654826956015</v>
+        <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>83</v>
@@ -3656,13 +3656,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46195.36858152778</v>
+        <v>46195.53524819444</v>
       </c>
       <c r="C38" s="5">
-        <v>46209.65489060185</v>
+        <v>46209.821557268515</v>
       </c>
       <c r="D38" s="5">
-        <v>46209.6548922338</v>
+        <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3711,11 +3711,11 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46195.36822203704</v>
+        <v>46195.5348887037</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.3438675463</v>
+        <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3760,13 +3760,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46195.36858796296</v>
+        <v>46195.535254629634</v>
       </c>
       <c r="C40" s="5">
-        <v>46198.34372291667</v>
+        <v>46198.51038958333</v>
       </c>
       <c r="D40" s="5">
-        <v>46205.04118946759</v>
+        <v>46205.207856134264</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3825,13 +3825,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46195.36859425926</v>
+        <v>46195.53526092593</v>
       </c>
       <c r="C41" s="8">
-        <v>46198.3438477662</v>
+        <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46208.53865528935</v>
+        <v>46208.70532195602</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3890,13 +3890,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46195.36860166666</v>
+        <v>46195.53526833333</v>
       </c>
       <c r="C42" s="5">
-        <v>46198.34390143519</v>
+        <v>46198.51056810185</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.34391752315</v>
+        <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>75</v>
@@ -3955,11 +3955,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46195.36861939815</v>
+        <v>46195.53528606481</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.41768052083</v>
+        <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4018,11 +4018,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46195.36862359954</v>
+        <v>46195.535290266205</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.41763832176</v>
+        <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4069,11 +4069,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46195.36862842593</v>
+        <v>46195.53529509259</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.41763506945</v>
+        <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4120,11 +4120,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46195.3686716088</v>
+        <v>46195.53533827546</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46195.40566826389</v>
+        <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4167,11 +4167,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46195.368675509264</v>
+        <v>46195.53534217592</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46209.65338204861</v>
+        <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4230,11 +4230,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46195.36868023148</v>
+        <v>46195.53534689815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.41788641203</v>
+        <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4293,11 +4293,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46195.36868672454</v>
+        <v>46195.5353533912</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46209.653798784726</v>
+        <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4356,11 +4356,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46195.36869131944</v>
+        <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.41788364583</v>
+        <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4419,11 +4419,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46195.36869502315</v>
+        <v>46195.535361689814</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46209.654909791665</v>
+        <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4482,11 +4482,11 @@
         <v>189</v>
       </c>
       <c r="B52" s="5">
-        <v>46195.3686990162</v>
+        <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.41787967592</v>
+        <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4545,11 +4545,11 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46195.36870266203</v>
+        <v>46195.5353693287</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.40720042824</v>
+        <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4592,11 +4592,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46195.36870565973</v>
+        <v>46195.53537232639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.41815065972</v>
+        <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4655,11 +4655,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="8">
-        <v>46195.36870965278</v>
+        <v>46195.53537631944</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.41811395834</v>
+        <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4708,11 +4708,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46195.36871512732</v>
+        <v>46195.53538179398</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.41811086806</v>
+        <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4761,11 +4761,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="8">
-        <v>46195.368734814816</v>
+        <v>46195.53540148148</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.418361759264</v>
+        <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4824,11 +4824,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46195.36873877315</v>
+        <v>46195.53540543982</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.34392024306</v>
+        <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4877,11 +4877,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46195.36874388889</v>
+        <v>46195.53541055556</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.34390849537</v>
+        <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4930,11 +4930,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46195.368760983794</v>
+        <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.676234212966</v>
+        <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -4993,11 +4993,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="8">
-        <v>46195.368765555555</v>
+        <v>46195.53543222223</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.34390984954</v>
+        <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5046,11 +5046,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46195.36877094908</v>
+        <v>46195.53543761574</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.34391065972</v>
+        <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5099,11 +5099,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46195.3687891088</v>
+        <v>46195.53545577546</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.401230648145</v>
+        <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5146,11 +5146,11 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46195.36879190972</v>
+        <v>46195.535458576385</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46210.03978841435</v>
+        <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5209,11 +5209,11 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46195.36879724537</v>
+        <v>46195.535463912034</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46210.039790509254</v>
+        <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5272,11 +5272,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46195.368809085645</v>
+        <v>46195.53547575232</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46210.03978868056</v>
+        <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5335,11 +5335,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46195.36885640046</v>
+        <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46209.45098511574</v>
+        <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5398,11 +5398,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46195.36886232639</v>
+        <v>46195.53552899306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.41117839121</v>
+        <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5445,11 +5445,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46195.36886619213</v>
+        <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.418684421296</v>
+        <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5508,11 +5508,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46195.368874907406</v>
+        <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.41864616898</v>
+        <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5561,11 +5561,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46195.36887936342</v>
+        <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.418642916666</v>
+        <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
@@ -5614,11 +5614,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46195.36889657407</v>
+        <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.4188153588</v>
+        <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5677,11 +5677,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46195.368901064816</v>
+        <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.34390733796</v>
+        <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5730,11 +5730,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46195.36890722222</v>
+        <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.34391114583</v>
+        <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -5783,11 +5783,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46195.36892862269</v>
+        <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.41893768519</v>
+        <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5844,11 +5844,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46195.36893298611</v>
+        <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.34390907407</v>
+        <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5895,11 +5895,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46195.36893917824</v>
+        <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.34392082176</v>
+        <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -5946,11 +5946,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46195.36896231482</v>
+        <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.41904408565</v>
+        <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6007,11 +6007,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="8">
-        <v>46195.368966875</v>
+        <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.343907835646</v>
+        <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6060,11 +6060,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46195.368972384254</v>
+        <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34390944445</v>
+        <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6113,11 +6113,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46195.369038993056</v>
+        <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.419168946755</v>
+        <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6174,11 +6174,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46195.36904384259</v>
+        <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.41912155093</v>
+        <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6227,11 +6227,11 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46195.36904954861</v>
+        <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.4191184375</v>
+        <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6280,11 +6280,11 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46195.36906917824</v>
+        <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.41929259259</v>
+        <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6343,11 +6343,11 @@
         <v>265</v>
       </c>
       <c r="B85" s="8">
-        <v>46195.36907429398</v>
+        <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.41925020833</v>
+        <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>165</v>
@@ -6396,11 +6396,11 @@
         <v>267</v>
       </c>
       <c r="B86" s="5">
-        <v>46195.36907854167</v>
+        <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.419247233796</v>
+        <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>165</v>
@@ -6449,11 +6449,11 @@
         <v>268</v>
       </c>
       <c r="B87" s="8">
-        <v>46195.369095636575</v>
+        <v>46195.53576230324</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.41406733796</v>
+        <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6496,11 +6496,11 @@
         <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46195.36909965277</v>
+        <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.419515671296</v>
+        <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6559,11 +6559,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46195.36910545139</v>
+        <v>46195.535772118055</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.41947037037</v>
+        <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>165</v>
@@ -6610,11 +6610,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46195.36911015047</v>
+        <v>46195.53577681713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.419467141204</v>
+        <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>165</v>
@@ -6663,11 +6663,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46195.36913409722</v>
+        <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.419691539355</v>
+        <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6726,11 +6726,11 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46195.36913894676</v>
+        <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.41965655093</v>
+        <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>165</v>
@@ -6779,11 +6779,11 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46195.36914364583</v>
+        <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.419653414356</v>
+        <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>165</v>
@@ -6832,11 +6832,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46195.36920184028</v>
+        <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.4198324537</v>
+        <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6895,11 +6895,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="8">
-        <v>46195.369207627315</v>
+        <v>46195.535874293986</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.41979299768</v>
+        <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>165</v>
@@ -6946,11 +6946,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46195.369218113425</v>
+        <v>46195.535884780096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.41979018519</v>
+        <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>165</v>
@@ -6997,11 +6997,11 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46195.36924396991</v>
+        <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.41997931713</v>
+        <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7060,11 +7060,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46195.369249456024</v>
+        <v>46195.53591612268</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.41993966435</v>
+        <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>165</v>
@@ -7111,11 +7111,11 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46195.36925358797</v>
+        <v>46195.535920254624</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.419936412036</v>
+        <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>165</v>
@@ -7162,11 +7162,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46195.36927013889</v>
+        <v>46195.53593680555</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46195.414523252315</v>
+        <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>296</v>
@@ -7209,11 +7209,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46195.36927350695</v>
+        <v>46195.535940173606</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46195.42016065972</v>
+        <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>299</v>
@@ -7272,11 +7272,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46195.36927831019</v>
+        <v>46195.53594497685</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46195.42010171297</v>
+        <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>303</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -509,16 +509,16 @@
     <t>Ingenieria y diseñoo:,Planos definitivos</t>
   </si>
   <si>
+    <t>1215922057259244</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215922057259244</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
   </si>
   <si>
     <t>1215932734132723</t>
@@ -3766,7 +3766,7 @@
         <v>46198.51038958333</v>
       </c>
       <c r="D40" s="5">
-        <v>46205.207856134264</v>
+        <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3810,8 +3810,8 @@
       <c r="R40" s="5">
         <v>46212</v>
       </c>
-      <c r="S40" s="12" t="s">
-        <v>151</v>
+      <c r="S40" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3831,10 +3831,10 @@
         <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46208.70532195602</v>
+        <v>46213.19847761574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -3867,7 +3867,7 @@
         <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3875,8 +3875,8 @@
       <c r="R41" s="8">
         <v>46220</v>
       </c>
-      <c r="S41" s="11" t="s">
-        <v>77</v>
+      <c r="S41" s="12" t="s">
+        <v>154</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3929,7 +3929,7 @@
         <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>158</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="305">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -119,6 +119,57 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1566 se tienen 2 ventiladores ZVN 1-9-86/2 para Xemortiz (Minas de Oro Nacional):
+    Planos para fabricación O/4363:
+        Ventilador ZVN 1-9-86/2 con motor WEG
+        Alcance: Tobera + Rejilla + Tipo A 900mm
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+    Fecha de entrega: 04-08-2026
+    Términos contractuales / penalidades:
+        Terminación por causa, en caso de incumplimiento de las obligaciones contractuales.
+        Indemnizaciones por retraso, equivalentes al 0.2% diario del valor de la Orden de Compra por atrasos en embarques o entrega de información, así como posibles penalizaciones asociadas al desempeño del suministro.
+ Buen día,
+Para el pedido 1566 se tienen 2 ventiladores ZVN 1-9-86/2 para Xemortiz (Minas de Oro Nacional):
+    Planos para fabricación O/4363:
+        Ventilador ZVN 1-9-86/2 con motor WEG
+        Alcance: Tobera + Rejilla + Tipo A 900mm
+    Selección de Rodete:
+        Rodete de placas s/plano 4999.00
+        Alabe s/ plano 4999.01
+        Z8 N590
+        Código 300000
+        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 86 kW, 2 Polos, FR 250.
+        Código: 350010
+        460 VAC, 60 Hz, IEC-IE3, IP55, FS 1.0.-
+        Se debe considerar duplicado de placas.
+    Fecha de entrega: 04-08-2026
+    Términos contractuales / penalidades:
+        Terminación por causa, en caso de incumplimiento de las obligaciones contractuales.
+        Indemnizaciones por retraso, equivalentes al 0.2% diario del valor de la Orden de Compra por atrasos en embarques o entrega de información, así como posibles penalizaciones asociadas al desempeño del suministro.
+ </t>
   </si>
   <si>
     <t>1215930353728777</t>
@@ -1710,7 +1761,7 @@
         <v>46197.84315976852</v>
       </c>
       <c r="D6" s="5">
-        <v>46197.84318438657</v>
+        <v>46213.76083745371</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1732,7 +1783,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1764,7 +1815,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8">
         <v>46195.53502171296</v>
@@ -1776,7 +1827,7 @@
         <v>46197.84319010416</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -1827,7 +1878,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>46195.535025543984</v>
@@ -1839,7 +1890,7 @@
         <v>46197.84318458333</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1858,7 +1909,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1870,7 +1921,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="5">
         <v>46196</v>
@@ -1890,7 +1941,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="8">
         <v>46195.534873819444</v>
@@ -1902,7 +1953,7 @@
         <v>46197.84432748843</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>25</v>
@@ -1926,7 +1977,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P9" s="9" t="s">
         <v>26</v>
@@ -1943,7 +1994,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5">
         <v>46195.53503290509</v>
@@ -1955,7 +2006,7 @@
         <v>46199.20165502315</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
@@ -1976,19 +2027,19 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q10" s="5">
         <v>46197</v>
@@ -2008,7 +2059,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="8">
         <v>46195.535038055554</v>
@@ -2020,7 +2071,7 @@
         <v>46199.201655150464</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -2041,19 +2092,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="8">
         <v>46197</v>
@@ -2073,7 +2124,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46195.53504337963</v>
@@ -2085,7 +2136,7 @@
         <v>46206.17883685185</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2106,19 +2157,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46197</v>
@@ -2138,7 +2189,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46195.53487891203</v>
@@ -2150,7 +2201,7 @@
         <v>46206.50647436343</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2174,7 +2225,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2191,7 +2242,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46195.53505578704</v>
@@ -2203,7 +2254,7 @@
         <v>46204.19501678241</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2230,13 +2281,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="5">
         <v>46199</v>
@@ -2256,7 +2307,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
         <v>46195.535061620365</v>
@@ -2268,7 +2319,7 @@
         <v>46204.19501679398</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2295,13 +2346,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="8">
         <v>46199</v>
@@ -2316,12 +2367,12 @@
         <v>1</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
@@ -2333,16 +2384,16 @@
         <v>46204.195016655096</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2360,13 +2411,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2381,12 +2432,12 @@
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2398,16 +2449,16 @@
         <v>46206.50589585648</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2425,13 +2476,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2440,7 +2491,7 @@
         <v>46225</v>
       </c>
       <c r="S17" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2451,7 +2502,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2463,16 +2514,16 @@
         <v>46206.506043506946</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2490,13 +2541,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2505,7 +2556,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2516,7 +2567,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2528,16 +2579,16 @@
         <v>46206.506269930556</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2555,13 +2606,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2570,7 +2621,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2581,7 +2632,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2593,16 +2644,16 @@
         <v>46206.50646081018</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2620,13 +2671,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2635,7 +2686,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2646,7 +2697,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2658,7 +2709,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2682,7 +2733,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2699,7 +2750,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2711,16 +2762,16 @@
         <v>46207.17694376157</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2738,13 +2789,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2759,12 +2810,12 @@
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2776,16 +2827,16 @@
         <v>46207.17694680556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2803,13 +2854,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2829,7 +2880,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2841,16 +2892,16 @@
         <v>46207.176943784725</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2868,13 +2919,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2894,7 +2945,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2904,7 +2955,7 @@
         <v>46209.82007104167</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2928,7 +2979,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2938,12 +2989,12 @@
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
       <c r="U25" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2955,16 +3006,16 @@
         <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -2982,13 +3033,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -2997,7 +3048,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3008,7 +3059,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3020,16 +3071,16 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3047,29 +3098,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3081,16 +3132,16 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3108,29 +3159,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3142,16 +3193,16 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3169,10 +3220,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3184,7 +3235,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3195,7 +3246,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3207,16 +3258,16 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3234,13 +3285,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3250,7 +3301,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3262,16 +3313,16 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3289,13 +3340,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3305,7 +3356,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3317,16 +3368,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3344,10 +3395,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3359,7 +3410,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3370,7 +3421,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3382,16 +3433,16 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3409,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3425,7 +3476,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3437,16 +3488,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3464,13 +3515,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3480,7 +3531,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3490,16 +3541,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3517,10 +3568,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3533,7 +3584,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3545,16 +3596,16 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3572,10 +3623,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3587,7 +3638,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3598,7 +3649,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3610,16 +3661,16 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3637,13 +3688,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3653,7 +3704,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3665,16 +3716,16 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3692,13 +3743,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3708,7 +3759,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3718,7 +3769,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3742,7 +3793,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3752,12 +3803,12 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3769,16 +3820,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3796,13 +3847,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3822,7 +3873,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3834,16 +3885,16 @@
         <v>46213.19847761574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3861,13 +3912,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3876,7 +3927,7 @@
         <v>46220</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3887,7 +3938,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3899,16 +3950,16 @@
         <v>46198.51058418982</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3926,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3941,7 +3992,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -3952,7 +4003,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -3962,16 +4013,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -3989,10 +4040,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4004,18 +4055,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4025,16 +4076,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4050,13 +4101,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4066,7 +4117,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4076,16 +4127,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4101,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4117,7 +4168,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4127,7 +4178,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4151,7 +4202,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4164,7 +4215,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4174,16 +4225,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4201,13 +4252,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4216,18 +4267,18 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4237,16 +4288,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4264,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4279,18 +4330,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4300,16 +4351,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4327,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4342,18 +4393,18 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
       </c>
       <c r="U49" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4363,16 +4414,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4390,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4405,18 +4456,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4426,16 +4477,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4453,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4468,18 +4519,18 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4489,16 +4540,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4516,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4531,18 +4582,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4552,7 +4603,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4576,7 +4627,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4589,7 +4640,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4599,16 +4650,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4626,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4641,18 +4692,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4662,16 +4713,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4689,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4705,7 +4756,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4715,16 +4766,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4742,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4758,7 +4809,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4768,16 +4819,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4795,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4810,18 +4861,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4831,16 +4882,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4858,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4874,7 +4925,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4884,16 +4935,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4911,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4927,7 +4978,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4937,16 +4988,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4964,13 +5015,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -4979,18 +5030,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5000,16 +5051,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5027,13 +5078,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5043,7 +5094,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5053,16 +5104,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5080,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5096,7 +5147,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5106,7 +5157,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5130,7 +5181,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5143,7 +5194,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5153,16 +5204,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5180,13 +5231,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5201,12 +5252,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5216,16 +5267,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5243,13 +5294,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5264,12 +5315,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5279,16 +5330,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5306,13 +5357,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5327,12 +5378,12 @@
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5342,16 +5393,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5369,13 +5420,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5384,18 +5435,18 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5405,7 +5456,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5429,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5442,7 +5493,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5452,16 +5503,16 @@
         <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5479,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5494,18 +5545,18 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5515,16 +5566,16 @@
         <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5542,10 +5593,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5558,7 +5609,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5568,16 +5619,16 @@
         <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5595,10 +5646,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5611,7 +5662,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5621,16 +5672,16 @@
         <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5648,13 +5699,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5663,18 +5714,18 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5684,16 +5735,16 @@
         <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5711,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5727,7 +5778,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5737,16 +5788,16 @@
         <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5764,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5780,7 +5831,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5790,16 +5841,16 @@
         <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5815,13 +5866,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5830,18 +5881,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5851,16 +5902,16 @@
         <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5876,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5892,7 +5943,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5902,16 +5953,16 @@
         <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5927,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5943,7 +5994,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -5953,16 +6004,16 @@
         <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5978,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5993,18 +6044,18 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6014,16 +6065,16 @@
         <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6041,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6057,7 +6108,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6067,16 +6118,16 @@
         <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6094,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6110,7 +6161,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6120,16 +6171,16 @@
         <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6145,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6160,18 +6211,18 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6181,16 +6232,16 @@
         <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6208,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6224,7 +6275,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6234,16 +6285,16 @@
         <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6261,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6277,7 +6328,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6287,16 +6338,16 @@
         <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6314,13 +6365,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6329,18 +6380,18 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6350,16 +6401,16 @@
         <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6377,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6393,7 +6444,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6403,16 +6454,16 @@
         <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6430,13 +6481,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6446,7 +6497,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6456,7 +6507,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6480,7 +6531,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6493,7 +6544,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6503,16 +6554,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6530,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6545,18 +6596,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6566,16 +6617,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6591,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6607,7 +6658,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6617,16 +6668,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6644,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6660,7 +6711,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6670,16 +6721,16 @@
         <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6697,13 +6748,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6712,18 +6763,18 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6733,16 +6784,16 @@
         <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6760,13 +6811,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6776,7 +6827,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6786,16 +6837,16 @@
         <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6813,13 +6864,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6829,7 +6880,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6839,16 +6890,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6866,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6881,18 +6932,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6902,16 +6953,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6927,13 +6978,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6943,7 +6994,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -6953,16 +7004,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6978,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6994,7 +7045,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -7004,16 +7055,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7031,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7046,18 +7097,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7067,16 +7118,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7092,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7108,7 +7159,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7118,16 +7169,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7143,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7159,7 +7210,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7169,7 +7220,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7193,7 +7244,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7206,7 +7257,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7216,16 +7267,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7243,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7258,18 +7309,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7279,7 +7330,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7306,13 +7357,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7321,13 +7372,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3947,7 +3947,7 @@
         <v>46198.51056810185</v>
       </c>
       <c r="D42" s="5">
-        <v>46198.51058418982</v>
+        <v>46216.191581562496</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>76</v>
@@ -3991,8 +3991,8 @@
       <c r="R42" s="5">
         <v>46223</v>
       </c>
-      <c r="S42" s="11" t="s">
-        <v>78</v>
+      <c r="S42" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -338,93 +338,96 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1215922057135204</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057135216</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215930353764509</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363</t>
+  </si>
+  <si>
+    <t>1215927804444266</t>
+  </si>
+  <si>
+    <t>Reserva Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>1215927804444272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215927804444273</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363</t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215927804444274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215922055649558</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805761393</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
-    <t>1215922057135204</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057135216</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215930353764509</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363</t>
-  </si>
-  <si>
-    <t>1215927804444266</t>
-  </si>
-  <si>
-    <t>Reserva Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>1215927804444272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215927804444273</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363</t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215927804444274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215922055649558</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805761393</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
     <t>1215927805772742</t>
   </si>
   <si>
@@ -567,9 +570,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215932734132723</t>
@@ -2446,7 +2446,7 @@
         <v>46206.505830497685</v>
       </c>
       <c r="D17" s="8">
-        <v>46206.50589585648</v>
+        <v>46218.171986932866</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>73</v>
@@ -2490,7 +2490,7 @@
       <c r="R17" s="8">
         <v>46225</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="S17" s="12" t="s">
         <v>78</v>
       </c>
       <c r="T17" s="9">
@@ -2511,7 +2511,7 @@
         <v>46206.50602077546</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.506043506946</v>
+        <v>46218.17198626157</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2555,7 +2555,7 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="S18" s="12" t="s">
         <v>78</v>
       </c>
       <c r="T18" s="6">
@@ -2576,7 +2576,7 @@
         <v>46206.50625340278</v>
       </c>
       <c r="D19" s="8">
-        <v>46206.506269930556</v>
+        <v>46218.17198559028</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2620,7 +2620,7 @@
       <c r="R19" s="8">
         <v>46225</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="S19" s="12" t="s">
         <v>78</v>
       </c>
       <c r="T19" s="9">
@@ -2641,7 +2641,7 @@
         <v>46206.50644165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.50646081018</v>
+        <v>46218.17199200232</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2685,7 +2685,7 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="11" t="s">
+      <c r="S20" s="12" t="s">
         <v>78</v>
       </c>
       <c r="T20" s="6">
@@ -3048,7 +3048,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3059,7 +3059,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3071,7 +3071,7 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3104,23 +3104,23 @@
         <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3132,7 +3132,7 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3162,26 +3162,26 @@
         <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3193,7 +3193,7 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3223,7 +3223,7 @@
         <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3235,7 +3235,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3285,13 +3285,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3313,7 +3313,7 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3340,13 +3340,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3368,16 +3368,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3398,7 +3398,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3410,7 +3410,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3439,10 +3439,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3460,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3488,16 +3488,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3515,13 +3515,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3541,16 +3541,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3568,10 +3568,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3596,7 +3596,7 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3626,7 +3626,7 @@
         <v>101</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3638,7 +3638,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3688,13 +3688,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3716,7 +3716,7 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3743,13 +3743,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3769,7 +3769,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3793,7 +3793,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3820,16 +3820,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3847,13 +3847,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3885,16 +3885,16 @@
         <v>46213.19847761574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3912,13 +3912,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3927,7 +3927,7 @@
         <v>46220</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3977,10 +3977,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>159</v>
@@ -3992,7 +3992,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4040,7 +4040,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>164</v>
@@ -4055,13 +4055,13 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4255,7 +4255,7 @@
         <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>176</v>
@@ -4267,7 +4267,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4294,10 +4294,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4330,13 +4330,13 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4381,7 +4381,7 @@
         <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>183</v>
@@ -4393,7 +4393,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4420,10 +4420,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4456,13 +4456,13 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4507,7 +4507,7 @@
         <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>189</v>
@@ -4519,7 +4519,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4546,10 +4546,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4582,13 +4582,13 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4692,13 +4692,13 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4861,13 +4861,13 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4994,10 +4994,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5030,13 +5030,13 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5057,10 +5057,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5110,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5423,7 +5423,7 @@
         <v>170</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>231</v>
@@ -5435,7 +5435,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5545,13 +5545,13 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5714,13 +5714,13 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5881,13 +5881,13 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6044,13 +6044,13 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,13 +6211,13 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6380,13 +6380,13 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6596,13 +6596,13 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6763,13 +6763,13 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6932,13 +6932,13 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7097,13 +7097,13 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7309,13 +7309,13 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7372,13 +7372,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="302">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -314,9 +314,6 @@
     <t>propuesta nucleo rodeteOT 4363</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Reserva rodete  OT 4363,Propuesta compras:</t>
   </si>
   <si>
@@ -324,12 +321,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2390,11 +2381,9 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H16" s="6"/>
       <c r="I16" s="5">
         <v>46199</v>
       </c>
@@ -2417,7 +2406,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2437,7 +2426,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2449,17 +2438,15 @@
         <v>46218.171986932866</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="8">
         <v>46224</v>
       </c>
@@ -2479,10 +2466,10 @@
         <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2491,7 +2478,7 @@
         <v>46225</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2502,7 +2489,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2514,17 +2501,15 @@
         <v>46218.17198626157</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46224</v>
       </c>
@@ -2544,10 +2529,10 @@
         <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2556,7 +2541,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2567,7 +2552,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2579,17 +2564,15 @@
         <v>46218.17198559028</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46224</v>
       </c>
@@ -2609,10 +2592,10 @@
         <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2621,7 +2604,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2632,7 +2615,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2644,17 +2627,15 @@
         <v>46218.17199200232</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46224</v>
       </c>
@@ -2674,10 +2655,10 @@
         <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2686,7 +2667,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2697,7 +2678,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2709,7 +2690,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2733,7 +2714,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2750,7 +2731,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2762,17 +2743,15 @@
         <v>46207.17694376157</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46204</v>
       </c>
@@ -2789,13 +2768,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2815,7 +2794,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2827,17 +2806,15 @@
         <v>46207.17694680556</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46204</v>
       </c>
@@ -2854,13 +2831,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2880,7 +2857,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2892,17 +2869,15 @@
         <v>46207.176943784725</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46204</v>
       </c>
@@ -2919,13 +2894,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2945,7 +2920,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2955,7 +2930,7 @@
         <v>46209.82007104167</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2979,7 +2954,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2994,7 +2969,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -3006,16 +2981,16 @@
         <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -3033,13 +3008,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -3048,7 +3023,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3059,7 +3034,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3071,16 +3046,16 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3098,29 +3073,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3132,16 +3107,16 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3159,29 +3134,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3193,16 +3168,16 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3220,10 +3195,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3235,7 +3210,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3246,7 +3221,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3258,16 +3233,16 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3285,13 +3260,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3301,7 +3276,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3313,16 +3288,16 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3340,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3356,7 +3331,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3368,16 +3343,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3395,10 +3370,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3410,7 +3385,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3421,7 +3396,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3433,16 +3408,16 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3460,13 +3435,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3476,7 +3451,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3488,16 +3463,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3515,13 +3490,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3531,7 +3506,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3541,16 +3516,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3568,10 +3543,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3584,7 +3559,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3596,16 +3571,16 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3623,10 +3598,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3638,7 +3613,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3649,7 +3624,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3661,16 +3636,16 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3688,13 +3663,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3704,7 +3679,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3716,16 +3691,16 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3743,13 +3718,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3759,7 +3734,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3769,7 +3744,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3793,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3808,7 +3783,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3820,16 +3795,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3847,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3873,7 +3848,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3885,16 +3860,16 @@
         <v>46213.19847761574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3912,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>149</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3927,7 +3902,7 @@
         <v>46220</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3938,7 +3913,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3950,16 +3925,16 @@
         <v>46216.191581562496</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3977,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3992,7 +3967,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4003,7 +3978,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4013,16 +3988,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4040,10 +4015,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4055,18 +4030,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4076,16 +4051,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4101,13 +4076,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4117,7 +4092,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4127,16 +4102,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4152,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4168,7 +4143,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4178,7 +4153,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4202,7 +4177,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4215,7 +4190,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4225,16 +4200,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4252,13 +4227,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4267,7 +4242,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4278,7 +4253,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4288,16 +4263,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4315,13 +4290,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4330,18 +4305,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4351,16 +4326,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4378,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4393,7 +4368,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4404,7 +4379,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4414,16 +4389,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4441,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4456,18 +4431,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4477,16 +4452,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4504,13 +4479,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4519,7 +4494,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4530,7 +4505,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4540,16 +4515,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4567,13 +4542,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4582,18 +4557,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4603,7 +4578,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4627,7 +4602,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4640,7 +4615,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4650,16 +4625,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4677,13 +4652,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4692,18 +4667,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4713,16 +4688,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4740,13 +4715,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4756,7 +4731,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4766,16 +4741,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4793,13 +4768,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4809,7 +4784,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4819,16 +4794,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4846,13 +4821,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4861,18 +4836,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4882,16 +4857,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4909,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4925,7 +4900,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4935,16 +4910,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4962,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4978,7 +4953,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4988,16 +4963,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5015,13 +4990,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5030,18 +5005,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5051,16 +5026,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5078,13 +5053,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5094,7 +5069,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5104,16 +5079,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5131,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5147,7 +5122,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5157,7 +5132,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5181,7 +5156,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5194,7 +5169,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5204,16 +5179,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5231,13 +5206,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5257,7 +5232,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5267,16 +5242,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5294,13 +5269,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5320,7 +5295,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5330,16 +5305,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5357,13 +5332,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5383,7 +5358,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5393,16 +5368,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5420,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5435,7 +5410,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5446,7 +5421,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5456,7 +5431,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5480,7 +5455,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5493,7 +5468,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5503,17 +5478,15 @@
         <v>46195.58535108797</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="8">
         <v>46258</v>
       </c>
@@ -5530,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5545,18 +5518,18 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5566,17 +5539,15 @@
         <v>46195.58531283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="5">
         <v>46258</v>
       </c>
@@ -5593,10 +5564,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5609,7 +5580,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5619,17 +5590,15 @@
         <v>46195.58530958333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="9"/>
       <c r="I71" s="8">
         <v>46258</v>
       </c>
@@ -5646,10 +5615,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="O71" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5662,7 +5631,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5672,17 +5641,15 @@
         <v>46195.58548202546</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
       <c r="I72" s="5">
         <v>46265</v>
       </c>
@@ -5699,13 +5666,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5714,18 +5681,18 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5735,17 +5702,15 @@
         <v>46198.51057400463</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46265</v>
       </c>
@@ -5762,13 +5727,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5778,7 +5743,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5788,17 +5753,15 @@
         <v>46198.5105778125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
       <c r="I74" s="5">
         <v>46265</v>
       </c>
@@ -5815,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5831,7 +5794,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5841,17 +5804,15 @@
         <v>46195.58560435185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="9"/>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
         <v>46266</v>
@@ -5866,13 +5827,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5881,18 +5842,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5902,17 +5863,15 @@
         <v>46198.510575740744</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
         <v>46266</v>
@@ -5927,13 +5886,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5943,7 +5902,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5953,17 +5912,15 @@
         <v>46198.510587488425</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
         <v>46266</v>
@@ -5978,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5994,7 +5951,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -6004,17 +5961,15 @@
         <v>46195.58571075232</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
         <v>46267</v>
@@ -6029,13 +5984,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6044,18 +5999,18 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6065,17 +6020,15 @@
         <v>46198.51057450232</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8">
         <v>46267</v>
       </c>
@@ -6092,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6108,7 +6061,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6118,17 +6071,15 @@
         <v>46198.51057611111</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46267</v>
       </c>
@@ -6145,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6161,7 +6112,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6171,17 +6122,15 @@
         <v>46195.58583561343</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="9"/>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
         <v>46268</v>
@@ -6196,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6211,18 +6160,18 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6232,17 +6181,15 @@
         <v>46195.58578821759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46268</v>
       </c>
@@ -6259,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6275,7 +6222,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6285,17 +6232,15 @@
         <v>46195.585785104166</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="9"/>
       <c r="I83" s="8">
         <v>46268</v>
       </c>
@@ -6312,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6328,7 +6273,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6338,17 +6283,15 @@
         <v>46195.58595925926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46272</v>
       </c>
@@ -6365,13 +6308,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6380,18 +6323,18 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6401,17 +6344,15 @@
         <v>46195.585916875</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="9"/>
       <c r="I85" s="8">
         <v>46272</v>
       </c>
@@ -6428,13 +6369,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="P85" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6444,7 +6385,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6454,17 +6395,15 @@
         <v>46195.58591390046</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46272</v>
       </c>
@@ -6481,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6497,7 +6436,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6507,7 +6446,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6531,7 +6470,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6544,7 +6483,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6554,16 +6493,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6581,13 +6520,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6596,18 +6535,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6617,16 +6556,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6642,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6658,7 +6597,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6668,16 +6607,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6695,13 +6634,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6711,7 +6650,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6721,17 +6660,15 @@
         <v>46195.58635820602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46274</v>
       </c>
@@ -6748,13 +6685,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6763,18 +6700,18 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6784,17 +6721,15 @@
         <v>46195.58632321759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46274</v>
       </c>
@@ -6811,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6827,7 +6762,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6837,17 +6772,15 @@
         <v>46195.58632008102</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46274</v>
       </c>
@@ -6864,13 +6797,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6880,7 +6813,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6890,16 +6823,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6917,13 +6850,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6932,18 +6865,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6953,16 +6886,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6978,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6994,7 +6927,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -7004,16 +6937,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7029,13 +6962,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7045,7 +6978,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -7055,16 +6988,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7082,13 +7015,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7097,18 +7030,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7118,16 +7051,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7143,13 +7076,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7159,7 +7092,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7169,16 +7102,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7194,13 +7127,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7210,7 +7143,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7220,7 +7153,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7244,7 +7177,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7257,7 +7190,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7267,16 +7200,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7294,13 +7227,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7309,18 +7242,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7330,7 +7263,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7357,13 +7290,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7372,13 +7305,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3857,7 +3857,7 @@
         <v>46198.51051443287</v>
       </c>
       <c r="D41" s="8">
-        <v>46213.19847761574</v>
+        <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3901,8 +3901,8 @@
       <c r="R41" s="8">
         <v>46220</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>75</v>
+      <c r="S41" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="303">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Reserva rodete  OT 4363,Propuesta compras:</t>
@@ -2372,7 +2375,7 @@
         <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46204.195016655096</v>
+        <v>46223.56229649305</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2381,9 +2384,11 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I16" s="5">
         <v>46199</v>
       </c>
@@ -2406,7 +2411,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2426,7 +2431,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2435,18 +2440,20 @@
         <v>46206.505830497685</v>
       </c>
       <c r="D17" s="8">
-        <v>46218.171986932866</v>
+        <v>46223.562293043986</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I17" s="8">
         <v>46224</v>
       </c>
@@ -2466,10 +2473,10 @@
         <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2478,7 +2485,7 @@
         <v>46225</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2489,7 +2496,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2498,18 +2505,20 @@
         <v>46206.50602077546</v>
       </c>
       <c r="D18" s="5">
-        <v>46218.17198626157</v>
+        <v>46223.562289733796</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I18" s="5">
         <v>46224</v>
       </c>
@@ -2529,10 +2538,10 @@
         <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2541,7 +2550,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2552,7 +2561,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2561,18 +2570,20 @@
         <v>46206.50625340278</v>
       </c>
       <c r="D19" s="8">
-        <v>46218.17198559028</v>
+        <v>46223.562286712964</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I19" s="8">
         <v>46224</v>
       </c>
@@ -2592,10 +2603,10 @@
         <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2604,7 +2615,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2615,7 +2626,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2624,18 +2635,20 @@
         <v>46206.50644165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46218.17199200232</v>
+        <v>46223.562281875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I20" s="5">
         <v>46224</v>
       </c>
@@ -2655,10 +2668,10 @@
         <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2667,7 +2680,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2678,7 +2691,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2690,7 +2703,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2714,7 +2727,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2731,7 +2744,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2740,18 +2753,20 @@
         <v>46197.49944752315</v>
       </c>
       <c r="D22" s="5">
-        <v>46207.17694376157</v>
+        <v>46223.56236976852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I22" s="5">
         <v>46204</v>
       </c>
@@ -2768,13 +2783,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2794,7 +2809,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2803,18 +2818,20 @@
         <v>46197.500224166666</v>
       </c>
       <c r="D23" s="8">
-        <v>46207.17694680556</v>
+        <v>46223.56236577546</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I23" s="8">
         <v>46204</v>
       </c>
@@ -2831,13 +2848,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2857,7 +2874,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2866,18 +2883,20 @@
         <v>46197.50023636574</v>
       </c>
       <c r="D24" s="5">
-        <v>46207.176943784725</v>
+        <v>46223.56236157408</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I24" s="5">
         <v>46204</v>
       </c>
@@ -2894,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2920,7 +2939,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2930,7 +2949,7 @@
         <v>46209.82007104167</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2954,7 +2973,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2969,7 +2988,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -2981,16 +3000,16 @@
         <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -3008,13 +3027,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -3023,7 +3042,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3034,7 +3053,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3046,16 +3065,16 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3073,29 +3092,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3107,16 +3126,16 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3134,29 +3153,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3168,16 +3187,16 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3195,10 +3214,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3210,7 +3229,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3221,7 +3240,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3233,16 +3252,16 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3260,13 +3279,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3276,7 +3295,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3288,16 +3307,16 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3315,13 +3334,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3331,7 +3350,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3343,16 +3362,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3370,10 +3389,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3385,7 +3404,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3396,7 +3415,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3408,16 +3427,16 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3435,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3451,7 +3470,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3463,16 +3482,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3490,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3506,7 +3525,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3516,16 +3535,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3543,10 +3562,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3559,7 +3578,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3571,16 +3590,16 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3598,10 +3617,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3613,7 +3632,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3624,7 +3643,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3636,16 +3655,16 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3663,13 +3682,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3679,7 +3698,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3691,16 +3710,16 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3718,13 +3737,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3734,7 +3753,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3744,7 +3763,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3768,7 +3787,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3783,7 +3802,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3795,16 +3814,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3822,13 +3841,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3848,7 +3867,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3860,16 +3879,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3887,13 +3906,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3913,7 +3932,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3925,16 +3944,16 @@
         <v>46216.191581562496</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3952,13 +3971,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -3967,7 +3986,7 @@
         <v>46223</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -3978,7 +3997,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -3988,16 +4007,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4015,10 +4034,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4030,18 +4049,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4051,16 +4070,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4076,13 +4095,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4092,7 +4111,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4102,16 +4121,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4127,13 +4146,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4143,7 +4162,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4153,7 +4172,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4177,7 +4196,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4190,7 +4209,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4200,16 +4219,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4227,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4242,7 +4261,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4253,7 +4272,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4263,16 +4282,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4290,13 +4309,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4305,18 +4324,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4326,16 +4345,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4353,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4368,7 +4387,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4379,7 +4398,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4389,16 +4408,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4416,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4431,18 +4450,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4452,16 +4471,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4479,13 +4498,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4494,7 +4513,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4505,7 +4524,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4515,16 +4534,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4542,13 +4561,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4557,18 +4576,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4578,7 +4597,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4602,7 +4621,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4615,7 +4634,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4625,16 +4644,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4652,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4667,18 +4686,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4688,16 +4707,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4715,13 +4734,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4731,7 +4750,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4741,16 +4760,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4768,13 +4787,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4784,7 +4803,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4794,16 +4813,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4821,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4836,18 +4855,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4857,16 +4876,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4884,13 +4903,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4900,7 +4919,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4910,16 +4929,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4937,13 +4956,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4953,7 +4972,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4963,16 +4982,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -4990,13 +5009,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5005,18 +5024,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5026,16 +5045,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5053,13 +5072,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5069,7 +5088,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5079,16 +5098,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5106,13 +5125,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5122,7 +5141,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5132,7 +5151,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5156,7 +5175,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5169,7 +5188,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5179,16 +5198,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5206,13 +5225,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5232,7 +5251,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5242,16 +5261,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5269,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5295,7 +5314,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5305,16 +5324,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5332,13 +5351,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5358,7 +5377,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5368,16 +5387,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5395,13 +5414,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5410,7 +5429,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5421,7 +5440,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5431,7 +5450,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5455,7 +5474,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5468,25 +5487,27 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.58535108797</v>
+        <v>46223.5631783912</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I69" s="8">
         <v>46258</v>
       </c>
@@ -5503,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5518,36 +5539,38 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46195.58531283565</v>
+        <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I70" s="5">
         <v>46258</v>
       </c>
@@ -5564,10 +5587,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5580,25 +5603,27 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46195.58530958333</v>
+        <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I71" s="8">
         <v>46258</v>
       </c>
@@ -5615,10 +5640,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5631,25 +5656,27 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.58548202546</v>
+        <v>46223.56317771991</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I72" s="5">
         <v>46265</v>
       </c>
@@ -5666,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5681,36 +5708,38 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.51057400463</v>
+        <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I73" s="8">
         <v>46265</v>
       </c>
@@ -5727,13 +5756,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5743,25 +5772,27 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.5105778125</v>
+        <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I74" s="5">
         <v>46265</v>
       </c>
@@ -5778,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5794,25 +5825,27 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46195.58560435185</v>
+        <v>46223.56317686343</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
         <v>46266</v>
@@ -5827,13 +5860,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5842,36 +5875,38 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.510575740744</v>
+        <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
         <v>46266</v>
@@ -5886,13 +5921,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5902,25 +5937,27 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.510587488425</v>
+        <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
         <v>46266</v>
@@ -5935,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5951,25 +5988,27 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.58571075232</v>
+        <v>46223.56317608796</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
         <v>46267</v>
@@ -5984,13 +6023,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -5999,36 +6038,38 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.51057450232</v>
+        <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I79" s="8">
         <v>46267</v>
       </c>
@@ -6045,13 +6086,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6061,25 +6102,27 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51057611111</v>
+        <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I80" s="5">
         <v>46267</v>
       </c>
@@ -6096,13 +6139,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6112,25 +6155,27 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46195.58583561343</v>
+        <v>46223.56317537037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
         <v>46268</v>
@@ -6145,13 +6190,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6160,36 +6205,38 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.58578821759</v>
+        <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I82" s="5">
         <v>46268</v>
       </c>
@@ -6206,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6222,25 +6269,27 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.585785104166</v>
+        <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I83" s="8">
         <v>46268</v>
       </c>
@@ -6257,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6273,25 +6322,27 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46195.58595925926</v>
+        <v>46223.563174641204</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I84" s="5">
         <v>46272</v>
       </c>
@@ -6308,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6323,36 +6374,38 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.585916875</v>
+        <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I85" s="8">
         <v>46272</v>
       </c>
@@ -6369,13 +6422,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6385,25 +6438,27 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.58591390046</v>
+        <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I86" s="5">
         <v>46272</v>
       </c>
@@ -6420,13 +6475,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6436,7 +6491,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6446,7 +6501,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6470,7 +6525,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6483,7 +6538,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6493,16 +6548,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6520,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6535,18 +6590,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6556,16 +6611,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6581,13 +6636,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6597,7 +6652,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6607,16 +6662,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6634,13 +6689,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6650,25 +6705,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.58635820602</v>
+        <v>46223.563337430554</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I91" s="8">
         <v>46274</v>
       </c>
@@ -6685,13 +6742,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6700,36 +6757,38 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46195.58632321759</v>
+        <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="I92" s="5">
         <v>46274</v>
       </c>
@@ -6746,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6762,25 +6821,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46195.58632008102</v>
+        <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="I93" s="8">
         <v>46274</v>
       </c>
@@ -6797,13 +6858,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6813,7 +6874,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6823,16 +6884,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6850,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6865,18 +6926,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6886,16 +6947,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6911,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6927,7 +6988,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -6937,16 +6998,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -6962,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6978,7 +7039,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -6988,16 +7049,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7015,13 +7076,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7030,18 +7091,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7051,16 +7112,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7076,13 +7137,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7092,7 +7153,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7102,16 +7163,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7127,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7143,7 +7204,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7153,7 +7214,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7177,7 +7238,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7190,7 +7251,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7200,16 +7261,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7227,13 +7288,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7242,18 +7303,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7263,7 +7324,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7290,13 +7351,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7305,13 +7366,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3941,7 +3941,7 @@
         <v>46198.51056810185</v>
       </c>
       <c r="D42" s="5">
-        <v>46216.191581562496</v>
+        <v>46224.2078484375</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>74</v>
@@ -3985,8 +3985,8 @@
       <c r="R42" s="5">
         <v>46223</v>
       </c>
-      <c r="S42" s="12" t="s">
-        <v>76</v>
+      <c r="S42" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -2944,9 +2944,11 @@
       <c r="B25" s="8">
         <v>46195.534883761575</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46224.832077025465</v>
+      </c>
       <c r="D25" s="8">
-        <v>46209.82007104167</v>
+        <v>46224.83209384259</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2981,9 +2983,11 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="12" t="s">
-        <v>67</v>
+      <c r="T25" s="9">
+        <v>1</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2387,7 +2390,7 @@
         <v>70</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2411,7 +2414,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2431,7 +2434,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2443,7 +2446,7 @@
         <v>46223.562293043986</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2452,7 +2455,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2473,10 +2476,10 @@
         <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2485,7 +2488,7 @@
         <v>46225</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2496,7 +2499,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2508,7 +2511,7 @@
         <v>46223.562289733796</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2517,7 +2520,7 @@
         <v>70</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2538,10 +2541,10 @@
         <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2550,7 +2553,7 @@
         <v>46225</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2561,7 +2564,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2573,7 +2576,7 @@
         <v>46223.562286712964</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2582,7 +2585,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2603,10 +2606,10 @@
         <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2615,7 +2618,7 @@
         <v>46225</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2626,7 +2629,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2638,7 +2641,7 @@
         <v>46223.562281875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2647,7 +2650,7 @@
         <v>70</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2668,10 +2671,10 @@
         <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2680,7 +2683,7 @@
         <v>46225</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2691,7 +2694,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2703,7 +2706,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2727,7 +2730,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2744,7 +2747,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2756,7 +2759,7 @@
         <v>46223.56236976852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2765,7 +2768,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2783,13 +2786,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2809,7 +2812,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2821,7 +2824,7 @@
         <v>46223.56236577546</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2830,7 +2833,7 @@
         <v>70</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2848,13 +2851,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2874,7 +2877,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2886,7 +2889,7 @@
         <v>46223.56236157408</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2895,7 +2898,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2913,13 +2916,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2939,7 +2942,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2951,7 +2954,7 @@
         <v>46224.83209384259</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2975,7 +2978,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2992,7 +2995,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -3004,16 +3007,16 @@
         <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -3031,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -3046,7 +3049,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3057,7 +3060,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3069,16 +3072,16 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3096,29 +3099,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3130,16 +3133,16 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3157,29 +3160,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3191,16 +3194,16 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3218,10 +3221,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3233,7 +3236,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3244,7 +3247,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3256,16 +3259,16 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3283,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3299,7 +3302,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3311,16 +3314,16 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3338,13 +3341,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3354,7 +3357,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3366,16 +3369,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3393,10 +3396,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3408,7 +3411,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3419,7 +3422,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3431,16 +3434,16 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3458,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3474,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3486,16 +3489,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3513,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3529,7 +3532,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3539,16 +3542,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3566,10 +3569,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3582,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3594,16 +3597,16 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3621,10 +3624,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3636,7 +3639,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3659,16 +3662,16 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3686,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3714,16 +3717,16 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3741,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3757,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3767,7 +3770,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3791,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3806,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3818,16 +3821,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3845,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3871,7 +3874,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3883,16 +3886,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3910,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3948,16 +3951,16 @@
         <v>46224.2078484375</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3975,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4001,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4011,16 +4014,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4038,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4053,18 +4056,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4074,16 +4077,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4099,13 +4102,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4115,7 +4118,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4125,16 +4128,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4150,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4166,7 +4169,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4176,7 +4179,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4200,7 +4203,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4213,7 +4216,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4223,16 +4226,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4265,7 +4268,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4286,16 +4289,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4328,18 +4331,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4349,16 +4352,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4376,13 +4379,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4391,7 +4394,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4402,7 +4405,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4412,16 +4415,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4439,13 +4442,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4454,18 +4457,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4475,16 +4478,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4502,13 +4505,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4517,7 +4520,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4528,7 +4531,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4538,16 +4541,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4565,13 +4568,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4580,18 +4583,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4601,7 +4604,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4625,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4648,16 +4651,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4675,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4690,18 +4693,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4711,16 +4714,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4738,13 +4741,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4754,7 +4757,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4764,16 +4767,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4791,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4807,7 +4810,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4817,16 +4820,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4844,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4859,18 +4862,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4880,16 +4883,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4907,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4923,7 +4926,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4933,16 +4936,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4960,13 +4963,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4976,7 +4979,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4986,16 +4989,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5013,13 +5016,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5028,18 +5031,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5049,16 +5052,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5076,13 +5079,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5102,16 +5105,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5129,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5145,7 +5148,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5155,7 +5158,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5179,7 +5182,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5192,7 +5195,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5202,16 +5205,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5229,13 +5232,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5255,7 +5258,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5265,16 +5268,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5292,13 +5295,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5318,7 +5321,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5328,16 +5331,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5355,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5381,7 +5384,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5391,16 +5394,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5418,13 +5421,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5433,7 +5436,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5444,7 +5447,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5454,7 +5457,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5478,7 +5481,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5501,7 +5504,7 @@
         <v>46223.5631783912</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5510,7 +5513,7 @@
         <v>70</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5528,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5543,18 +5546,18 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5564,7 +5567,7 @@
         <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5573,7 +5576,7 @@
         <v>70</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5591,10 +5594,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5607,7 +5610,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5617,7 +5620,7 @@
         <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5626,7 +5629,7 @@
         <v>70</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5644,10 +5647,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5660,7 +5663,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5670,7 +5673,7 @@
         <v>46223.56317771991</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5679,7 +5682,7 @@
         <v>70</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5697,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5712,18 +5715,18 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5733,7 +5736,7 @@
         <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5742,7 +5745,7 @@
         <v>70</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5760,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5776,7 +5779,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5786,7 +5789,7 @@
         <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5795,7 +5798,7 @@
         <v>70</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5813,13 +5816,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5829,7 +5832,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5839,7 +5842,7 @@
         <v>46223.56317686343</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5848,7 +5851,7 @@
         <v>70</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5879,18 +5882,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5900,7 +5903,7 @@
         <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5909,7 +5912,7 @@
         <v>70</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5925,13 +5928,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5951,7 +5954,7 @@
         <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5960,7 +5963,7 @@
         <v>70</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -5976,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5992,7 +5995,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -6002,7 +6005,7 @@
         <v>46223.56317608796</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6011,7 +6014,7 @@
         <v>70</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6027,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6042,18 +6045,18 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6063,7 +6066,7 @@
         <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6072,7 +6075,7 @@
         <v>70</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6090,13 +6093,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6106,7 +6109,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6116,7 +6119,7 @@
         <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6125,7 +6128,7 @@
         <v>70</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6143,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6159,7 +6162,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6169,7 +6172,7 @@
         <v>46223.56317537037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6178,7 +6181,7 @@
         <v>70</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6194,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6209,18 +6212,18 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6230,7 +6233,7 @@
         <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6239,7 +6242,7 @@
         <v>70</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6257,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6273,7 +6276,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6283,7 +6286,7 @@
         <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6292,7 +6295,7 @@
         <v>70</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6310,13 +6313,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6326,7 +6329,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6336,7 +6339,7 @@
         <v>46223.563174641204</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6345,7 +6348,7 @@
         <v>70</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6363,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6378,18 +6381,18 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6399,7 +6402,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6408,7 +6411,7 @@
         <v>70</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6426,13 +6429,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6442,7 +6445,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6452,7 +6455,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6461,7 +6464,7 @@
         <v>70</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6479,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6495,7 +6498,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6505,7 +6508,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6529,7 +6532,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6542,7 +6545,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6552,16 +6555,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6579,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6594,18 +6597,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6615,16 +6618,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6640,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6656,7 +6659,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6666,16 +6669,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6693,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6709,7 +6712,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6719,7 +6722,7 @@
         <v>46223.563337430554</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6728,7 +6731,7 @@
         <v>70</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6746,13 +6749,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6761,18 +6764,18 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6782,7 +6785,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6791,7 +6794,7 @@
         <v>70</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6809,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6825,7 +6828,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6835,7 +6838,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6844,7 +6847,7 @@
         <v>70</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>
@@ -6862,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6888,16 +6891,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6915,13 +6918,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6930,18 +6933,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6951,16 +6954,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6976,13 +6979,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6992,7 +6995,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -7002,16 +7005,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7027,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -7053,16 +7056,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7095,18 +7098,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7116,16 +7119,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7141,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7157,7 +7160,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7167,16 +7170,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7192,13 +7195,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7208,7 +7211,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7218,7 +7221,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7242,7 +7245,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7255,7 +7258,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7265,16 +7268,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7292,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7307,18 +7310,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7328,7 +7331,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7355,13 +7358,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7370,13 +7373,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="303">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -333,9 +333,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215922057135204</t>
@@ -2443,7 +2440,7 @@
         <v>46206.505830497685</v>
       </c>
       <c r="D17" s="8">
-        <v>46223.562293043986</v>
+        <v>46226.179252766204</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2487,8 +2484,8 @@
       <c r="R17" s="8">
         <v>46225</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>77</v>
+      <c r="S17" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2499,7 +2496,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2508,10 +2505,10 @@
         <v>46206.50602077546</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.562289733796</v>
+        <v>46226.17925253473</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2544,7 +2541,7 @@
         <v>75</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2552,8 +2549,8 @@
       <c r="R18" s="5">
         <v>46225</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>77</v>
+      <c r="S18" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2564,7 +2561,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2573,10 +2570,10 @@
         <v>46206.50625340278</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.562286712964</v>
+        <v>46226.17925291667</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2609,7 +2606,7 @@
         <v>75</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2617,8 +2614,8 @@
       <c r="R19" s="8">
         <v>46225</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>77</v>
+      <c r="S19" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2629,7 +2626,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2638,10 +2635,10 @@
         <v>46206.50644165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.562281875</v>
+        <v>46226.17925273148</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2674,7 +2671,7 @@
         <v>75</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2682,8 +2679,8 @@
       <c r="R20" s="5">
         <v>46225</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>77</v>
+      <c r="S20" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2694,7 +2691,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2706,7 +2703,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2730,7 +2727,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2747,7 +2744,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2759,7 +2756,7 @@
         <v>46223.56236976852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2786,13 +2783,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2812,7 +2809,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46195.5550796412</v>
@@ -2824,7 +2821,7 @@
         <v>46223.56236577546</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2851,13 +2848,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46204</v>
@@ -2877,7 +2874,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46195.555127037034</v>
@@ -2889,7 +2886,7 @@
         <v>46223.56236157408</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2916,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46204</v>
@@ -2942,7 +2939,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46195.534883761575</v>
@@ -2954,7 +2951,7 @@
         <v>46224.83209384259</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2978,7 +2975,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2995,7 +2992,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46195.53514152778</v>
@@ -3007,16 +3004,16 @@
         <v>46209.820063900464</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46226</v>
@@ -3034,13 +3031,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46226</v>
@@ -3049,7 +3046,7 @@
         <v>46238</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3060,7 +3057,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3072,16 +3069,16 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46225</v>
@@ -3099,29 +3096,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3133,16 +3130,16 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46227</v>
@@ -3160,29 +3157,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3194,16 +3191,16 @@
         <v>46209.82047291667</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46226</v>
@@ -3221,10 +3218,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3236,7 +3233,7 @@
         <v>46238</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3247,7 +3244,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3259,16 +3256,16 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46226</v>
@@ -3286,13 +3283,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3302,7 +3299,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3314,16 +3311,16 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46230</v>
@@ -3341,13 +3338,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3357,7 +3354,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3369,16 +3366,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3396,10 +3393,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3411,7 +3408,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3422,7 +3419,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3434,16 +3431,16 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3461,13 +3458,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3477,7 +3474,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3489,16 +3486,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3516,13 +3513,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3532,7 +3529,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3542,16 +3539,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3569,10 +3566,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3585,7 +3582,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3597,16 +3594,16 @@
         <v>46209.82158354166</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46226</v>
@@ -3624,10 +3621,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3639,7 +3636,7 @@
         <v>46238</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3650,7 +3647,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3662,16 +3659,16 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46226</v>
@@ -3689,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3705,7 +3702,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3717,16 +3714,16 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46230</v>
@@ -3744,13 +3741,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3757,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3770,7 +3767,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3794,7 +3791,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3809,7 +3806,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3821,16 +3818,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3848,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3874,7 +3871,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3886,16 +3883,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3913,13 +3910,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3939,7 +3936,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3957,10 +3954,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3978,13 +3975,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4004,7 +4001,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4014,16 +4011,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4041,10 +4038,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4056,18 +4053,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4077,16 +4074,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4102,13 +4099,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4118,7 +4115,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4128,16 +4125,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4153,13 +4150,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4169,7 +4166,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4179,7 +4176,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4203,7 +4200,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4216,7 +4213,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4226,16 +4223,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4253,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4268,7 +4265,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4289,16 +4286,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4316,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4331,18 +4328,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4352,16 +4349,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4379,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4394,7 +4391,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4405,7 +4402,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4415,16 +4412,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4442,13 +4439,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4457,18 +4454,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4478,16 +4475,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4505,13 +4502,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4520,7 +4517,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4531,7 +4528,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4541,16 +4538,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4568,13 +4565,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4583,18 +4580,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4604,7 +4601,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4628,7 +4625,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4641,7 +4638,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4651,16 +4648,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4678,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4693,18 +4690,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4714,16 +4711,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4741,13 +4738,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4757,7 +4754,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4767,16 +4764,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4794,13 +4791,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4810,7 +4807,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4820,16 +4817,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4847,13 +4844,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4862,18 +4859,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4883,16 +4880,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4910,13 +4907,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4926,7 +4923,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4936,16 +4933,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4963,13 +4960,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4979,7 +4976,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4989,16 +4986,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5016,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5031,18 +5028,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5052,16 +5049,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5079,13 +5076,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5095,7 +5092,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5105,16 +5102,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5132,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5148,7 +5145,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5158,7 +5155,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5182,7 +5179,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5195,7 +5192,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5205,16 +5202,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5232,13 +5229,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5258,7 +5255,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5268,16 +5265,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5295,13 +5292,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5321,7 +5318,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5331,16 +5328,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5358,13 +5355,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5384,7 +5381,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5394,16 +5391,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5421,13 +5418,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5436,7 +5433,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5447,7 +5444,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5457,7 +5454,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5481,7 +5478,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5494,7 +5491,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5504,7 +5501,7 @@
         <v>46223.5631783912</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5531,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5546,18 +5543,18 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5567,7 +5564,7 @@
         <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5594,10 +5591,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5610,7 +5607,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5620,7 +5617,7 @@
         <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5647,10 +5644,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5663,7 +5660,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5673,7 +5670,7 @@
         <v>46223.56317771991</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5700,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5715,18 +5712,18 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5736,7 +5733,7 @@
         <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5763,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5779,7 +5776,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5789,7 +5786,7 @@
         <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5816,13 +5813,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5832,7 +5829,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5842,7 +5839,7 @@
         <v>46223.56317686343</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5867,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5882,18 +5879,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5903,7 +5900,7 @@
         <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5928,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5944,7 +5941,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5954,7 +5951,7 @@
         <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5979,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5995,7 +5992,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -6005,7 +6002,7 @@
         <v>46223.56317608796</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6030,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6045,18 +6042,18 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6066,7 +6063,7 @@
         <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6093,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6109,7 +6106,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6119,7 +6116,7 @@
         <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6146,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6162,7 +6159,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6172,7 +6169,7 @@
         <v>46223.56317537037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6197,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6212,18 +6209,18 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6233,7 +6230,7 @@
         <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6260,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6276,7 +6273,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6286,7 +6283,7 @@
         <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6313,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6329,7 +6326,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6339,7 +6336,7 @@
         <v>46223.563174641204</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6366,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6381,18 +6378,18 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6402,7 +6399,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6429,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6445,7 +6442,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6455,7 +6452,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6482,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6498,7 +6495,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6508,7 +6505,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6532,7 +6529,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6545,7 +6542,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6555,16 +6552,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6582,13 +6579,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6597,18 +6594,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6618,16 +6615,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6643,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6659,7 +6656,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6669,16 +6666,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6696,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6712,7 +6709,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6722,7 +6719,7 @@
         <v>46223.563337430554</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6749,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6764,18 +6761,18 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6785,7 +6782,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6812,13 +6809,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6828,7 +6825,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6838,7 +6835,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6865,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6881,7 +6878,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6891,16 +6888,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6918,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6933,18 +6930,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6954,16 +6951,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6979,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6995,7 +6992,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -7005,16 +7002,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7030,13 +7027,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7046,7 +7043,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -7056,16 +7053,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7083,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7098,18 +7095,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7119,16 +7116,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7144,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7160,7 +7157,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7170,16 +7167,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7195,13 +7192,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7211,7 +7208,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7221,7 +7218,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7245,7 +7242,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7258,7 +7255,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7268,16 +7265,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="9" t="s">
+      <c r="H101" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7295,13 +7292,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7310,18 +7307,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7331,7 +7328,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7358,13 +7355,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7373,13 +7370,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1755,7 +1755,7 @@
         <v>46197.84315976852</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.76083745371</v>
+        <v>46229.54405435185</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1818,7 +1818,7 @@
         <v>46197.84316024306</v>
       </c>
       <c r="D7" s="8">
-        <v>46197.84319010416</v>
+        <v>46229.54408450231</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -419,16 +419,19 @@
     <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1215927805772742</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1215927805772742</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -3001,7 +3004,7 @@
         <v>46209.82004709491</v>
       </c>
       <c r="D26" s="5">
-        <v>46209.820063900464</v>
+        <v>46231.200965462966</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -3045,7 +3048,7 @@
       <c r="R26" s="5">
         <v>46238</v>
       </c>
-      <c r="S26" s="11" t="s">
+      <c r="S26" s="12" t="s">
         <v>105</v>
       </c>
       <c r="T26" s="6">
@@ -3107,18 +3110,18 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3130,7 +3133,7 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3163,23 +3166,23 @@
         <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3188,10 +3191,10 @@
         <v>46209.82046094908</v>
       </c>
       <c r="D29" s="8">
-        <v>46209.82047291667</v>
+        <v>46231.2009665625</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3221,7 +3224,7 @@
         <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3232,7 +3235,7 @@
       <c r="R29" s="8">
         <v>46238</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="S29" s="12" t="s">
         <v>105</v>
       </c>
       <c r="T29" s="9">
@@ -3244,7 +3247,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3283,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3299,7 +3302,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3311,7 +3314,7 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3338,13 +3341,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3354,7 +3357,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3366,16 +3369,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3396,7 +3399,7 @@
         <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3408,7 +3411,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3419,7 +3422,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3437,10 +3440,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3458,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3474,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3486,16 +3489,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3513,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3529,7 +3532,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3539,16 +3542,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3566,10 +3569,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3582,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3591,10 +3594,10 @@
         <v>46209.82157210648</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.82158354166</v>
+        <v>46231.20096587963</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3624,7 +3627,7 @@
         <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3635,7 +3638,7 @@
       <c r="R36" s="5">
         <v>46238</v>
       </c>
-      <c r="S36" s="11" t="s">
+      <c r="S36" s="12" t="s">
         <v>105</v>
       </c>
       <c r="T36" s="6">
@@ -3647,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3686,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3714,7 +3717,7 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3741,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3757,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3767,7 +3770,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3791,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3806,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3818,16 +3821,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3845,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3871,7 +3874,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3883,16 +3886,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3910,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3954,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3975,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4001,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4011,16 +4014,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4038,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4053,18 +4056,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4074,16 +4077,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4099,13 +4102,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4115,7 +4118,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4125,16 +4128,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4150,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4166,7 +4169,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4176,7 +4179,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4200,7 +4203,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4213,7 +4216,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4223,16 +4226,16 @@
         <v>46209.82004871528</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4265,7 +4268,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4286,16 +4289,16 @@
         <v>46195.584553078705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4328,18 +4331,18 @@
         <v>46244</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4349,16 +4352,16 @@
         <v>46209.82046545139</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4376,13 +4379,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4391,7 +4394,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4402,7 +4405,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4412,16 +4415,16 @@
         <v>46195.5845503125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4439,13 +4442,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4454,18 +4457,18 @@
         <v>46244</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4475,16 +4478,16 @@
         <v>46209.82157645833</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4502,13 +4505,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4517,7 +4520,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4528,7 +4531,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4538,16 +4541,16 @@
         <v>46195.584546342594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4565,13 +4568,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4580,18 +4583,18 @@
         <v>46244</v>
       </c>
       <c r="S52" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4601,7 +4604,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4625,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4648,16 +4651,16 @@
         <v>46195.58481732639</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4675,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4690,18 +4693,18 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4711,16 +4714,16 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4738,13 +4741,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4754,7 +4757,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4764,16 +4767,16 @@
         <v>46195.58477753472</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4791,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4807,7 +4810,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4817,16 +4820,16 @@
         <v>46195.58502842592</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4844,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4859,18 +4862,18 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4880,16 +4883,16 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4907,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4923,7 +4926,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4933,16 +4936,16 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4960,13 +4963,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4976,7 +4979,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4986,16 +4989,16 @@
         <v>46197.84290087963</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5013,13 +5016,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5028,18 +5031,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5049,16 +5052,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5076,13 +5079,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5102,16 +5105,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5129,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5145,7 +5148,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5155,7 +5158,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5179,7 +5182,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5192,7 +5195,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5202,16 +5205,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5229,13 +5232,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5255,7 +5258,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5265,16 +5268,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5292,13 +5295,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5318,7 +5321,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5328,16 +5331,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5355,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5381,7 +5384,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5391,16 +5394,16 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5418,13 +5421,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5433,7 +5436,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5444,7 +5447,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5454,7 +5457,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5478,7 +5481,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5501,7 +5504,7 @@
         <v>46223.5631783912</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5528,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5543,18 +5546,18 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5564,7 +5567,7 @@
         <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5591,10 +5594,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5607,7 +5610,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5617,7 +5620,7 @@
         <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5644,10 +5647,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5660,7 +5663,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5670,7 +5673,7 @@
         <v>46223.56317771991</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5697,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5712,18 +5715,18 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5733,7 +5736,7 @@
         <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5760,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5776,7 +5779,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5786,7 +5789,7 @@
         <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5813,13 +5816,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5829,7 +5832,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5839,7 +5842,7 @@
         <v>46223.56317686343</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5879,18 +5882,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5900,7 +5903,7 @@
         <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5925,13 +5928,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5951,7 +5954,7 @@
         <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5976,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5992,7 +5995,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -6002,7 +6005,7 @@
         <v>46223.56317608796</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6027,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6042,18 +6045,18 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6063,7 +6066,7 @@
         <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6090,13 +6093,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6106,7 +6109,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6116,7 +6119,7 @@
         <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6143,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6159,7 +6162,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6169,7 +6172,7 @@
         <v>46223.56317537037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6194,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6209,18 +6212,18 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6230,7 +6233,7 @@
         <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6257,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6273,7 +6276,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6283,7 +6286,7 @@
         <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6310,13 +6313,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6326,7 +6329,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6336,7 +6339,7 @@
         <v>46223.563174641204</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6363,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6378,18 +6381,18 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6399,7 +6402,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6426,13 +6429,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6442,7 +6445,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6452,7 +6455,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6479,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6495,7 +6498,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6505,7 +6508,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6529,7 +6532,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6542,7 +6545,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
@@ -6552,16 +6555,16 @@
         <v>46195.58618233797</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6579,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6594,18 +6597,18 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6615,16 +6618,16 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6640,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6656,7 +6659,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6666,16 +6669,16 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6693,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6709,7 +6712,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
@@ -6719,7 +6722,7 @@
         <v>46223.563337430554</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6746,13 +6749,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6761,18 +6764,18 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6782,7 +6785,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6809,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6825,7 +6828,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6835,7 +6838,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6862,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
@@ -6888,16 +6891,16 @@
         <v>46195.58649912037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6915,13 +6918,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6930,18 +6933,18 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -6951,16 +6954,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6976,13 +6979,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -6992,7 +6995,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -7002,16 +7005,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7027,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
@@ -7053,16 +7056,16 @@
         <v>46195.5866459838</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7095,18 +7098,18 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7116,16 +7119,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7141,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7157,7 +7160,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7167,16 +7170,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7192,13 +7195,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7208,7 +7211,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7218,7 +7221,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7242,7 +7245,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7255,7 +7258,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7265,16 +7268,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7292,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7307,18 +7310,18 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7328,7 +7331,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7355,13 +7358,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
@@ -7370,13 +7373,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46209.82004871528</v>
+        <v>46233.18431923611</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4267,8 +4267,8 @@
       <c r="R47" s="8">
         <v>46240</v>
       </c>
-      <c r="S47" s="11" t="s">
-        <v>109</v>
+      <c r="S47" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46209.82046545139</v>
+        <v>46233.18431914352</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4393,8 +4393,8 @@
       <c r="R49" s="8">
         <v>46240</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>109</v>
+      <c r="S49" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46209.82157645833</v>
+        <v>46233.18432418982</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4519,8 +4519,8 @@
       <c r="R51" s="8">
         <v>46240</v>
       </c>
-      <c r="S51" s="11" t="s">
-        <v>109</v>
+      <c r="S51" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -305,79 +305,79 @@
     <t xml:space="preserve">Propuesta compras:,Reserva Alabe OT 4363 </t>
   </si>
   <si>
+    <t>1215932733979125</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodeteOT 4363</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1215932733979147</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057135204</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>1215922057135216</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215930353764509</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363</t>
+  </si>
+  <si>
+    <t>1215927804444266</t>
+  </si>
+  <si>
+    <t>Reserva Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
+  </si>
+  <si>
+    <t>1215927804444272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva motor OT 4363 </t>
+  </si>
+  <si>
+    <t>Reserva Material,Recepcion motor</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215932733979125</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodeteOT 4363</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Reserva rodete  OT 4363,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1215932733979147</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057135204</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>1215922057135216</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215930353764509</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363</t>
-  </si>
-  <si>
-    <t>1215927804444266</t>
-  </si>
-  <si>
-    <t>Reserva Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 ,Reserva rodete  OT 4363,Reserva Alabe OT 4363 </t>
-  </si>
-  <si>
-    <t>1215927804444272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva motor OT 4363 </t>
-  </si>
-  <si>
-    <t>Reserva Material,Recepcion motor</t>
   </si>
   <si>
     <t>1215927804444273</t>
@@ -2313,7 +2313,7 @@
         <v>46197.49930170139</v>
       </c>
       <c r="D15" s="8">
-        <v>46204.19501679398</v>
+        <v>46237.54592135416</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2363,13 +2363,13 @@
       <c r="T15" s="9">
         <v>1</v>
       </c>
-      <c r="U15" s="12" t="s">
-        <v>67</v>
+      <c r="U15" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46195.53506689815</v>
@@ -2378,19 +2378,19 @@
         <v>46197.49934962963</v>
       </c>
       <c r="D16" s="5">
-        <v>46223.56229649305</v>
+        <v>46237.545945289356</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I16" s="5">
         <v>46199</v>
@@ -2414,7 +2414,7 @@
         <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46199</v>
@@ -2428,13 +2428,13 @@
       <c r="T16" s="6">
         <v>1</v>
       </c>
-      <c r="U16" s="12" t="s">
-        <v>67</v>
+      <c r="U16" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8">
         <v>46195.53507237269</v>
@@ -2446,16 +2446,16 @@
         <v>46226.179252766204</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I17" s="8">
         <v>46224</v>
@@ -2476,10 +2476,10 @@
         <v>59</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="Q17" s="8">
         <v>46224</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46195.535077141205</v>
@@ -2511,16 +2511,16 @@
         <v>46226.17925253473</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I18" s="5">
         <v>46224</v>
@@ -2541,10 +2541,10 @@
         <v>59</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46224</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46195.53508107639</v>
@@ -2576,16 +2576,16 @@
         <v>46226.17925291667</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I19" s="8">
         <v>46224</v>
@@ -2606,10 +2606,10 @@
         <v>59</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46224</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46195.535084918985</v>
@@ -2641,16 +2641,16 @@
         <v>46226.17925273148</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I20" s="5">
         <v>46224</v>
@@ -2671,10 +2671,10 @@
         <v>59</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46224</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46195.55482737269</v>
@@ -2706,7 +2706,7 @@
         <v>46203.636544884255</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2730,7 +2730,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46195.55503578704</v>
@@ -2759,16 +2759,16 @@
         <v>46223.56236976852</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I22" s="5">
         <v>46204</v>
@@ -2786,13 +2786,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46204</v>
@@ -2807,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2830,10 +2830,10 @@
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I23" s="8">
         <v>46204</v>
@@ -2851,10 +2851,10 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>94</v>
@@ -2895,10 +2895,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I24" s="5">
         <v>46204</v>
@@ -2916,7 +2916,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>65</v>
@@ -3102,7 +3102,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>108</v>
@@ -3259,7 +3259,7 @@
         <v>46209.82040827547</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3289,7 +3289,7 @@
         <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>118</v>
@@ -3344,7 +3344,7 @@
         <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>121</v>
@@ -3434,7 +3434,7 @@
         <v>46209.617592256945</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3464,7 +3464,7 @@
         <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>128</v>
@@ -3519,7 +3519,7 @@
         <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>131</v>
@@ -3662,7 +3662,7 @@
         <v>46209.82149362269</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3692,7 +3692,7 @@
         <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>140</v>
@@ -3747,7 +3747,7 @@
         <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>143</v>
@@ -3804,7 +3804,7 @@
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
       <c r="U39" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3951,7 +3951,7 @@
         <v>46224.2078484375</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.584553078705</v>
+        <v>46237.17920200231</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4330,8 +4330,8 @@
       <c r="R48" s="5">
         <v>46244</v>
       </c>
-      <c r="S48" s="11" t="s">
-        <v>109</v>
+      <c r="S48" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46195.5845503125</v>
+        <v>46237.17920196759</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4456,8 +4456,8 @@
       <c r="R50" s="5">
         <v>46244</v>
       </c>
-      <c r="S50" s="11" t="s">
-        <v>109</v>
+      <c r="S50" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4526,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46195.584546342594</v>
+        <v>46237.17920196759</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4582,8 +4582,8 @@
       <c r="R52" s="5">
         <v>46244</v>
       </c>
-      <c r="S52" s="11" t="s">
-        <v>109</v>
+      <c r="S52" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -5253,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5316,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5361,7 +5361,7 @@
         <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>227</v>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5510,10 +5510,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I69" s="8">
         <v>46258</v>
@@ -5573,10 +5573,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I70" s="5">
         <v>46258</v>
@@ -5626,10 +5626,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I71" s="8">
         <v>46258</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46223.56317771991</v>
+        <v>46237.546838587965</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5679,10 +5679,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I72" s="5">
         <v>46265</v>
@@ -5720,8 +5720,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>110</v>
+      <c r="U72" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5742,10 +5742,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I73" s="8">
         <v>46265</v>
@@ -5795,10 +5795,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I74" s="5">
         <v>46265</v>
@@ -5848,10 +5848,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5909,10 +5909,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5960,10 +5960,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -6011,10 +6011,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6072,10 +6072,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6125,10 +6125,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6178,10 +6178,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6239,10 +6239,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I82" s="5">
         <v>46268</v>
@@ -6292,10 +6292,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I83" s="8">
         <v>46268</v>
@@ -6345,10 +6345,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I84" s="5">
         <v>46272</v>
@@ -6408,10 +6408,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I85" s="8">
         <v>46272</v>
@@ -6461,10 +6461,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I86" s="5">
         <v>46272</v>
@@ -6728,10 +6728,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I91" s="8">
         <v>46274</v>
@@ -6791,10 +6791,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -6844,10 +6844,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I93" s="8">
         <v>46274</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -419,217 +419,217 @@
     <t>Fabricacion Corte Laser OT 4363 ,Generación OC materiales corte Laser OT 4363</t>
   </si>
   <si>
+    <t>1215927805772742</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215922057038280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4363 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4363,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215922057235538</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>1215922057235550</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>1215932734087331</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT4363</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4363,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215932734087348</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805840763</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805840780</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>1215932734105392</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215932734105404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4363 </t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115811</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115828</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215922055649560</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259222</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259244</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215932734132723</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Propuesta Fabricación externa  OT 4363,propuesta Corte Laser OT 4363,Propuesta Corte plasma OT 4363,Propuesta Mecanizado OT 4363, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734142205</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215941551854210</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215941551854222</t>
+  </si>
+  <si>
+    <t>1215930353891784</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215930353891796</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215927805772742</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser OT 4363 ,Materiales corte Laser OT 4363</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215922057038280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4363 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4363,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215922057235538</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>1215922057235550</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363,Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>1215932734087331</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT4363</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4363,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215932734087348</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805840763</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805840780</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>1215932734105392</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215932734105404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4363 </t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115811</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115828</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215922055649560</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259222</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259244</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215932734132723</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Propuesta Fabricación externa  OT 4363,propuesta Corte Laser OT 4363,Propuesta Corte plasma OT 4363,Propuesta Mecanizado OT 4363, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734142205</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215941551854210</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215941551854222</t>
-  </si>
-  <si>
-    <t>1215930353891784</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215930353891796</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215941551880377</t>
@@ -3004,7 +3004,7 @@
         <v>46209.82004709491</v>
       </c>
       <c r="D26" s="5">
-        <v>46231.200965462966</v>
+        <v>46239.182705115745</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -3048,8 +3048,8 @@
       <c r="R26" s="5">
         <v>46238</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>105</v>
+      <c r="S26" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46195.535146215276</v>
@@ -3072,7 +3072,7 @@
         <v>46209.8199925463</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3105,23 +3105,23 @@
         <v>73</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46195.53519951389</v>
@@ -3133,7 +3133,7 @@
         <v>46209.82003284722</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3163,26 +3163,26 @@
         <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46195.535206608794</v>
@@ -3191,10 +3191,10 @@
         <v>46209.82046094908</v>
       </c>
       <c r="D29" s="8">
-        <v>46231.2009665625</v>
+        <v>46239.18270478009</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3224,7 +3224,7 @@
         <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3235,8 +3235,8 @@
       <c r="R29" s="8">
         <v>46238</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>105</v>
+      <c r="S29" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46195.53521144676</v>
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46195.53521638889</v>
@@ -3314,7 +3314,7 @@
         <v>46209.82044996528</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3341,13 +3341,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46195.53522158565</v>
@@ -3369,16 +3369,16 @@
         <v>46209.6177050463</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46226</v>
@@ -3399,7 +3399,7 @@
         <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3411,7 +3411,7 @@
         <v>46266</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3440,10 +3440,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46226</v>
@@ -3461,13 +3461,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3489,16 +3489,16 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46237</v>
@@ -3516,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3542,16 +3542,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3569,10 +3569,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3594,10 +3594,10 @@
         <v>46209.82157210648</v>
       </c>
       <c r="D36" s="5">
-        <v>46231.20096587963</v>
+        <v>46239.18270481481</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3627,7 +3627,7 @@
         <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3638,8 +3638,8 @@
       <c r="R36" s="5">
         <v>46238</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>105</v>
+      <c r="S36" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3717,7 +3717,7 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3770,7 +3770,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3821,16 +3821,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3848,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3886,16 +3886,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3913,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3957,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3978,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4014,16 +4014,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4041,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4056,18 +4056,18 @@
         <v>46269</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4077,16 +4077,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4102,13 +4102,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4128,16 +4128,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4153,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4179,7 +4179,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4203,7 +4203,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4226,16 +4226,16 @@
         <v>46233.18431923611</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4268,7 +4268,7 @@
         <v>46240</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4295,10 +4295,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4316,7 +4316,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>178</v>
@@ -4331,13 +4331,13 @@
         <v>46244</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4358,10 +4358,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4379,10 +4379,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>182</v>
@@ -4394,7 +4394,7 @@
         <v>46240</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4442,7 +4442,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>181</v>
@@ -4457,13 +4457,13 @@
         <v>46244</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4484,10 +4484,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4505,10 +4505,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>188</v>
@@ -4520,7 +4520,7 @@
         <v>46240</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4568,7 +4568,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>187</v>
@@ -4583,13 +4583,13 @@
         <v>46244</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4693,13 +4693,13 @@
         <v>46247</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4714,7 +4714,7 @@
         <v>46195.584780624995</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4850,7 +4850,7 @@
         <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>191</v>
@@ -4862,13 +4862,13 @@
         <v>46254</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4883,7 +4883,7 @@
         <v>46198.51058690972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4936,7 +4936,7 @@
         <v>46198.510575162036</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4995,10 +4995,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5019,7 +5019,7 @@
         <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>191</v>
@@ -5031,13 +5031,13 @@
         <v>46255</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5052,16 +5052,16 @@
         <v>46198.5105765162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5105,16 +5105,16 @@
         <v>46198.51057732639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5158,7 +5158,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5211,10 +5211,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5232,7 +5232,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>93</v>
@@ -5274,10 +5274,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5295,7 +5295,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>96</v>
@@ -5337,10 +5337,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5358,7 +5358,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>89</v>
@@ -5400,10 +5400,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5421,10 +5421,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>230</v>
@@ -5436,7 +5436,7 @@
         <v>46266</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>46262</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5567,7 +5567,7 @@
         <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5620,7 +5620,7 @@
         <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5703,7 +5703,7 @@
         <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>232</v>
@@ -5715,7 +5715,7 @@
         <v>46265</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5736,7 +5736,7 @@
         <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5789,7 +5789,7 @@
         <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5870,7 +5870,7 @@
         <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>232</v>
@@ -5882,13 +5882,13 @@
         <v>46266</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5903,7 +5903,7 @@
         <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5954,7 +5954,7 @@
         <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6033,7 +6033,7 @@
         <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>232</v>
@@ -6045,13 +6045,13 @@
         <v>46267</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6066,7 +6066,7 @@
         <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6119,7 +6119,7 @@
         <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6200,7 +6200,7 @@
         <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>232</v>
@@ -6212,13 +6212,13 @@
         <v>46268</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6233,7 +6233,7 @@
         <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6263,7 +6263,7 @@
         <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>260</v>
@@ -6286,7 +6286,7 @@
         <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6316,7 +6316,7 @@
         <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>260</v>
@@ -6369,7 +6369,7 @@
         <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>264</v>
@@ -6381,13 +6381,13 @@
         <v>46272</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6402,7 +6402,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6432,7 +6432,7 @@
         <v>263</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>266</v>
@@ -6455,7 +6455,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6485,7 +6485,7 @@
         <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>266</v>
@@ -6597,13 +6597,13 @@
         <v>46273</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6618,7 +6618,7 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6646,7 +6646,7 @@
         <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>277</v>
@@ -6669,7 +6669,7 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6699,7 +6699,7 @@
         <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>277</v>
@@ -6752,7 +6752,7 @@
         <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>269</v>
@@ -6764,13 +6764,13 @@
         <v>46274</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6815,7 +6815,7 @@
         <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>282</v>
@@ -6838,7 +6838,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6868,7 +6868,7 @@
         <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>282</v>
@@ -6921,7 +6921,7 @@
         <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>269</v>
@@ -6933,13 +6933,13 @@
         <v>46275</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6954,7 +6954,7 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -6982,7 +6982,7 @@
         <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>287</v>
@@ -7005,7 +7005,7 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7033,7 +7033,7 @@
         <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>289</v>
@@ -7086,7 +7086,7 @@
         <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>292</v>
@@ -7098,13 +7098,13 @@
         <v>46276</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7119,7 +7119,7 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7147,7 +7147,7 @@
         <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>291</v>
@@ -7170,7 +7170,7 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7198,7 +7198,7 @@
         <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>291</v>
@@ -7310,13 +7310,13 @@
         <v>46287</v>
       </c>
       <c r="S101" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
       </c>
       <c r="U101" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7373,13 +7373,13 @@
         <v>46287</v>
       </c>
       <c r="S102" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T102" s="6">
         <v>0</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46233.18431923611</v>
+        <v>46240.16870627315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46233.18431914352</v>
+        <v>46240.16871517361</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46233.18432418982</v>
+        <v>46240.16873871528</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46195.58481732639</v>
+        <v>46240.18234653935</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4692,8 +4692,8 @@
       <c r="R54" s="5">
         <v>46247</v>
       </c>
-      <c r="S54" s="11" t="s">
-        <v>108</v>
+      <c r="S54" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -629,19 +629,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1215941551880377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Bodega:, ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215941551880377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Bodega:, ot 4363  ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215932734202816</t>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46240.16870627315</v>
+        <v>46241.182685694446</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4267,8 +4267,8 @@
       <c r="R47" s="8">
         <v>46240</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>175</v>
+      <c r="S47" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4289,7 +4289,7 @@
         <v>46237.17920200231</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4319,10 +4319,10 @@
         <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4331,7 +4331,7 @@
         <v>46244</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46240.16871517361</v>
+        <v>46241.18268534722</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4393,8 +4393,8 @@
       <c r="R49" s="8">
         <v>46240</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>175</v>
+      <c r="S49" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -4457,7 +4457,7 @@
         <v>46244</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46240.16873871528</v>
+        <v>46241.18268515046</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>187</v>
@@ -4519,8 +4519,8 @@
       <c r="R51" s="8">
         <v>46240</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>175</v>
+      <c r="S51" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>46244</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>46247</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46237.17920200231</v>
+        <v>46244.169137523146</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46237.17920196759</v>
+        <v>46244.169100162035</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46237.17920196759</v>
+        <v>46244.16908849537</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -641,58 +641,58 @@
     <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Bodega:, ot 4363  ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>1215932734202816</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215932734202838</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215941551880760</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215927805923801</t>
+  </si>
+  <si>
+    <t>1215927805923818</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215927805923830</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215932734202816</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215932734202838</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363  ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215941551880760</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215927805923801</t>
-  </si>
-  <si>
-    <t>1215927805923818</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215927805923830</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
     <t>1215927805933398</t>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46244.169137523146</v>
+        <v>46245.168955601854</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4330,8 +4330,8 @@
       <c r="R48" s="5">
         <v>46244</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>179</v>
+      <c r="S48" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4352,7 +4352,7 @@
         <v>46241.18268534722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4385,7 +4385,7 @@
         <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4405,17 +4405,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46244.169100162035</v>
+        <v>46245.168955393514</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4445,10 +4445,10 @@
         <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4456,8 +4456,8 @@
       <c r="R50" s="5">
         <v>46244</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>179</v>
+      <c r="S50" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4478,7 +4478,7 @@
         <v>46241.18268515046</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4511,7 +4511,7 @@
         <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4531,17 +4531,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46244.16908849537</v>
+        <v>46245.16895542824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4571,10 +4571,10 @@
         <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4582,8 +4582,8 @@
       <c r="R52" s="5">
         <v>46244</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>179</v>
+      <c r="S52" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4604,7 +4604,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4628,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4651,16 +4651,16 @@
         <v>46240.18234653935</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4678,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4693,7 +4693,7 @@
         <v>46247</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4720,10 +4720,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4741,7 +4741,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>198</v>
@@ -4773,10 +4773,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4794,7 +4794,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>202</v>
@@ -4826,10 +4826,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4847,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4889,10 +4889,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4942,10 +4942,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -5016,13 +5016,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -6897,10 +6897,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6960,10 +6960,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -7011,10 +7011,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7062,10 +7062,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7125,10 +7125,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7176,10 +7176,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46240.18234653935</v>
+        <v>46247.168339861106</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.584780624995</v>
+        <v>46247.1683419676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>164</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.58477753472</v>
+        <v>46247.16834949074</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.58502842592</v>
+        <v>46247.200006747684</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4861,8 +4861,8 @@
       <c r="R57" s="8">
         <v>46254</v>
       </c>
-      <c r="S57" s="11" t="s">
-        <v>108</v>
+      <c r="S57" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -692,34 +692,34 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
+    <t>1215927805933398</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734211704</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215922057304565</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215927805933398</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734211704</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215922057304565</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1215932734213367</t>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46247.168339861106</v>
+        <v>46248.19094503472</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4692,8 +4692,8 @@
       <c r="R54" s="5">
         <v>46247</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>196</v>
+      <c r="S54" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4744,10 +4744,10 @@
         <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4767,7 +4767,7 @@
         <v>46247.16834949074</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4797,10 +4797,10 @@
         <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4820,7 +4820,7 @@
         <v>46247.200006747684</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4862,7 +4862,7 @@
         <v>46254</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>207</v>
@@ -4963,7 +4963,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>210</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46197.84290087963</v>
+        <v>46248.18986024306</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5030,8 +5030,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="11" t="s">
-        <v>108</v>
+      <c r="S60" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46247.200006747684</v>
+        <v>46254.16826832176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46198.51058690972</v>
+        <v>46254.16828515046</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>164</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46198.510575162036</v>
+        <v>46254.16828640046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>164</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -719,31 +719,31 @@
     <t>Armado</t>
   </si>
   <si>
+    <t>1215932734213367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Armado</t>
+  </si>
+  <si>
+    <t>1215932734213389</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215930354016401</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215932734213367</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Armado</t>
-  </si>
-  <si>
-    <t>1215932734213389</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215930354016401</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
   </si>
   <si>
     <t>1215930354026690</t>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46254.16826832176</v>
+        <v>46255.16911224537</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -4861,8 +4861,8 @@
       <c r="R57" s="8">
         <v>46254</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>205</v>
+      <c r="S57" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4913,10 +4913,10 @@
         <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4966,10 +4966,10 @@
         <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4979,17 +4979,17 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46248.18986024306</v>
+        <v>46255.16903023148</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5031,7 +5031,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46198.5105765162</v>
+        <v>46255.16903265046</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>164</v>
@@ -5079,10 +5079,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>215</v>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.51057732639</v>
+        <v>46255.169033865735</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>164</v>
@@ -5132,10 +5132,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>217</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46223.5631783912</v>
+        <v>46255.175512581016</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5545,8 +5545,8 @@
       <c r="R69" s="8">
         <v>46262</v>
       </c>
-      <c r="S69" s="11" t="s">
-        <v>108</v>
+      <c r="S69" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -743,76 +743,76 @@
     <t>Control de calidad Armado</t>
   </si>
   <si>
+    <t>1215930354026690</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Revestimiento,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215930354026712</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734228548</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215932734228560</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Bodega:</t>
+  </si>
+  <si>
+    <t>1215932734236070</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215922057367621</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215930353891849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215923636418868</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje Alabe,Montaje Rodete,Montaje motor,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215923636418880</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa , ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215930354026690</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Revestimiento,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215930354026712</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734228548</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215932734228560</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Bodega:</t>
-  </si>
-  <si>
-    <t>1215932734236070</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215922057367621</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215930353891849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215923636418868</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje Alabe,Montaje Rodete,Montaje motor,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215923636418880</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa , ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215922057394981</t>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46255.16903023148</v>
+        <v>46256.1835681713</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5030,8 +5030,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>213</v>
+      <c r="S60" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5085,7 +5085,7 @@
         <v>206</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5138,7 +5138,7 @@
         <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5182,7 +5182,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5205,7 +5205,7 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5238,7 +5238,7 @@
         <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5268,7 +5268,7 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5301,7 +5301,7 @@
         <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5331,7 +5331,7 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5364,7 +5364,7 @@
         <v>89</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5394,7 +5394,7 @@
         <v>46209.617651782406</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5427,7 +5427,7 @@
         <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5457,7 +5457,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5481,7 +5481,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5504,7 +5504,7 @@
         <v>46255.175512581016</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5531,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5546,7 +5546,7 @@
         <v>46262</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>238</v>
@@ -5647,7 +5647,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>238</v>
@@ -5700,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5867,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -6030,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6197,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6366,7 +6366,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>162</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46237.546838587965</v>
+        <v>46258.19795055556</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5714,8 +5714,8 @@
       <c r="R72" s="5">
         <v>46265</v>
       </c>
-      <c r="S72" s="11" t="s">
-        <v>108</v>
+      <c r="S72" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -482,6 +482,9 @@
     <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215927805840763</t>
   </si>
   <si>
@@ -810,9 +813,6 @@
   </si>
   <si>
     <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa , ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215922057394981</t>
@@ -3366,7 +3366,7 @@
         <v>46209.61768758102</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.6177050463</v>
+        <v>46259.18154832176</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3410,8 +3410,8 @@
       <c r="R32" s="5">
         <v>46266</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>108</v>
+      <c r="S32" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3467,7 +3467,7 @@
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3489,7 +3489,7 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3522,7 +3522,7 @@
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3542,16 +3542,16 @@
         <v>46209.61764521991</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3572,7 +3572,7 @@
         <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3597,7 +3597,7 @@
         <v>46239.18270481481</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3627,7 +3627,7 @@
         <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3717,7 +3717,7 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3770,7 +3770,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3821,16 +3821,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3848,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3886,16 +3886,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3913,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3957,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3978,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4014,16 +4014,16 @@
         <v>46195.5843471875</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4041,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4077,16 +4077,16 @@
         <v>46195.58430498843</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4102,13 +4102,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4128,16 +4128,16 @@
         <v>46195.58430173611</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4153,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4179,7 +4179,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4203,7 +4203,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4226,16 +4226,16 @@
         <v>46241.182685694446</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4289,16 +4289,16 @@
         <v>46245.168955601854</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4316,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4342,7 +4342,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4352,16 +4352,16 @@
         <v>46241.18268534722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4379,13 +4379,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4415,16 +4415,16 @@
         <v>46245.168955393514</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4442,13 +4442,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4478,16 +4478,16 @@
         <v>46241.18268515046</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4505,13 +4505,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4541,16 +4541,16 @@
         <v>46245.16895542824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4568,13 +4568,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4604,7 +4604,7 @@
         <v>46195.57386709491</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4628,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4651,16 +4651,16 @@
         <v>46248.19094503472</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4678,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4714,16 +4714,16 @@
         <v>46247.1683419676</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4741,13 +4741,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4767,16 +4767,16 @@
         <v>46247.16834949074</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4794,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4820,16 +4820,16 @@
         <v>46255.16911224537</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4847,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4883,16 +4883,16 @@
         <v>46254.16828515046</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4910,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4926,7 +4926,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4936,16 +4936,16 @@
         <v>46254.16828640046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4963,13 +4963,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -4989,16 +4989,16 @@
         <v>46256.1835681713</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5016,13 +5016,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5052,16 +5052,16 @@
         <v>46255.16903265046</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5079,13 +5079,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5105,16 +5105,16 @@
         <v>46255.169033865735</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5132,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5158,7 +5158,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5182,7 +5182,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5205,16 +5205,16 @@
         <v>46210.20645508102</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5232,13 +5232,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5268,16 +5268,16 @@
         <v>46210.206457175926</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5295,13 +5295,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5331,16 +5331,16 @@
         <v>46210.20645534722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5358,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5384,26 +5384,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46209.617651782406</v>
+        <v>46259.181548645836</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5421,13 +5421,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5435,8 +5435,8 @@
       <c r="R67" s="8">
         <v>46266</v>
       </c>
-      <c r="S67" s="11" t="s">
-        <v>108</v>
+      <c r="S67" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5457,7 +5457,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5481,7 +5481,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5504,7 +5504,7 @@
         <v>46255.175512581016</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5531,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5546,7 +5546,7 @@
         <v>46262</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>46223.56247709491</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5594,7 +5594,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>238</v>
@@ -5620,7 +5620,7 @@
         <v>46223.56247644676</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5647,7 +5647,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>238</v>
@@ -5700,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5715,7 +5715,7 @@
         <v>46265</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5736,7 +5736,7 @@
         <v>46223.56257947917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5789,7 +5789,7 @@
         <v>46223.56257876157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46223.56317686343</v>
+        <v>46259.18154827546</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5867,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5881,8 +5881,8 @@
       <c r="R75" s="8">
         <v>46266</v>
       </c>
-      <c r="S75" s="11" t="s">
-        <v>108</v>
+      <c r="S75" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
@@ -5903,7 +5903,7 @@
         <v>46223.56267032407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5954,7 +5954,7 @@
         <v>46223.562669756946</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6030,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6066,7 +6066,7 @@
         <v>46223.56275505787</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6119,7 +6119,7 @@
         <v>46223.56275440972</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6197,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6233,7 +6233,7 @@
         <v>46223.562948425926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6263,7 +6263,7 @@
         <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>260</v>
@@ -6286,7 +6286,7 @@
         <v>46223.56294780092</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6316,7 +6316,7 @@
         <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>260</v>
@@ -6366,10 +6366,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>264</v>
@@ -6402,7 +6402,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6432,7 +6432,7 @@
         <v>263</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>266</v>
@@ -6455,7 +6455,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6485,7 +6485,7 @@
         <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>266</v>
@@ -6618,7 +6618,7 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6646,7 +6646,7 @@
         <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>277</v>
@@ -6669,7 +6669,7 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6699,7 +6699,7 @@
         <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>277</v>
@@ -6752,7 +6752,7 @@
         <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>269</v>
@@ -6785,7 +6785,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6815,7 +6815,7 @@
         <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>282</v>
@@ -6838,7 +6838,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6868,7 +6868,7 @@
         <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>282</v>
@@ -6897,10 +6897,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6921,7 +6921,7 @@
         <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>269</v>
@@ -6954,16 +6954,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6982,7 +6982,7 @@
         <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>287</v>
@@ -7005,16 +7005,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7033,7 +7033,7 @@
         <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>289</v>
@@ -7062,10 +7062,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7086,7 +7086,7 @@
         <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>292</v>
@@ -7119,16 +7119,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7147,7 +7147,7 @@
         <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>291</v>
@@ -7170,16 +7170,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7198,7 +7198,7 @@
         <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>291</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46223.56317608796</v>
+        <v>46260.179138217594</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6044,8 +6044,8 @@
       <c r="R78" s="5">
         <v>46267</v>
       </c>
-      <c r="S78" s="11" t="s">
-        <v>108</v>
+      <c r="S78" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.57386709491</v>
+        <v>46260.58700864583</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4646,9 +4646,11 @@
       <c r="B54" s="5">
         <v>46195.53537232639</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46260.58671038195</v>
+      </c>
       <c r="D54" s="5">
-        <v>46248.19094503472</v>
+        <v>46260.59069322917</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4696,10 +4698,10 @@
         <v>32</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4709,9 +4711,11 @@
       <c r="B55" s="8">
         <v>46195.53537631944</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46260.586811747686</v>
+      </c>
       <c r="D55" s="8">
-        <v>46247.1683419676</v>
+        <v>46260.58681349537</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>165</v>
@@ -4762,9 +4766,11 @@
       <c r="B56" s="5">
         <v>46195.53538179398</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46260.58690101852</v>
+      </c>
       <c r="D56" s="5">
-        <v>46247.16834949074</v>
+        <v>46260.586903206015</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4815,9 +4821,11 @@
       <c r="B57" s="8">
         <v>46195.53540148148</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46260.5869990625</v>
+      </c>
       <c r="D57" s="8">
-        <v>46255.16911224537</v>
+        <v>46260.58701207176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4865,10 +4873,10 @@
         <v>32</v>
       </c>
       <c r="T57" s="9">
-        <v>0</v>
-      </c>
-      <c r="U57" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4878,9 +4886,11 @@
       <c r="B58" s="5">
         <v>46195.53540543982</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46260.58697520834</v>
+      </c>
       <c r="D58" s="5">
-        <v>46254.16828515046</v>
+        <v>46260.58697668981</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>165</v>
@@ -4931,9 +4941,11 @@
       <c r="B59" s="8">
         <v>46195.53541055556</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46260.58698325232</v>
+      </c>
       <c r="D59" s="8">
-        <v>46254.16828640046</v>
+        <v>46260.58698486111</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>165</v>
@@ -4986,7 +4998,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46256.1835681713</v>
+        <v>46260.59071152778</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5036,8 +5048,8 @@
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="10" t="s">
-        <v>109</v>
+      <c r="U60" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5049,7 +5061,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46255.16903265046</v>
+        <v>46260.586980127315</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>165</v>
@@ -5102,7 +5114,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46255.169033865735</v>
+        <v>46260.58699188658</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>165</v>
@@ -5202,7 +5214,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46210.20645508102</v>
+        <v>46260.59078993056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5252,8 +5264,8 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>91</v>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5265,7 +5277,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46210.206457175926</v>
+        <v>46260.59081489583</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>224</v>
@@ -5315,8 +5327,8 @@
       <c r="T65" s="9">
         <v>0</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>91</v>
+      <c r="U65" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5328,7 +5340,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46210.20645534722</v>
+        <v>46260.59082912037</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5378,8 +5390,8 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>91</v>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5391,7 +5403,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46259.181548645836</v>
+        <v>46260.590860428245</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5441,8 +5453,8 @@
       <c r="T67" s="9">
         <v>0</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>91</v>
+      <c r="U67" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5501,7 +5513,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46255.175512581016</v>
+        <v>46260.59089402777</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5551,8 +5563,8 @@
       <c r="T69" s="9">
         <v>0</v>
       </c>
-      <c r="U69" s="10" t="s">
-        <v>109</v>
+      <c r="U69" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5839,7 +5851,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46259.18154827546</v>
+        <v>46260.59090943287</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5887,8 +5899,8 @@
       <c r="T75" s="9">
         <v>0</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>109</v>
+      <c r="U75" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6002,7 +6014,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46260.179138217594</v>
+        <v>46260.59092870371</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6050,8 +6062,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>109</v>
+      <c r="U78" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6169,7 +6181,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46223.56317537037</v>
+        <v>46260.590943981486</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6217,8 +6229,8 @@
       <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>109</v>
+      <c r="U81" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6336,7 +6348,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46223.563174641204</v>
+        <v>46260.59096447917</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6386,8 +6398,8 @@
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="10" t="s">
-        <v>109</v>
+      <c r="U84" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6719,7 +6731,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46223.563337430554</v>
+        <v>46260.591004409725</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6769,8 +6781,8 @@
       <c r="T91" s="9">
         <v>0</v>
       </c>
-      <c r="U91" s="10" t="s">
-        <v>109</v>
+      <c r="U91" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6888,7 +6900,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46195.58649912037</v>
+        <v>46260.59102431713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6938,8 +6950,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="10" t="s">
-        <v>109</v>
+      <c r="U94" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46260.590943981486</v>
+        <v>46261.20224831019</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6223,8 +6223,8 @@
       <c r="R81" s="8">
         <v>46268</v>
       </c>
-      <c r="S81" s="11" t="s">
-        <v>108</v>
+      <c r="S81" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46260.59089402777</v>
+        <v>46262.16926818287</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46223.56247709491</v>
+        <v>46262.169264571756</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>165</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46223.56247644676</v>
+        <v>46262.16926988426</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46195.5843471875</v>
+        <v>46262.18089949074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4055,8 +4055,8 @@
       <c r="R43" s="8">
         <v>46269</v>
       </c>
-      <c r="S43" s="11" t="s">
-        <v>108</v>
+      <c r="S43" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46262.16926818287</v>
+        <v>46263.17081568287</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5557,8 +5557,8 @@
       <c r="R69" s="8">
         <v>46262</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>126</v>
+      <c r="S69" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -1646,7 +1646,7 @@
         <v>46197.84318319445</v>
       </c>
       <c r="D4" s="5">
-        <v>46197.8432930787</v>
+        <v>46263.77739836805</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>46197.84431706018</v>
       </c>
       <c r="D9" s="8">
-        <v>46197.84432748843</v>
+        <v>46263.76700403936</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2951,7 +2951,7 @@
         <v>46224.832077025465</v>
       </c>
       <c r="D25" s="8">
-        <v>46224.83209384259</v>
+        <v>46263.76745226852</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46262.18089949074</v>
+        <v>46263.76860283565</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4650,7 +4650,7 @@
         <v>46260.58671038195</v>
       </c>
       <c r="D54" s="5">
-        <v>46260.59069322917</v>
+        <v>46263.76957377315</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4825,7 +4825,7 @@
         <v>46260.5869990625</v>
       </c>
       <c r="D57" s="8">
-        <v>46260.58701207176</v>
+        <v>46263.76959292824</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>205</v>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46260.59071152778</v>
+        <v>46263.76967357639</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46263.17081568287</v>
+        <v>46263.77353957176</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46258.19795055556</v>
+        <v>46263.77368297454</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46260.59090943287</v>
+        <v>46263.77374159722</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46260.59092870371</v>
+        <v>46263.77409542824</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46261.20224831019</v>
+        <v>46263.77417350694</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46260.59096447917</v>
+        <v>46263.77543009259</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46195.58618233797</v>
+        <v>46263.77570484954</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46260.591004409725</v>
+        <v>46263.77620959491</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46260.59102431713</v>
+        <v>46263.77653796296</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46195.5866459838</v>
+        <v>46263.77670127315</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46263.77368297454</v>
+        <v>46265.16917417824</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.56257947917</v>
+        <v>46265.16917706019</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46223.56257876157</v>
+        <v>46265.16918952546</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46263.77543009259</v>
+        <v>46265.17653545139</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>263</v>
@@ -6392,8 +6392,8 @@
       <c r="R84" s="5">
         <v>46272</v>
       </c>
-      <c r="S84" s="11" t="s">
-        <v>108</v>
+      <c r="S84" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="304">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -4599,9 +4599,11 @@
       <c r="B53" s="8">
         <v>46195.5353693287</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46265.871350057874</v>
+      </c>
       <c r="D53" s="8">
-        <v>46260.58700864583</v>
+        <v>46265.87136106481</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4636,8 +4638,12 @@
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="T53" s="9">
+        <v>1</v>
+      </c>
+      <c r="U53" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -4996,9 +5002,11 @@
       <c r="B60" s="5">
         <v>46195.535427650466</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46265.87132972223</v>
+      </c>
       <c r="D60" s="5">
-        <v>46263.76967357639</v>
+        <v>46265.8713505787</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5046,7 +5054,7 @@
         <v>32</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>33</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3539,7 +3539,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46209.61764521991</v>
+        <v>46266.16875239583</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46260.590860428245</v>
+        <v>46266.16874368055</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46265.16917417824</v>
+        <v>46266.20393454861</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5734,8 +5734,8 @@
       <c r="R72" s="5">
         <v>46265</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>126</v>
+      <c r="S72" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46263.77374159722</v>
+        <v>46266.168727870376</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46223.56267032407</v>
+        <v>46266.16872998842</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46223.562669756946</v>
+        <v>46266.16873424768</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>165</v>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46263.77570484954</v>
+        <v>46266.17209177083</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>272</v>
@@ -6616,8 +6616,8 @@
       <c r="R88" s="5">
         <v>46273</v>
       </c>
-      <c r="S88" s="11" t="s">
-        <v>108</v>
+      <c r="S88" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -482,118 +482,118 @@
     <t>Generacion OC Fabricación Externa OT 4363,Fabricación estructura proveedor externo OT 4363</t>
   </si>
   <si>
+    <t>1215927805840763</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>1215927805840780</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4363</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>1215932734105392</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4363</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215932734105404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4363 </t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115811</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215932734115828</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215922055649560</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259222</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215922057259244</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215932734132723</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Propuesta Fabricación externa  OT 4363,propuesta Corte Laser OT 4363,Propuesta Corte plasma OT 4363,Propuesta Mecanizado OT 4363, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734142205</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215927805840763</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4363,Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>1215927805840780</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4363</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa  OT 4363,Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>1215932734105392</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4363</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215932734105404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4363 </t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115811</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215932734115828</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4363 ,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215922055649560</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259222</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215922057259244</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215932734132723</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Propuesta Fabricación externa  OT 4363,propuesta Corte Laser OT 4363,Propuesta Corte plasma OT 4363,Propuesta Mecanizado OT 4363, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734142205</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215941551854210</t>
@@ -3366,7 +3366,7 @@
         <v>46209.61768758102</v>
       </c>
       <c r="D32" s="5">
-        <v>46259.18154832176</v>
+        <v>46267.18400015046</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3410,8 +3410,8 @@
       <c r="R32" s="5">
         <v>46266</v>
       </c>
-      <c r="S32" s="12" t="s">
-        <v>126</v>
+      <c r="S32" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46195.53522605324</v>
@@ -3467,7 +3467,7 @@
         <v>83</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46195.5352309375</v>
@@ -3489,7 +3489,7 @@
         <v>46209.61763451389</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3522,7 +3522,7 @@
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46195.53523623843</v>
@@ -3542,16 +3542,16 @@
         <v>46266.16875239583</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46266</v>
@@ -3572,7 +3572,7 @@
         <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>26</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46195.535239398145</v>
@@ -3597,7 +3597,7 @@
         <v>46239.18270481481</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3627,7 +3627,7 @@
         <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46195.53524336805</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46195.53524819444</v>
@@ -3717,7 +3717,7 @@
         <v>46209.82155890046</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46195.5348887037</v>
@@ -3770,7 +3770,7 @@
         <v>46198.51053421297</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46195.535254629634</v>
@@ -3821,16 +3821,16 @@
         <v>46213.180665555556</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46206</v>
@@ -3848,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46206</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46195.53526092593</v>
@@ -3886,16 +3886,16 @@
         <v>46221.19570064815</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="8">
         <v>46213</v>
@@ -3913,13 +3913,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46213</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46195.53526833333</v>
@@ -3957,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46223</v>
@@ -3978,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46223</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46195.53528606481</v>
@@ -4014,16 +4014,16 @@
         <v>46263.76860283565</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="8">
         <v>46269</v>
@@ -4041,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4056,7 +4056,7 @@
         <v>46269</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4083,10 +4083,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4102,7 +4102,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>165</v>
@@ -4134,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4153,7 +4153,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>165</v>
@@ -4295,10 +4295,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46241</v>
@@ -4421,10 +4421,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4508,7 +4508,7 @@
         <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>188</v>
@@ -4547,10 +4547,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I52" s="5">
         <v>46241</v>
@@ -4864,7 +4864,7 @@
         <v>191</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>191</v>
@@ -5015,10 +5015,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I60" s="5">
         <v>46255</v>
@@ -5039,7 +5039,7 @@
         <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>191</v>
@@ -5078,10 +5078,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="I61" s="8">
         <v>46255</v>
@@ -5131,10 +5131,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I62" s="5">
         <v>46255</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46266.16874368055</v>
+        <v>46267.18399873843</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5444,7 +5444,7 @@
         <v>169</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>230</v>
@@ -5455,8 +5455,8 @@
       <c r="R67" s="8">
         <v>46266</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>126</v>
+      <c r="S67" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>232</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46266.168727870376</v>
+        <v>46267.18399990741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>247</v>
@@ -5890,7 +5890,7 @@
         <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>232</v>
@@ -5901,8 +5901,8 @@
       <c r="R75" s="8">
         <v>46266</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>126</v>
+      <c r="S75" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46263.77409542824</v>
+        <v>46267.168226180554</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6053,7 +6053,7 @@
         <v>232</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>232</v>
@@ -6065,7 +6065,7 @@
         <v>46267</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46223.56275505787</v>
+        <v>46267.16822049768</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>165</v>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46223.56275440972</v>
+        <v>46267.16822202546</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -6220,7 +6220,7 @@
         <v>232</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>232</v>
@@ -6232,7 +6232,7 @@
         <v>46268</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
@@ -6389,7 +6389,7 @@
         <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>264</v>
@@ -6401,7 +6401,7 @@
         <v>46272</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6617,7 +6617,7 @@
         <v>46273</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46263.77620959491</v>
+        <v>46267.20100958333</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -6772,7 +6772,7 @@
         <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>269</v>
@@ -6783,8 +6783,8 @@
       <c r="R91" s="8">
         <v>46274</v>
       </c>
-      <c r="S91" s="11" t="s">
-        <v>108</v>
+      <c r="S91" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6941,7 +6941,7 @@
         <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>269</v>
@@ -7106,7 +7106,7 @@
         <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>292</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46267.168226180554</v>
+        <v>46268.19665978009</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6064,8 +6064,8 @@
       <c r="R78" s="5">
         <v>46267</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>163</v>
+      <c r="S78" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46263.77417350694</v>
+        <v>46268.168070300926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46223.562948425926</v>
+        <v>46268.16809245371</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>165</v>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46223.56294780092</v>
+        <v>46268.16809391204</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>165</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46263.77653796296</v>
+        <v>46268.20122461805</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -6952,8 +6952,8 @@
       <c r="R94" s="5">
         <v>46275</v>
       </c>
-      <c r="S94" s="11" t="s">
-        <v>108</v>
+      <c r="S94" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -3765,9 +3765,11 @@
       <c r="B39" s="8">
         <v>46195.5348887037</v>
       </c>
-      <c r="C39" s="9"/>
+      <c r="C39" s="8">
+        <v>46268.899198900464</v>
+      </c>
       <c r="D39" s="8">
-        <v>46198.51053421297</v>
+        <v>46268.899213067125</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3802,9 +3804,11 @@
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="12" t="s">
-        <v>91</v>
+      <c r="T39" s="9">
+        <v>1</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4009,9 +4013,11 @@
       <c r="B43" s="8">
         <v>46195.53528606481</v>
       </c>
-      <c r="C43" s="9"/>
+      <c r="C43" s="8">
+        <v>46268.899181712964</v>
+      </c>
       <c r="D43" s="8">
-        <v>46263.76860283565</v>
+        <v>46268.89919976852</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4059,10 +4065,10 @@
         <v>163</v>
       </c>
       <c r="T43" s="9">
-        <v>0</v>
-      </c>
-      <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.58430498843</v>
+        <v>46269.168789375</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.58430173611</v>
+        <v>46269.16879098379</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46268.168070300926</v>
+        <v>46269.18719766204</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>258</v>
@@ -6237,8 +6237,8 @@
       <c r="R81" s="8">
         <v>46268</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>163</v>
+      <c r="S81" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46263.77670127315</v>
+        <v>46269.200251574075</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>291</v>
@@ -7123,8 +7123,8 @@
       <c r="R97" s="8">
         <v>46276</v>
       </c>
-      <c r="S97" s="11" t="s">
-        <v>108</v>
+      <c r="S97" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -593,310 +593,310 @@
     <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>1215941551854210</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215941551854222</t>
+  </si>
+  <si>
+    <t>1215930353891784</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215930353891796</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215941551880377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Bodega:, ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734202816</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215932734202838</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215941551880760</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215927805923801</t>
+  </si>
+  <si>
+    <t>1215927805923818</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215927805923830</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>1215927805933398</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734211704</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215922057304565</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1215932734213367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Armado</t>
+  </si>
+  <si>
+    <t>1215932734213389</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215930354016401</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215930354026690</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Revestimiento,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215930354026712</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215932734228548</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215932734228560</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Bodega:</t>
+  </si>
+  <si>
+    <t>1215932734236070</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215922057367621</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215930353891849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215923636418868</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje Alabe,Montaje Rodete,Montaje motor,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215923636418880</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa , ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215922057394981</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215923636422501</t>
+  </si>
+  <si>
+    <t>1215922057413110</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215922057413127</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215930354145340</t>
+  </si>
+  <si>
+    <t>1215922057426521</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215922057426538</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1215927806064902</t>
+  </si>
+  <si>
+    <t>1215927806081804</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1215923636442061</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215923636442083</t>
+  </si>
+  <si>
+    <t>1215932734285164</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215927806138040</t>
+  </si>
+  <si>
+    <t>Pruebas FAT, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215927806138062</t>
+  </si>
+  <si>
+    <t>1215932734389748</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215941551854210</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215941551854222</t>
-  </si>
-  <si>
-    <t>1215930353891784</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215930353891796</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215941551880377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Bodega:, ot 4363  ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734202816</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215932734202838</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363  ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215941551880760</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215927805923801</t>
-  </si>
-  <si>
-    <t>1215927805923818</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Armado,Preparación Materiales,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215927805923830</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>1215927805933398</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734211704</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215922057304565</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1215932734213367</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Armado</t>
-  </si>
-  <si>
-    <t>1215932734213389</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363  ZVN 1-9-86/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215930354016401</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215930354026690</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Revestimiento,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215930354026712</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215932734228548</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215932734228560</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2,Bodega:</t>
-  </si>
-  <si>
-    <t>1215932734236070</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215922057367621</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215930353891849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215923636418868</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje Alabe,Montaje Rodete,Montaje motor,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215923636418880</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa , ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215922057394981</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215923636422501</t>
-  </si>
-  <si>
-    <t>1215922057413110</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215922057413127</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215930354145340</t>
-  </si>
-  <si>
-    <t>1215922057426521</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215922057426538</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1215927806064902</t>
-  </si>
-  <si>
-    <t>1215927806081804</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1215923636442061</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215923636442083</t>
-  </si>
-  <si>
-    <t>1215932734285164</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215927806138040</t>
-  </si>
-  <si>
-    <t>Pruebas FAT, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215927806138062</t>
-  </si>
-  <si>
-    <t>1215932734389748</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1215923636547795</t>
@@ -4017,7 +4017,7 @@
         <v>46268.899181712964</v>
       </c>
       <c r="D43" s="8">
-        <v>46268.89919976852</v>
+        <v>46270.18990378472</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4061,8 +4061,8 @@
       <c r="R43" s="8">
         <v>46269</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>163</v>
+      <c r="S43" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46195.535290266205</v>
@@ -4083,7 +4083,7 @@
         <v>46269.168789375</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4111,10 +4111,10 @@
         <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46195.53529509259</v>
@@ -4134,7 +4134,7 @@
         <v>46269.16879098379</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4162,10 +4162,10 @@
         <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4175,7 +4175,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46195.53533827546</v>
@@ -4185,7 +4185,7 @@
         <v>46195.572334930555</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4209,7 +4209,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46195.53534217592</v>
@@ -4232,16 +4232,16 @@
         <v>46241.182685694446</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46239</v>
@@ -4259,13 +4259,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46239</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46195.53534689815</v>
@@ -4295,7 +4295,7 @@
         <v>46245.168955601854</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4322,13 +4322,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46241</v>
@@ -4348,7 +4348,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46195.5353533912</v>
@@ -4358,16 +4358,16 @@
         <v>46241.18268534722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46239</v>
@@ -4385,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>119</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46239</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46195.53535798611</v>
@@ -4421,7 +4421,7 @@
         <v>46245.168955393514</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4448,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="5">
         <v>46241</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46195.535361689814</v>
@@ -4484,16 +4484,16 @@
         <v>46241.18268515046</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I51" s="8">
         <v>46239</v>
@@ -4511,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>141</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46239</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46195.53536568287</v>
@@ -4547,7 +4547,7 @@
         <v>46245.16895542824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4574,13 +4574,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46241</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46195.5353693287</v>
@@ -4612,7 +4612,7 @@
         <v>46265.87136106481</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4636,7 +4636,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46195.53537232639</v>
@@ -4665,16 +4665,16 @@
         <v>46263.76957377315</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I54" s="5">
         <v>46245</v>
@@ -4692,13 +4692,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="5">
         <v>46245</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46195.53537631944</v>
@@ -4730,16 +4730,16 @@
         <v>46260.58681349537</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46245</v>
@@ -4757,13 +4757,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46195.53538179398</v>
@@ -4785,16 +4785,16 @@
         <v>46260.586903206015</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46245</v>
@@ -4812,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46195.53540148148</v>
@@ -4840,16 +4840,16 @@
         <v>46263.76959292824</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I57" s="8">
         <v>46248</v>
@@ -4867,13 +4867,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="8">
         <v>46248</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46195.53540543982</v>
@@ -4905,16 +4905,16 @@
         <v>46260.58697668981</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46248</v>
@@ -4932,13 +4932,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46195.53541055556</v>
@@ -4960,16 +4960,16 @@
         <v>46260.58698486111</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I59" s="8">
         <v>46248</v>
@@ -4987,13 +4987,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46195.535427650466</v>
@@ -5015,7 +5015,7 @@
         <v>46265.8713505787</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5042,13 +5042,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="5">
         <v>46255</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46195.53543222223</v>
@@ -5078,7 +5078,7 @@
         <v>46260.586980127315</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5105,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46195.53543761574</v>
@@ -5131,7 +5131,7 @@
         <v>46260.58699188658</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5158,13 +5158,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46195.53545577546</v>
@@ -5184,7 +5184,7 @@
         <v>46195.56789731482</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5208,7 +5208,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46195.535458576385</v>
@@ -5231,16 +5231,16 @@
         <v>46260.59078993056</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I64" s="5">
         <v>46209</v>
@@ -5258,13 +5258,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>93</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46209</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46195.535463912034</v>
@@ -5294,16 +5294,16 @@
         <v>46260.59081489583</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I65" s="8">
         <v>46209</v>
@@ -5321,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>96</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="8">
         <v>46209</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46195.53547575232</v>
@@ -5357,16 +5357,16 @@
         <v>46260.59082912037</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I66" s="5">
         <v>46209</v>
@@ -5384,13 +5384,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q66" s="5">
         <v>46209</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46195.53552306713</v>
@@ -5420,16 +5420,16 @@
         <v>46267.18399873843</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I67" s="8">
         <v>46266</v>
@@ -5447,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="8">
         <v>46266</v>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46195.53552899306</v>
@@ -5483,7 +5483,7 @@
         <v>46195.577845057865</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5507,7 +5507,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46195.5355328588</v>
@@ -5530,7 +5530,7 @@
         <v>46263.77353957176</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5557,13 +5557,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="8">
         <v>46258</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46195.53554157408</v>
@@ -5593,7 +5593,7 @@
         <v>46262.169264571756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5620,10 +5620,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46195.53554603009</v>
@@ -5646,7 +5646,7 @@
         <v>46262.16926988426</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5673,10 +5673,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46195.535563240745</v>
@@ -5699,7 +5699,7 @@
         <v>46266.20393454861</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5726,13 +5726,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="5">
         <v>46265</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46195.53556773148</v>
@@ -5762,7 +5762,7 @@
         <v>46265.16917706019</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5789,13 +5789,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5805,7 +5805,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46195.53557388889</v>
@@ -5815,7 +5815,7 @@
         <v>46265.16918952546</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5842,13 +5842,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46195.53559528935</v>
@@ -5868,7 +5868,7 @@
         <v>46267.18399990741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5893,13 +5893,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q75" s="8">
         <v>46266</v>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46195.53559965278</v>
@@ -5929,7 +5929,7 @@
         <v>46266.16872998842</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5954,13 +5954,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46195.53560584491</v>
@@ -5980,7 +5980,7 @@
         <v>46266.16873424768</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6005,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46195.53562898148</v>
@@ -6031,7 +6031,7 @@
         <v>46268.19665978009</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6056,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46195.535633541665</v>
@@ -6092,7 +6092,7 @@
         <v>46267.16822049768</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6119,13 +6119,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46195.535639050926</v>
@@ -6145,7 +6145,7 @@
         <v>46267.16822202546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6172,13 +6172,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46195.53570565972</v>
@@ -6198,7 +6198,7 @@
         <v>46269.18719766204</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6223,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q81" s="8">
         <v>46268</v>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46195.535710509255</v>
@@ -6259,7 +6259,7 @@
         <v>46268.16809245371</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6286,13 +6286,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46195.53571621528</v>
@@ -6312,7 +6312,7 @@
         <v>46268.16809391204</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6339,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6355,7 +6355,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46195.53573584491</v>
@@ -6365,7 +6365,7 @@
         <v>46265.17653545139</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6392,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46272</v>
@@ -6407,7 +6407,7 @@
         <v>46272</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6428,7 +6428,7 @@
         <v>46223.56302869213</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6455,10 +6455,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>266</v>
@@ -6481,7 +6481,7 @@
         <v>46223.56302799769</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6508,10 +6508,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>266</v>
@@ -6623,7 +6623,7 @@
         <v>46273</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46195.58613703704</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6672,7 +6672,7 @@
         <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>277</v>
@@ -6695,7 +6695,7 @@
         <v>46195.58613380787</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6725,7 +6725,7 @@
         <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>277</v>
@@ -6790,7 +6790,7 @@
         <v>46274</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>46223.56325827546</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6841,7 +6841,7 @@
         <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>282</v>
@@ -6864,7 +6864,7 @@
         <v>46223.56325763889</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6894,7 +6894,7 @@
         <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>282</v>
@@ -6923,10 +6923,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6959,7 +6959,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -6980,16 +6980,16 @@
         <v>46195.58645966435</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -7008,7 +7008,7 @@
         <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>287</v>
@@ -7031,16 +7031,16 @@
         <v>46195.58645685185</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7059,7 +7059,7 @@
         <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>289</v>
@@ -7088,10 +7088,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I97" s="8">
         <v>46276</v>
@@ -7124,7 +7124,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7145,16 +7145,16 @@
         <v>46195.58660633102</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7173,7 +7173,7 @@
         <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>291</v>
@@ -7196,16 +7196,16 @@
         <v>46195.5866030787</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="8">
@@ -7224,7 +7224,7 @@
         <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>291</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46265.17653545139</v>
+        <v>46272.16760431713</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>262</v>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46223.56302869213</v>
+        <v>46272.16758511574</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>164</v>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46223.56302799769</v>
+        <v>46272.16758680556</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>164</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -896,40 +896,40 @@
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
+    <t>1215923636547795</t>
+  </si>
+  <si>
+    <t>RE-PINTADO, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215923636547812</t>
+  </si>
+  <si>
+    <t>1215923636550356</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Coordinacion Entrega con Cliente,Embalaje,Despacho</t>
+  </si>
+  <si>
+    <t>1215923636552662</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215923636547795</t>
-  </si>
-  <si>
-    <t>RE-PINTADO, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215923636547812</t>
-  </si>
-  <si>
-    <t>1215923636550356</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Coordinacion Entrega con Cliente,Embalaje,Despacho</t>
-  </si>
-  <si>
-    <t>1215923636552662</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215923636552684</t>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46272.16760431713</v>
+        <v>46273.15996618055</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>262</v>
@@ -6406,8 +6406,8 @@
       <c r="R84" s="5">
         <v>46272</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>264</v>
+      <c r="S84" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46195.53574096065</v>
@@ -6461,7 +6461,7 @@
         <v>164</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6471,7 +6471,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46195.53574520833</v>
@@ -6514,7 +6514,7 @@
         <v>164</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46195.53576230324</v>
@@ -6534,7 +6534,7 @@
         <v>46195.58073400463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6558,7 +6558,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6571,26 +6571,26 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46195.535766319445</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46266.17209177083</v>
+        <v>46273.16806848379</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6608,13 +6608,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -6623,7 +6623,7 @@
         <v>46273</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46195.58613703704</v>
+        <v>46273.16807002315</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>164</v>
@@ -6650,10 +6650,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>274</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6669,7 +6669,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>164</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.58613380787</v>
+        <v>46273.168073912035</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>164</v>
@@ -6701,10 +6701,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="I90" s="5">
         <v>46273</v>
@@ -6722,7 +6722,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>164</v>
@@ -6775,13 +6775,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q91" s="8">
         <v>46274</v>
@@ -6790,7 +6790,7 @@
         <v>46274</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="5">
         <v>46275</v>
@@ -6959,7 +6959,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>162</v>
@@ -7124,7 +7124,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -929,22 +929,22 @@
     <t>RE-PINTADO, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>1215923636552684</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1215927806183846</t>
+  </si>
+  <si>
+    <t>1215927806190540</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215923636552684</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1215927806183846</t>
-  </si>
-  <si>
-    <t>1215927806190540</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
   </si>
   <si>
     <t>1215922057558752</t>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46273.16806848379</v>
+        <v>46274.13346145833</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>271</v>
@@ -6622,8 +6622,8 @@
       <c r="R88" s="5">
         <v>46273</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>275</v>
+      <c r="S88" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46195.535772118055</v>
@@ -6675,7 +6675,7 @@
         <v>164</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46195.53577681713</v>
@@ -6728,7 +6728,7 @@
         <v>164</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6738,17 +6738,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46195.535800763886</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46267.20100958333</v>
+        <v>46274.16807314815</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6790,7 +6790,7 @@
         <v>46274</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.56325827546</v>
+        <v>46274.16807092592</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>164</v>
@@ -6838,7 +6838,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>164</v>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46223.56325763889</v>
+        <v>46274.16807201389</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>164</v>
@@ -6891,7 +6891,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>164</v>
@@ -6959,7 +6959,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7124,7 +7124,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -944,22 +944,22 @@
     <t>Embalaje</t>
   </si>
   <si>
+    <t>1215922057558752</t>
+  </si>
+  <si>
+    <t>Embalaje, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215922057558769</t>
+  </si>
+  <si>
+    <t>1215923636550375</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215922057558752</t>
-  </si>
-  <si>
-    <t>Embalaje, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215922057558769</t>
-  </si>
-  <si>
-    <t>1215923636550375</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>1215930354324584</t>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46274.16807314815</v>
+        <v>46275.154713564814</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>279</v>
@@ -6789,8 +6789,8 @@
       <c r="R91" s="8">
         <v>46274</v>
       </c>
-      <c r="S91" s="12" t="s">
-        <v>280</v>
+      <c r="S91" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46195.53580561343</v>
@@ -6844,7 +6844,7 @@
         <v>164</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46195.5358103125</v>
@@ -6897,7 +6897,7 @@
         <v>164</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6907,17 +6907,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46195.535868506944</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46268.20122461805</v>
+        <v>46275.168104537035</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6959,7 +6959,7 @@
         <v>46275</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46195.58645966435</v>
+        <v>46275.16811569444</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>164</v>
@@ -7005,7 +7005,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>164</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46195.58645685185</v>
+        <v>46275.168116851855</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>164</v>
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>164</v>
@@ -7124,7 +7124,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -959,28 +959,28 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1215930354324584</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Planos Preliminar, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215930354324606</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,PACKING LIST,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1215932734471432</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Costos,Logistica:,Gestion</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215930354324584</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Planos Preliminar, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215930354324606</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ot 4363 ZVN 1-9-86/2,PACKING LIST,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1215932734471432</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Costos,Logistica:,Gestion</t>
   </si>
   <si>
     <t>1215930354344887</t>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46275.168104537035</v>
+        <v>46276.131211932865</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>284</v>
@@ -6958,8 +6958,8 @@
       <c r="R94" s="5">
         <v>46275</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>285</v>
+      <c r="S94" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46195.535874293986</v>
@@ -7011,7 +7011,7 @@
         <v>164</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46195.535884780096</v>
@@ -7062,7 +7062,7 @@
         <v>164</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7072,17 +7072,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46195.53591063658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46269.200251574075</v>
+        <v>46276.16844678241</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7115,7 +7115,7 @@
         <v>162</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="8">
         <v>46276</v>
@@ -7124,7 +7124,7 @@
         <v>46276</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46195.58660633102</v>
+        <v>46276.168440416666</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>164</v>
@@ -7170,13 +7170,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46195.5866030787</v>
+        <v>46276.16843336806</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>164</v>
@@ -7221,13 +7221,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>164</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7324,7 +7324,7 @@
         <v>296</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>296</v>
@@ -7387,7 +7387,7 @@
         <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>296</v>

--- a/data/50001566 - XEMORTIZ.xlsx
+++ b/data/50001566 - XEMORTIZ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="303">
   <si>
     <t>50001566 - XEMORTIZ</t>
   </si>
@@ -978,9 +978,6 @@
   </si>
   <si>
     <t>Costos,Logistica:,Gestion</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215930354344887</t>
@@ -7079,7 +7076,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46276.16844678241</v>
+        <v>46277.13169126157</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>290</v>
@@ -7123,8 +7120,8 @@
       <c r="R97" s="8">
         <v>46276</v>
       </c>
-      <c r="S97" s="12" t="s">
-        <v>292</v>
+      <c r="S97" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7135,7 +7132,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46195.53591612268</v>
@@ -7186,7 +7183,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46195.535920254624</v>
@@ -7237,7 +7234,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46195.53593680555</v>
@@ -7247,7 +7244,7 @@
         <v>46195.58118991899</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
@@ -7271,7 +7268,7 @@
         <v>26</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>26</v>
@@ -7284,7 +7281,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46195.535940173606</v>
@@ -7294,16 +7291,16 @@
         <v>46195.58682732639</v>
       </c>
       <c r="E101" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="9" t="s">
+      <c r="H101" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="I101" s="8">
         <v>46279</v>
@@ -7321,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>290</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="8">
         <v>46279</v>
@@ -7347,7 +7344,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46195.53594497685</v>
@@ -7357,7 +7354,7 @@
         <v>46195.58676837963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7384,13 +7381,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>290</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="5">
         <v>46279</v>
